--- a/Result/checksun_type/電子觸控白板.xlsx
+++ b/Result/checksun_type/電子觸控白板.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>578.0</t>
+          <t>5114.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-39.66</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>76.10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,67 +1009,67 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>28.76</t>
+          <t>48.37</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>73.38000000000001</t>
+          <t>73.62</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>72.71</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>68.19</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>68.51</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-12.47</t>
+          <t>-10.21</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-74.47</t>
+          <t>-75.11</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>135673.2373371925</t>
+          <t>136354.1510115607</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>42261.0</t>
+          <t>404577.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>43168.4</t>
+          <t>112272.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>71541.8</t>
+          <t>106038.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>40084.32</t>
+          <t>47927.76</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-28373</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>4503.448780935657</t>
+          <t>7603.661126890231</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-1480.07</v>
+        <v>24654.83</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,42 +1177,42 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-4.25191946836667</t>
+          <t>117.8366423644483</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-51.85176028481013</t>
+          <t>90.00919392228472</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>33.2519674685127</t>
+          <t>22.16097965796244</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>16.12</t>
+          <t>16.34</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>578.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-23.93</t>
+          <t>-39.66</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,275 +1440,275 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>28.76</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.92</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
+          <t>73.38000000000001</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>72.71</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>68.4</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>-12.47</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>7.72</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-74.47</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>136354.1510115607</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>42261.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>43168.4</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>71541.8</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>40084.32</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-28373</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>4503.448780935657</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>-1480.07</v>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>72.9</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>青雲</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>青雲</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>117.8366423644483</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>90.00919392228472</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>22.16097965796244</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>24.14</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>16.34</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>6.00%</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>2.42%</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>49.69</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>2706</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>青雲-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
           <t>73.2</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>72.32</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>67.81</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>68.33</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>-13.38</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>7.72</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-73.68</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>135673.2373371925</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>48823.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>54530.4</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>71688.6</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>39731.78</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>-17158</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>5591.361638466338</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>56.79</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>72.9</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>青雲</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>青雲</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>-4.25191946836667</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>-51.85176028481013</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>33.2519674685127</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>3.66</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>24.14</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>16.12</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>6.00%</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>2.42%</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>45.88</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>2670</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>青雲-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>72.5</t>
-        </is>
-      </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>21.70</t>
+          <t>-23.93</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>13.07</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>72.96</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>71.85</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>67.68</t>
+          <t>67.81</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>68.37</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-13.38</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-72.80</t>
+          <t>-73.68</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>135673.2373371925</t>
+          <t>136354.1510115607</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>20226.0</t>
+          <t>48823.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>94009.8</t>
+          <t>54530.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>77244.4</t>
+          <t>71688.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>38919.48</t>
+          <t>39731.78</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>16765</t>
+          <t>-17158</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>6597.648045869192</t>
+          <t>5591.361638466338</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>1547.2</v>
+        <v>56.79</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,42 +2039,42 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-4.25191946836667</t>
+          <t>117.8366423644483</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-51.85176028481013</t>
+          <t>90.00919392228472</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>33.2519674685127</t>
+          <t>22.16097965796244</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>16.12</t>
+          <t>16.34</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>611.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,74 +2186,74 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>21.70</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-08-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>72.7</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-0.46</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>27.98</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>72.3</t>
@@ -2266,12 +2266,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,62 +2317,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>73.97999999999999</t>
+          <t>72.96</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>71.49</t>
+          <t>71.85</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>67.61</t>
+          <t>67.68</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>68.44</t>
+          <t>68.37</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-71.89</t>
+          <t>-72.80</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,45 +2392,45 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>135673.2373371925</t>
+          <t>136354.1510115607</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>45477.0</t>
+          <t>20226.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>100809.6</t>
+          <t>94009.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>78769.4</t>
+          <t>77244.4</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>38684.38</t>
+          <t>38919.48</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>22040</t>
+          <t>16765</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>7515.911547269975</t>
+          <t>6597.648045869192</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>6685.07</v>
+        <v>1547.2</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,42 +2470,42 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-4.25191946836667</t>
+          <t>117.8366423644483</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-51.85176028481013</t>
+          <t>90.00919392228472</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>33.2519674685127</t>
+          <t>22.16097965796244</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>16.12</t>
+          <t>16.34</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>813.0</t>
+          <t>611.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>29.61</t>
+          <t>27.98</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>17.56</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>74.74</t>
+          <t>73.97999999999999</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>71.16</t>
+          <t>71.49</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>67.52</t>
+          <t>67.61</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>68.49</t>
+          <t>68.44</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-71.58</t>
+          <t>-71.89</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>135673.2373371925</t>
+          <t>136354.1510115607</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>59055.0</t>
+          <t>45477.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>99805.0</t>
+          <t>100809.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>77003.9</t>
+          <t>78769.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>38043.2</t>
+          <t>38684.38</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>22801</t>
+          <t>22040</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>7666.974277312432</t>
+          <t>7515.911547269975</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>11080.66</v>
+        <v>6685.07</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,42 +2901,42 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-4.25191946836667</t>
+          <t>117.8366423644483</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-51.85176028481013</t>
+          <t>90.00919392228472</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>33.2519674685127</t>
+          <t>22.16097965796244</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>16.12</t>
+          <t>16.34</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1337.0</t>
+          <t>813.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>33.70</t>
+          <t>29.61</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19.90</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>52.18</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>75.38</t>
+          <t>74.74</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>70.89</t>
+          <t>71.16</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>67.41</t>
+          <t>67.52</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>68.53</t>
+          <t>68.49</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>12.33</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-71.91</t>
+          <t>-71.58</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>135673.2373371925</t>
+          <t>136354.1510115607</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>99071.0</t>
+          <t>59055.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>99915.2</t>
+          <t>99805.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>74730.4</t>
+          <t>77003.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>37063.94</t>
+          <t>38043.2</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>25184</t>
+          <t>22801</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>7046.303976305286</t>
+          <t>7666.974277312432</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>15509.56</v>
+        <v>11080.66</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,42 +3332,42 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-4.25191946836667</t>
+          <t>117.8366423644483</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-51.85176028481013</t>
+          <t>90.00919392228472</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>33.2519674685127</t>
+          <t>22.16097965796244</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>16.12</t>
+          <t>16.34</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3208.0</t>
+          <t>1337.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>32.34</t>
+          <t>33.70</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>47.74</t>
+          <t>19.90</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-14.81</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>27.12</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>72.83</t>
+          <t>52.18</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>75.72</t>
+          <t>75.38</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>70.44</t>
+          <t>70.89</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>67.31</t>
+          <t>67.41</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>68.57</t>
+          <t>68.53</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>24.10</t>
+          <t>12.33</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-72.78</t>
+          <t>-71.91</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>135673.2373371925</t>
+          <t>136354.1510115607</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>246220.0</t>
+          <t>99071.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>88846.8</t>
+          <t>99915.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>67134.6</t>
+          <t>74730.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>35428.7</t>
+          <t>37063.94</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>21712</t>
+          <t>25184</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>5507.530535506201</t>
+          <t>7046.303976305286</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>16995.21</v>
+        <v>15509.56</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,22 +3763,22 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-4.25191946836667</t>
+          <t>117.8366423644483</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-51.85176028481013</t>
+          <t>90.00919392228472</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>33.2519674685127</t>
+          <t>22.16097965796244</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
@@ -3788,17 +3788,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>16.12</t>
+          <t>16.34</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>723.0</t>
+          <t>3208.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3990,12 +3990,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>47.74</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>-14.81</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>27.12</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>97.13</t>
+          <t>72.83</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>76.14000000000001</t>
+          <t>75.72</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>70.44</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>67.31</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>68.57</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>24.10</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-74.42</t>
+          <t>-72.78</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>135673.2373371925</t>
+          <t>136354.1510115607</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>54225.0</t>
+          <t>246220.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>60479.0</t>
+          <t>88846.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>57840.5</t>
+          <t>67134.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>30749.9</t>
+          <t>35428.7</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>21712</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>3418.861139151172</t>
+          <t>5507.530535506201</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>2744.64</v>
+        <v>16995.21</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,42 +4194,42 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-4.25191946836667</t>
+          <t>117.8366423644483</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-51.85176028481013</t>
+          <t>90.00919392228472</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>33.2519674685127</t>
+          <t>22.16097965796244</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>16.12</t>
+          <t>16.34</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>527.0</t>
+          <t>723.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4421,12 +4421,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,17 +4457,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>91.38</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4477,57 +4477,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.14000000000001</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>69.34</t>
+          <t>70.05</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>67.03</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>68.57</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>54.28</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-77.29</t>
+          <t>-74.42</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>135673.2373371925</t>
+          <t>136354.1510115607</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>40454.0</t>
+          <t>54225.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>56729.2</t>
+          <t>60479.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>58477.6</t>
+          <t>57840.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>29829.24</t>
+          <t>30749.9</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1748</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>3541.446915050525</t>
+          <t>3418.861139151172</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>2859.55</v>
+        <v>2744.64</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,27 +4625,27 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-4.25191946836667</t>
+          <t>117.8366423644483</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-51.85176028481013</t>
+          <t>90.00919392228472</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>33.2519674685127</t>
+          <t>22.16097965796244</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>16.12</t>
+          <t>16.34</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>774.0</t>
+          <t>527.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,74 +4772,74 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-2.99</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-08-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>77.0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-4.05</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-0.46</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-2.04</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>77.0</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
       <c r="T11" t="inlineStr">
         <is>
           <t>72.3</t>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>91.38</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.13</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>68.68</t>
+          <t>69.34</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>66.84</t>
+          <t>67.03</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>68.53</t>
+          <t>68.57</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>66.77</t>
+          <t>54.28</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-80.37</t>
+          <t>-77.29</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>135673.2373371925</t>
+          <t>136354.1510115607</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>59606.0</t>
+          <t>40454.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>54202.8</t>
+          <t>56729.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>55330.9</t>
+          <t>58477.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>29250.26</t>
+          <t>29829.24</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1128</t>
+          <t>-1748</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>3665.428501645016</t>
+          <t>3541.446915050525</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>4397.04</v>
+        <v>2859.55</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,27 +5056,27 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-4.25191946836667</t>
+          <t>117.8366423644483</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-51.85176028481013</t>
+          <t>90.00919392228472</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>33.2519674685127</t>
+          <t>22.16097965796244</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>16.12</t>
+          <t>16.34</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>581.0</t>
+          <t>774.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,22 +5213,22 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,33 +5298,33 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5339,57 +5339,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>73.24</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>67.97</t>
+          <t>68.68</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>66.84</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>68.47</t>
+          <t>68.53</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>75.26</t>
+          <t>66.77</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-83.65</t>
+          <t>-80.37</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,45 +5409,45 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>135673.2373371925</t>
+          <t>136354.1510115607</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>43729.0</t>
+          <t>59606.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>49545.6</t>
+          <t>54202.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>50608.2</t>
+          <t>55330.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>28300.98</t>
+          <t>29250.26</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1062</t>
+          <t>-1128</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>3532.408009865368</t>
+          <t>3665.428501645016</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>4384.42</v>
+        <v>4397.04</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,27 +5487,27 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-4.25191946836667</t>
+          <t>117.8366423644483</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-51.85176028481013</t>
+          <t>90.00919392228472</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>33.2519674685127</t>
+          <t>22.16097965796244</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>16.12</t>
+          <t>16.34</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/電子觸控白板.xlsx
+++ b/Result/checksun_type/電子觸控白板.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5114.0</t>
+          <t>1299.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>76.10</t>
+          <t>19.33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-7.09</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>48.37</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>73.62</t>
+          <t>73.17999999999999</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>73.16</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>68.19</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>68.51</t>
+          <t>68.55</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-10.21</t>
+          <t>-25.43</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-75.11</t>
+          <t>-76.60</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>136354.1510115607</t>
+          <t>136360.4437229437</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>404577.0</t>
+          <t>93810.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>112272.8</t>
+          <t>121939.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>106038.9</t>
+          <t>111374.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>47927.76</t>
+          <t>49406.96</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>10564</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>7603.661126890231</t>
+          <t>9360.846181135705</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>24654.83</v>
+        <v>19025.36</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>16.34</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1257,27 +1257,27 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>578.0</t>
+          <t>5114.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-39.66</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>76.10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,67 +1440,67 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>28.76</t>
+          <t>48.37</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>73.38000000000001</t>
+          <t>73.62</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>72.71</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>68.19</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>68.51</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-12.47</t>
+          <t>-10.21</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-74.47</t>
+          <t>-75.11</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>136354.1510115607</t>
+          <t>136360.4437229437</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>42261.0</t>
+          <t>404577.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>43168.4</t>
+          <t>112272.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>71541.8</t>
+          <t>106038.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>40084.32</t>
+          <t>47927.76</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-28373</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>4503.448780935657</t>
+          <t>7603.661126890231</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-1480.07</v>
+        <v>24654.83</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>16.34</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1688,27 +1688,27 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>578.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-23.93</t>
+          <t>-39.66</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,275 +1871,275 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>28.76</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.92</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
+          <t>73.38000000000001</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>72.71</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>68.4</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>-12.47</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>7.72</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-74.47</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>136360.4437229437</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>42261.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>43168.4</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>71541.8</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>40084.32</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>-28373</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>4503.448780935657</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>-1480.07</v>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>72.9</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>青雲</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>青雲</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>117.8366423644483</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>90.00919392228472</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>22.16097965796244</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>24.14</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>15.36</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>6.00%</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>2.42%</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>48.7</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>2544</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>青雲-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業平上櫃</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
           <t>73.2</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>72.32</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>67.81</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>68.33</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>-13.38</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>7.72</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-73.68</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>136354.1510115607</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>48823.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>54530.4</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>71688.6</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>39731.78</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>-17158</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>5591.361638466338</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>56.79</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>72.9</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>青雲</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>青雲</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>117.8366423644483</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>90.00919392228472</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>22.16097965796244</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>3.66</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>24.14</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>16.34</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>6.00%</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>2.42%</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>49.69</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>2706</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>青雲-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>72.5</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>21.70</t>
+          <t>-23.93</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>13.07</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>72.96</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>71.85</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>67.68</t>
+          <t>67.81</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>68.37</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-13.38</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-72.80</t>
+          <t>-73.68</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>136354.1510115607</t>
+          <t>136360.4437229437</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>20226.0</t>
+          <t>48823.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>94009.8</t>
+          <t>54530.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>77244.4</t>
+          <t>71688.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>38919.48</t>
+          <t>39731.78</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>16765</t>
+          <t>-17158</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>6597.648045869192</t>
+          <t>5591.361638466338</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>1547.2</v>
+        <v>56.79</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>16.34</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2550,27 +2550,27 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>611.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,74 +2617,74 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-2.13</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-2.13</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>21.70</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-08-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>72.7</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>3.07</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-0.49</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>27.98</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
       <c r="T6" t="inlineStr">
         <is>
           <t>72.3</t>
@@ -2697,12 +2697,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,62 +2748,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>73.97999999999999</t>
+          <t>72.96</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>71.49</t>
+          <t>71.85</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>67.61</t>
+          <t>67.68</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>68.44</t>
+          <t>68.37</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-71.89</t>
+          <t>-72.80</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,45 +2823,45 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>136354.1510115607</t>
+          <t>136360.4437229437</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>45477.0</t>
+          <t>20226.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>100809.6</t>
+          <t>94009.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>78769.4</t>
+          <t>77244.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>38684.38</t>
+          <t>38919.48</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>22040</t>
+          <t>16765</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>7515.911547269975</t>
+          <t>6597.648045869192</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>6685.07</v>
+        <v>1547.2</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>16.34</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2981,27 +2981,27 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>813.0</t>
+          <t>611.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>29.61</t>
+          <t>27.98</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>17.56</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>74.74</t>
+          <t>73.97999999999999</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>71.16</t>
+          <t>71.49</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>67.52</t>
+          <t>67.61</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>68.49</t>
+          <t>68.44</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-71.58</t>
+          <t>-71.89</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>136354.1510115607</t>
+          <t>136360.4437229437</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>59055.0</t>
+          <t>45477.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>99805.0</t>
+          <t>100809.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>77003.9</t>
+          <t>78769.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>38043.2</t>
+          <t>38684.38</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>22801</t>
+          <t>22040</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>7666.974277312432</t>
+          <t>7515.911547269975</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>11080.66</v>
+        <v>6685.07</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>16.34</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3412,27 +3412,27 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1337.0</t>
+          <t>813.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>33.70</t>
+          <t>29.61</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19.90</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>52.18</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>75.38</t>
+          <t>74.74</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>70.89</t>
+          <t>71.16</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>67.41</t>
+          <t>67.52</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>68.53</t>
+          <t>68.49</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>12.33</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-71.91</t>
+          <t>-71.58</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>136354.1510115607</t>
+          <t>136360.4437229437</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>99071.0</t>
+          <t>59055.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>99915.2</t>
+          <t>99805.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>74730.4</t>
+          <t>77003.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>37063.94</t>
+          <t>38043.2</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>25184</t>
+          <t>22801</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>7046.303976305286</t>
+          <t>7666.974277312432</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>15509.56</v>
+        <v>11080.66</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>16.34</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3843,27 +3843,27 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3208.0</t>
+          <t>1337.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>32.34</t>
+          <t>33.70</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3990,12 +3990,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>47.74</t>
+          <t>19.90</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-14.81</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>27.12</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>72.83</t>
+          <t>52.18</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>75.72</t>
+          <t>75.38</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>70.44</t>
+          <t>70.89</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>67.31</t>
+          <t>67.41</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>68.57</t>
+          <t>68.53</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>24.10</t>
+          <t>12.33</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-72.78</t>
+          <t>-71.91</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>136354.1510115607</t>
+          <t>136360.4437229437</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>246220.0</t>
+          <t>99071.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>88846.8</t>
+          <t>99915.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>67134.6</t>
+          <t>74730.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>35428.7</t>
+          <t>37063.94</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>21712</t>
+          <t>25184</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>5507.530535506201</t>
+          <t>7046.303976305286</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>16995.21</v>
+        <v>15509.56</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4219,17 +4219,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>16.34</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4274,27 +4274,27 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>723.0</t>
+          <t>3208.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4421,12 +4421,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>47.74</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>-14.81</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>27.12</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>97.13</t>
+          <t>72.83</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>76.14000000000001</t>
+          <t>75.72</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>70.44</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>67.31</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>68.57</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>24.10</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-74.42</t>
+          <t>-72.78</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>136354.1510115607</t>
+          <t>136360.4437229437</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>54225.0</t>
+          <t>246220.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>60479.0</t>
+          <t>88846.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>57840.5</t>
+          <t>67134.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>30749.9</t>
+          <t>35428.7</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>21712</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>3418.861139151172</t>
+          <t>5507.530535506201</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>2744.64</v>
+        <v>16995.21</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,22 +4645,22 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>16.34</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4705,27 +4705,27 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>527.0</t>
+          <t>723.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,17 +4888,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>91.38</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4908,57 +4908,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.14000000000001</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>69.34</t>
+          <t>70.05</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>67.03</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>68.57</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>54.28</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-77.29</t>
+          <t>-74.42</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>136354.1510115607</t>
+          <t>136360.4437229437</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>40454.0</t>
+          <t>54225.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>56729.2</t>
+          <t>60479.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>58477.6</t>
+          <t>57840.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>29829.24</t>
+          <t>30749.9</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1748</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>3541.446915050525</t>
+          <t>3418.861139151172</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>2859.55</v>
+        <v>2744.64</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>16.34</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,27 +5136,27 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>774.0</t>
+          <t>527.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,74 +5203,74 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-8.51</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-2.13</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-2.99</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-08-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>77.0</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-2.67</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-0.49</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-2.04</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>77.0</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
       <c r="T12" t="inlineStr">
         <is>
           <t>72.3</t>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>91.38</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.13</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>68.68</t>
+          <t>69.34</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>66.84</t>
+          <t>67.03</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>68.53</t>
+          <t>68.57</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>66.77</t>
+          <t>54.28</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-80.37</t>
+          <t>-77.29</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>136354.1510115607</t>
+          <t>136360.4437229437</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>59606.0</t>
+          <t>40454.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>54202.8</t>
+          <t>56729.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>55330.9</t>
+          <t>58477.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>29250.26</t>
+          <t>29829.24</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1128</t>
+          <t>-1748</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>3665.428501645016</t>
+          <t>3541.446915050525</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>4397.04</v>
+        <v>2859.55</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>16.34</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5567,27 +5567,27 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/電子觸控白板.xlsx
+++ b/Result/checksun_type/電子觸控白板.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1299.0</t>
+          <t>607.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-7.09</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>607</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>21.09</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>7.33</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>73.17999999999999</t>
+          <t>72.91999999999999</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>73.49</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>68.47</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>68.55</t>
+          <t>68.58</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-25.43</t>
+          <t>-36.50</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-76.60</t>
+          <t>-78.55</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>136360.4437229437</t>
+          <t>136257.2139769453</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>93810.0</t>
+          <t>43146.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>121939.4</t>
+          <t>126523.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>111374.5</t>
+          <t>110266.6</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>49406.96</t>
+          <t>50056.24</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>10564</t>
+          <t>16256</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>9360.846181135705</t>
+          <t>9583.685898636437</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>19025.36</v>
+        <v>10809.3</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5114.0</t>
+          <t>1299.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>76.10</t>
+          <t>19.33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-7.09</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>607</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>48.37</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>73.62</t>
+          <t>73.17999999999999</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>73.16</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>68.19</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>68.51</t>
+          <t>68.55</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-10.21</t>
+          <t>-25.43</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-75.11</t>
+          <t>-76.60</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>136360.4437229437</t>
+          <t>136257.2139769453</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>404577.0</t>
+          <t>93810.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>112272.8</t>
+          <t>121939.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>106038.9</t>
+          <t>111374.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>47927.76</t>
+          <t>49406.96</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>10564</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>7603.661126890231</t>
+          <t>9360.846181135705</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>24654.83</v>
+        <v>19025.36</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>578.0</t>
+          <t>5114.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-39.66</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>76.10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,67 +1871,67 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>607</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>28.76</t>
+          <t>48.37</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>73.38000000000001</t>
+          <t>73.62</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>72.71</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>68.19</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>68.51</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-12.47</t>
+          <t>-10.21</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-74.47</t>
+          <t>-75.11</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>136360.4437229437</t>
+          <t>136257.2139769453</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>42261.0</t>
+          <t>404577.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>43168.4</t>
+          <t>112272.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>71541.8</t>
+          <t>106038.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>40084.32</t>
+          <t>47927.76</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-28373</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>4503.448780935657</t>
+          <t>7603.661126890231</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-1480.07</v>
+        <v>24654.83</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>578.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-5.23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-23.93</t>
+          <t>-39.66</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,275 +2302,275 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>607</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>28.76</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.92</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
+          <t>73.38000000000001</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>72.71</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>68.4</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>-12.47</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>7.72</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-74.47</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>136257.2139769453</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>42261.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>43168.4</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>71541.8</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>40084.32</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>-28373</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>4503.448780935657</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>-1480.07</v>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>72.9</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>青雲</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>青雲</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>117.8366423644483</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>90.00919392228472</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>22.16097965796244</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>24.14</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>15.4</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>6.00%</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>2.42%</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>2551</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>青雲-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業平上櫃</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
           <t>73.2</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>72.32</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>67.81</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>68.33</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>-13.38</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>7.72</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-73.68</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>136360.4437229437</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>48823.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>54530.4</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>71688.6</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>39731.78</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>-17158</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>5591.361638466338</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>56.79</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>72.9</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>青雲</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>青雲</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>117.8366423644483</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>90.00919392228472</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>22.16097965796244</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>3.66</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>2.79</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>24.14</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>15.36</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>6.00%</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>2.42%</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>48.7</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>2544</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>青雲-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業平上櫃</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>72.5</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>21.70</t>
+          <t>-23.93</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>607</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>13.07</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>72.96</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>71.85</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>67.68</t>
+          <t>67.81</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>68.37</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-13.38</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-72.80</t>
+          <t>-73.68</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>136360.4437229437</t>
+          <t>136257.2139769453</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>20226.0</t>
+          <t>48823.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>94009.8</t>
+          <t>54530.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>77244.4</t>
+          <t>71688.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>38919.48</t>
+          <t>39731.78</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>16765</t>
+          <t>-17158</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>6597.648045869192</t>
+          <t>5591.361638466338</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>1547.2</v>
+        <v>56.79</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>611.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,74 +3048,74 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-1.84</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-2.19</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>21.70</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-08-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
           <t>72.7</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-3.12</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-2.13</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>27.98</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
       <c r="T7" t="inlineStr">
         <is>
           <t>72.3</t>
@@ -3128,12 +3128,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>607</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,62 +3179,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>73.97999999999999</t>
+          <t>72.96</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>71.49</t>
+          <t>71.85</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>67.61</t>
+          <t>67.68</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>68.44</t>
+          <t>68.37</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-71.89</t>
+          <t>-72.80</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,45 +3254,45 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>136360.4437229437</t>
+          <t>136257.2139769453</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>45477.0</t>
+          <t>20226.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>100809.6</t>
+          <t>94009.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>78769.4</t>
+          <t>77244.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>38684.38</t>
+          <t>38919.48</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>22040</t>
+          <t>16765</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>7515.911547269975</t>
+          <t>6597.648045869192</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>6685.07</v>
+        <v>1547.2</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>813.0</t>
+          <t>611.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,102 +3489,102 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>-2.83</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-2.19</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>27.98</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-08-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>72.3</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>69.6</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>-5.58</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>10.63</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>9.09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
           <t>-4.68</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-2.13</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>29.61</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>69.6</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>-4.16</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>10.63</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12.10</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2.88</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>607</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>17.56</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>74.74</t>
+          <t>73.97999999999999</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>71.16</t>
+          <t>71.49</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>67.52</t>
+          <t>67.61</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>68.49</t>
+          <t>68.44</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-71.58</t>
+          <t>-71.89</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>136360.4437229437</t>
+          <t>136257.2139769453</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>59055.0</t>
+          <t>45477.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>99805.0</t>
+          <t>100809.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>77003.9</t>
+          <t>78769.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>38043.2</t>
+          <t>38684.38</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>22801</t>
+          <t>22040</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>7666.974277312432</t>
+          <t>7515.911547269975</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>11080.66</v>
+        <v>6685.07</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1337.0</t>
+          <t>813.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>33.70</t>
+          <t>29.61</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3990,12 +3990,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19.90</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>607</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>52.18</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>75.38</t>
+          <t>74.74</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>70.89</t>
+          <t>71.16</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>67.41</t>
+          <t>67.52</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>68.53</t>
+          <t>68.49</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>12.33</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-71.91</t>
+          <t>-71.58</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>136360.4437229437</t>
+          <t>136257.2139769453</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>99071.0</t>
+          <t>59055.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>99915.2</t>
+          <t>99805.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>74730.4</t>
+          <t>77003.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>37063.94</t>
+          <t>38043.2</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>25184</t>
+          <t>22801</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>7046.303976305286</t>
+          <t>7666.974277312432</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>15509.56</v>
+        <v>11080.66</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3208.0</t>
+          <t>1337.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>32.34</t>
+          <t>33.70</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4421,12 +4421,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>47.74</t>
+          <t>19.90</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-14.81</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>607</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>27.12</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>72.83</t>
+          <t>52.18</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>75.72</t>
+          <t>75.38</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>70.44</t>
+          <t>70.89</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>67.31</t>
+          <t>67.41</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>68.57</t>
+          <t>68.53</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>24.10</t>
+          <t>12.33</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-72.78</t>
+          <t>-71.91</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>136360.4437229437</t>
+          <t>136257.2139769453</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>246220.0</t>
+          <t>99071.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>88846.8</t>
+          <t>99915.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>67134.6</t>
+          <t>74730.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>35428.7</t>
+          <t>37063.94</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>21712</t>
+          <t>25184</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>5507.530535506201</t>
+          <t>7046.303976305286</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>16995.21</v>
+        <v>15509.56</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4650,17 +4650,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>723.0</t>
+          <t>3208.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>47.74</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>-14.81</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>607</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>27.12</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>97.13</t>
+          <t>72.83</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>76.14000000000001</t>
+          <t>75.72</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>70.44</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>67.31</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>68.57</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>24.10</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-74.42</t>
+          <t>-72.78</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>136360.4437229437</t>
+          <t>136257.2139769453</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>54225.0</t>
+          <t>246220.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>60479.0</t>
+          <t>88846.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>57840.5</t>
+          <t>67134.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>30749.9</t>
+          <t>35428.7</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>21712</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>3418.861139151172</t>
+          <t>5507.530535506201</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>2744.64</v>
+        <v>16995.21</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>527.0</t>
+          <t>723.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-9.05</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,17 +5319,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>607</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>91.38</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5339,57 +5339,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.14000000000001</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>69.34</t>
+          <t>70.05</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>67.03</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>68.57</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>54.28</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-77.29</t>
+          <t>-74.42</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>136360.4437229437</t>
+          <t>136257.2139769453</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>40454.0</t>
+          <t>54225.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>56729.2</t>
+          <t>60479.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>58477.6</t>
+          <t>57840.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>29829.24</t>
+          <t>30749.9</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1748</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>3541.446915050525</t>
+          <t>3418.861139151172</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>2859.55</v>
+        <v>2744.64</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/電子觸控白板.xlsx
+++ b/Result/checksun_type/電子觸控白板.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>607.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>39.77</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>10.07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>677</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>21.09</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>7.33</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>72.91999999999999</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>73.49</t>
+          <t>73.44</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>68.47</t>
+          <t>68.61</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>68.58</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-36.50</t>
+          <t>-43.74</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-78.55</t>
+          <t>-80.67</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>136257.2139769453</t>
+          <t>136166.6805755396</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>43146.0</t>
+          <t>48891.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>126523.4</t>
+          <t>126537.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>110266.6</t>
+          <t>90533.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>50056.24</t>
+          <t>50941.56</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>16256</t>
+          <t>36003</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>9583.685898636437</t>
+          <t>8912.15037454644</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>10809.3</v>
+        <v>5218.7</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1299.0</t>
+          <t>607.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-7.09</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>677</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>21.09</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>7.33</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>73.17999999999999</t>
+          <t>72.91999999999999</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>73.49</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>68.47</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>68.55</t>
+          <t>68.58</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-25.43</t>
+          <t>-36.50</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-76.60</t>
+          <t>-78.55</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>136257.2139769453</t>
+          <t>136166.6805755396</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>93810.0</t>
+          <t>43146.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>121939.4</t>
+          <t>126523.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>111374.5</t>
+          <t>110266.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>49406.96</t>
+          <t>50056.24</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>10564</t>
+          <t>16256</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>9360.846181135705</t>
+          <t>9583.685898636437</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>19025.36</v>
+        <v>10809.3</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5114.0</t>
+          <t>1299.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-6.08</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>76.10</t>
+          <t>19.33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-7.09</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>677</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>48.37</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>73.62</t>
+          <t>73.17999999999999</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>73.16</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>68.19</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>68.51</t>
+          <t>68.55</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-10.21</t>
+          <t>-25.43</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-75.11</t>
+          <t>-76.60</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>136257.2139769453</t>
+          <t>136166.6805755396</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>404577.0</t>
+          <t>93810.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>112272.8</t>
+          <t>121939.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>106038.9</t>
+          <t>111374.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>47927.76</t>
+          <t>49406.96</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>10564</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>7603.661126890231</t>
+          <t>9360.846181135705</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>24654.83</v>
+        <v>19025.36</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>578.0</t>
+          <t>5114.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.23</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-39.66</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>76.10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,67 +2302,67 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>677</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>28.76</t>
+          <t>48.37</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>73.38000000000001</t>
+          <t>73.62</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>72.71</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>68.19</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>68.51</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-12.47</t>
+          <t>-10.21</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-74.47</t>
+          <t>-75.11</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>136257.2139769453</t>
+          <t>136166.6805755396</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>42261.0</t>
+          <t>404577.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>43168.4</t>
+          <t>112272.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>71541.8</t>
+          <t>106038.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>40084.32</t>
+          <t>47927.76</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-28373</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>4503.448780935657</t>
+          <t>7603.661126890231</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-1480.07</v>
+        <v>24654.83</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>578.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.67</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-23.93</t>
+          <t>-39.66</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,275 +2733,275 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>677</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>28.76</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.92</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
+          <t>73.38000000000001</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>72.71</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>68.4</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>-12.47</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>7.72</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-74.47</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>136166.6805755396</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>42261.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>43168.4</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>71541.8</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>40084.32</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>-28373</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>4503.448780935657</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>-1480.07</v>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>72.9</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>青雲</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>青雲</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>117.8366423644483</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>90.00919392228472</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>22.16097965796244</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>24.14</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>15.49</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>6.00%</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>2.42%</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>48.69</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>2565</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>青雲-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業平上櫃</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
           <t>73.2</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>72.32</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>67.81</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>68.33</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>-13.38</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>7.72</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-73.68</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>136257.2139769453</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>48823.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>54530.4</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>71688.6</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>39731.78</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>-17158</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>5591.361638466338</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>56.79</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>72.9</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>青雲</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>青雲</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>117.8366423644483</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>90.00919392228472</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>22.16097965796244</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>3.66</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>2.78</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>24.14</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>15.4</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>6.00%</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>2.42%</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>48.2</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>2551</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>青雲-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業平上櫃</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>72.5</t>
-        </is>
-      </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>21.70</t>
+          <t>-23.93</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>677</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>13.07</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>72.96</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>71.85</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>67.68</t>
+          <t>67.81</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>68.37</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-13.38</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-72.80</t>
+          <t>-73.68</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>136257.2139769453</t>
+          <t>136166.6805755396</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>20226.0</t>
+          <t>48823.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>94009.8</t>
+          <t>54530.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>77244.4</t>
+          <t>71688.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>38919.48</t>
+          <t>39731.78</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>16765</t>
+          <t>-17158</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>6597.648045869192</t>
+          <t>5591.361638466338</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>1547.2</v>
+        <v>56.79</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>611.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,72 +3479,72 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-1.27</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-1.25</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>21.70</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-08-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>72.7</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-2.83</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-2.19</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>27.98</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3595,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>677</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,62 +3610,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>73.97999999999999</t>
+          <t>72.96</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>71.49</t>
+          <t>71.85</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>67.61</t>
+          <t>67.68</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>68.44</t>
+          <t>68.37</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-71.89</t>
+          <t>-72.80</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,45 +3685,45 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>136257.2139769453</t>
+          <t>136166.6805755396</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>45477.0</t>
+          <t>20226.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>100809.6</t>
+          <t>94009.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>78769.4</t>
+          <t>77244.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>38684.38</t>
+          <t>38919.48</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>22040</t>
+          <t>16765</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>7515.911547269975</t>
+          <t>6597.648045869192</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>6685.07</v>
+        <v>1547.2</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>813.0</t>
+          <t>611.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>29.61</t>
+          <t>27.98</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3990,12 +3990,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>677</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>17.56</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>74.74</t>
+          <t>73.97999999999999</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>71.16</t>
+          <t>71.49</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>67.52</t>
+          <t>67.61</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>68.49</t>
+          <t>68.44</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-71.58</t>
+          <t>-71.89</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>136257.2139769453</t>
+          <t>136166.6805755396</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>59055.0</t>
+          <t>45477.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>99805.0</t>
+          <t>100809.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>77003.9</t>
+          <t>78769.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>38043.2</t>
+          <t>38684.38</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>22801</t>
+          <t>22040</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>7666.974277312432</t>
+          <t>7515.911547269975</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>11080.66</v>
+        <v>6685.07</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1337.0</t>
+          <t>813.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>33.70</t>
+          <t>29.61</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4421,12 +4421,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19.90</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>677</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>52.18</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>75.38</t>
+          <t>74.74</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>70.89</t>
+          <t>71.16</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>67.41</t>
+          <t>67.52</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>68.53</t>
+          <t>68.49</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>12.33</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-71.91</t>
+          <t>-71.58</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>136257.2139769453</t>
+          <t>136166.6805755396</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>99071.0</t>
+          <t>59055.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>99915.2</t>
+          <t>99805.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>74730.4</t>
+          <t>77003.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>37063.94</t>
+          <t>38043.2</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>25184</t>
+          <t>22801</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>7046.303976305286</t>
+          <t>7666.974277312432</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>15509.56</v>
+        <v>11080.66</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3208.0</t>
+          <t>1337.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>32.34</t>
+          <t>33.70</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>47.74</t>
+          <t>19.90</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-14.81</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>677</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>27.12</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>72.83</t>
+          <t>52.18</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>75.72</t>
+          <t>75.38</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>70.44</t>
+          <t>70.89</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>67.31</t>
+          <t>67.41</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>68.57</t>
+          <t>68.53</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>24.10</t>
+          <t>12.33</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-72.78</t>
+          <t>-71.91</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>136257.2139769453</t>
+          <t>136166.6805755396</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>246220.0</t>
+          <t>99071.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>88846.8</t>
+          <t>99915.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>67134.6</t>
+          <t>74730.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>35428.7</t>
+          <t>37063.94</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>21712</t>
+          <t>25184</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>5507.530535506201</t>
+          <t>7046.303976305286</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>16995.21</v>
+        <v>15509.56</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>723.0</t>
+          <t>3208.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>47.74</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>-14.81</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>677</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>27.12</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>97.13</t>
+          <t>72.83</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>76.14000000000001</t>
+          <t>75.72</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>70.44</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>67.31</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>68.57</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>24.10</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-74.42</t>
+          <t>-72.78</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>136257.2139769453</t>
+          <t>136166.6805755396</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>54225.0</t>
+          <t>246220.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>60479.0</t>
+          <t>88846.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>57840.5</t>
+          <t>67134.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>30749.9</t>
+          <t>35428.7</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>21712</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>3418.861139151172</t>
+          <t>5507.530535506201</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>2744.64</v>
+        <v>16995.21</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/電子觸控白板.xlsx
+++ b/Result/checksun_type/電子觸控白板.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI12"/>
+  <dimension ref="A1:CJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,165 +701,170 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Volume_Price_Change_sum</t>
+          <t>VPC_MACD</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>Volume_Price_Change</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -878,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>677.0</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>-39.08</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>72.34</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>73.44</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>68.61</t>
+          <t>68.81</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>68.64</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-43.74</t>
+          <t>-84.77</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-80.67</t>
+          <t>-86.35</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,198 +1104,203 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>136166.6805755396</t>
+          <t>135905.1413199426</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>48891.0</t>
+          <t>18778.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>126537.0</t>
+          <t>49174.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>90533.7</t>
+          <t>80723.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>50941.56</t>
+          <t>51860.5</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>36003</t>
+          <t>-31549</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>8912.15037454644</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>5218.7</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>5792.96236735511</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-4330.624895495712</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>18778</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>72.9</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-2.47</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>-5.35</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
       <c r="BM2" t="inlineStr">
         <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
           <t>117.8366423644483</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>90.00919392228472</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>22.16097965796244</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>24.14</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>15.49</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
+          <t>15.03</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
           <t>6.00%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>2.42%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>48.69</t>
-        </is>
-      </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>青雲-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>72.1</t>
-        </is>
-      </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>20.21</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 顯示器模組、記憶體、主機板、顯示卡** 平面顯示器 - 顯示器模組** 觸控面板 - 電子觸控白板、工業用設備</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1309,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>607.0</t>
+          <t>604.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>8.99</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>21.09</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>7.33</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>72.91999999999999</t>
+          <t>71.06</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>73.49</t>
+          <t>73.26</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>68.47</t>
+          <t>68.69</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>68.58</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-36.50</t>
+          <t>-67.37</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-78.55</t>
+          <t>-83.45</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,198 +1540,203 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>136166.6805755396</t>
+          <t>135905.1413199426</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>43146.0</t>
+          <t>41249.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>126523.4</t>
+          <t>126334.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>110266.6</t>
+          <t>84751.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>50056.24</t>
+          <t>51658.1</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>16256</t>
+          <t>41583</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>9583.685898636437</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>10809.3</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>7633.614596964351</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>601.6678202628682</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>41249</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>72.9</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>-3.02</t>
-        </is>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
+          <t>-6.72</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
       <c r="BM3" t="inlineStr">
         <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
           <t>117.8366423644483</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>90.00919392228472</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>22.16097965796244</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ3" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>24.14</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>15.49</t>
-        </is>
-      </c>
       <c r="BV3" t="inlineStr">
         <is>
+          <t>15.03</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
           <t>6.00%</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>2.42%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>48.69</t>
-        </is>
-      </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
           <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>青雲-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>70.9</t>
-        </is>
-      </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>20.21</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 顯示器模組、記憶體、主機板、顯示卡** 平面顯示器 - 顯示器模組** 觸控面板 - 電子觸控白板、工業用設備</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1740,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1299.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>39.77</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>10.07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-7.09</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>73.17999999999999</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>73.44</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>68.61</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>68.55</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-25.43</t>
+          <t>-43.74</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-76.60</t>
+          <t>-80.67</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,198 +1976,203 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>136166.6805755396</t>
+          <t>135905.1413199426</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>93810.0</t>
+          <t>48891.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>121939.4</t>
+          <t>126537.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>111374.5</t>
+          <t>90533.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>49406.96</t>
+          <t>50941.56</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>10564</t>
+          <t>36003</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>9360.846181135705</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>19025.36</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>8912.15037454644</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>5218.704992051455</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>48891</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>72.9</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>-3.29</t>
-        </is>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>-2.47</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
       <c r="BM4" t="inlineStr">
         <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
           <t>117.8366423644483</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>90.00919392228472</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>22.16097965796244</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>價跌量增</t>
-        </is>
-      </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>24.14</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>15.49</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
+          <t>15.03</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
           <t>6.00%</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>2.42%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>48.69</t>
-        </is>
-      </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>青雲-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
+          <t>71.1</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>20.21</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 顯示器模組、記憶體、主機板、顯示卡** 平面顯示器 - 顯示器模組** 觸控面板 - 電子觸控白板、工業用設備</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2171,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5114.0</t>
+          <t>607.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>76.10</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>48.37</t>
+          <t>21.09</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>7.33</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>73.62</t>
+          <t>72.91999999999999</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>73.16</t>
+          <t>73.49</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>68.19</t>
+          <t>68.47</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>68.51</t>
+          <t>68.58</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-10.21</t>
+          <t>-36.50</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-75.11</t>
+          <t>-78.55</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,198 +2412,203 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>136166.6805755396</t>
+          <t>135905.1413199426</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>404577.0</t>
+          <t>43146.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>112272.8</t>
+          <t>126523.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>106038.9</t>
+          <t>110266.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>47927.76</t>
+          <t>50056.24</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>16256</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>7603.661126890231</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>24654.83</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>9583.685898636437</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>10809.30434489046</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>43146</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>72.9</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>-3.02</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
       <c r="BM5" t="inlineStr">
         <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
           <t>117.8366423644483</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>90.00919392228472</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>22.16097965796244</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
           <t>24.14</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>15.49</t>
-        </is>
-      </c>
       <c r="BV5" t="inlineStr">
         <is>
+          <t>15.03</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
           <t>6.00%</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>2.42%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>48.69</t>
-        </is>
-      </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>青雲-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>76.8</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>70.7</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>20.21</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 顯示器模組、記憶體、主機板、顯示卡** 平面顯示器 - 顯示器模組** 觸控面板 - 電子觸控白板、工業用設備</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2602,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>578.0</t>
+          <t>1299.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-39.66</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>19.33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>-7.09</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>28.76</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>73.38000000000001</t>
+          <t>73.17999999999999</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>72.71</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>68.55</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-12.47</t>
+          <t>-25.43</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-74.47</t>
+          <t>-76.60</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,198 +2848,203 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>136166.6805755396</t>
+          <t>135905.1413199426</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>42261.0</t>
+          <t>93810.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>43168.4</t>
+          <t>121939.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>71541.8</t>
+          <t>111374.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>40084.32</t>
+          <t>49406.96</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-28373</t>
+          <t>10564</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>4503.448780935657</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>-1480.07</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>9360.846181135705</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>19025.36397948582</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>93810</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
           <t>72.9</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2.06</t>
-        </is>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
+          <t>-3.29</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BL6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
       <c r="BM6" t="inlineStr">
         <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
           <t>117.8366423644483</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>90.00919392228472</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>22.16097965796244</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>24.14</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>15.49</t>
-        </is>
-      </c>
       <c r="BV6" t="inlineStr">
         <is>
+          <t>15.03</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
           <t>6.00%</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>2.42%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>48.69</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>青雲-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>73.2</t>
-        </is>
-      </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
+          <t>70.5</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>20.21</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 顯示器模組、記憶體、主機板、顯示卡** 平面顯示器 - 顯示器模組** 觸控面板 - 電子觸控白板、工業用設備</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3033,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>5114.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-8.7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-23.93</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>76.10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>48.37</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.62</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>72.32</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>67.81</t>
+          <t>68.19</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>68.51</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-13.38</t>
+          <t>-10.21</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-73.68</t>
+          <t>-75.11</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,198 +3284,203 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>136166.6805755396</t>
+          <t>135905.1413199426</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>48823.0</t>
+          <t>404577.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>54530.4</t>
+          <t>112272.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>71688.6</t>
+          <t>106038.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>39731.78</t>
+          <t>47927.76</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-17158</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>5591.361638466338</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>56.79</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>7603.661126890231</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>24654.82902964039</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>404577</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>72.9</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
       <c r="BM7" t="inlineStr">
         <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
           <t>117.8366423644483</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>90.00919392228472</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>22.16097965796244</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>24.14</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>15.49</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
+          <t>15.03</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
           <t>6.00%</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>2.42%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>48.69</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>青雲-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>72.5</t>
-        </is>
-      </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
           <t>20.21</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 顯示器模組、記憶體、主機板、顯示卡** 平面顯示器 - 顯示器模組** 觸控面板 - 電子觸控白板、工業用設備</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3464,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>578.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-7.83</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>21.70</t>
+          <t>-39.66</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>28.76</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.92</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>72.96</t>
+          <t>73.38000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>71.85</t>
+          <t>72.71</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>67.68</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>68.37</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-12.47</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-72.80</t>
+          <t>-74.47</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,198 +3720,203 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>136166.6805755396</t>
+          <t>135905.1413199426</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>20226.0</t>
+          <t>42261.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>94009.8</t>
+          <t>43168.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>77244.4</t>
+          <t>71541.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>38919.48</t>
+          <t>40084.32</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>16765</t>
+          <t>-28373</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>6597.648045869192</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>1547.2</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>4503.448780935657</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-1480.071935483087</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>42261</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
           <t>72.9</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>-1.23</t>
-        </is>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
       <c r="BM8" t="inlineStr">
         <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
           <t>117.8366423644483</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>90.00919392228472</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>22.16097965796244</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
           <t>24.14</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>15.49</t>
-        </is>
-      </c>
       <c r="BV8" t="inlineStr">
         <is>
+          <t>15.03</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
           <t>6.00%</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>2.42%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>48.69</t>
-        </is>
-      </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>青雲-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>73.2</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>73.7</t>
-        </is>
-      </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
+          <t>74.4</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
           <t>20.21</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 顯示器模組、記憶體、主機板、顯示卡** 平面顯示器 - 顯示器模組** 觸控面板 - 電子觸控白板、工業用設備</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3895,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>611.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,72 +3950,72 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-7.25</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-1.99</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-23.93</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-08-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>72.7</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-2.25</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-1.25</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>27.98</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
-      </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -3990,12 +4030,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>13.07</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>73.97999999999999</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>71.49</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>67.61</t>
+          <t>67.81</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>68.44</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-13.38</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-71.89</t>
+          <t>-73.68</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,198 +4156,203 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>136166.6805755396</t>
+          <t>135905.1413199426</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>45477.0</t>
+          <t>48823.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>100809.6</t>
+          <t>54530.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>78769.4</t>
+          <t>71688.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>38684.38</t>
+          <t>39731.78</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>22040</t>
+          <t>-17158</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>7515.911547269975</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>6685.07</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
+          <t>5591.361638466338</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>56.78639775064221</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>48823</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
           <t>72.9</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
       <c r="BM9" t="inlineStr">
         <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
           <t>117.8366423644483</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>90.00919392228472</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>22.16097965796244</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
-        </is>
-      </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
           <t>24.14</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>15.49</t>
-        </is>
-      </c>
       <c r="BV9" t="inlineStr">
         <is>
+          <t>15.03</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
           <t>6.00%</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>2.42%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>48.69</t>
-        </is>
-      </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>青雲-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>75.5</t>
-        </is>
-      </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>20.21</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 顯示器模組、記憶體、主機板、顯示卡** 平面顯示器 - 顯示器模組** 觸控面板 - 電子觸控白板、工業用設備</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4326,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>813.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,22 +4396,22 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>29.61</t>
+          <t>21.70</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -4406,7 +4451,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -4421,12 +4466,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>74.74</t>
+          <t>72.96</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>71.16</t>
+          <t>71.85</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>67.52</t>
+          <t>67.68</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>68.49</t>
+          <t>68.37</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-71.58</t>
+          <t>-72.80</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,198 +4592,203 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>136166.6805755396</t>
+          <t>135905.1413199426</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>59055.0</t>
+          <t>20226.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>99805.0</t>
+          <t>94009.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>77003.9</t>
+          <t>77244.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>38043.2</t>
+          <t>38919.48</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>22801</t>
+          <t>16765</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>7666.974277312432</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>11080.66</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
+          <t>6597.648045869192</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>1547.198788164882</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>20226</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
           <t>72.9</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BL10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
       <c r="BM10" t="inlineStr">
         <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
           <t>117.8366423644483</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>90.00919392228472</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>22.16097965796244</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ10" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>3.65</t>
-        </is>
-      </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
           <t>24.14</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>15.49</t>
-        </is>
-      </c>
       <c r="BV10" t="inlineStr">
         <is>
+          <t>15.03</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
           <t>6.00%</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>2.42%</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>48.69</t>
-        </is>
-      </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
           <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>青雲-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
           <t>20.21</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 顯示器模組、記憶體、主機板、顯示卡** 平面顯示器 - 顯示器模組** 觸控面板 - 電子觸控白板、工業用設備</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4757,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1337.0</t>
+          <t>611.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>33.70</t>
+          <t>27.98</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,12 +4902,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19.90</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,72 +4938,72 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>52.18</t>
+          <t>17.56</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>75.38</t>
+          <t>73.97999999999999</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>70.89</t>
+          <t>71.49</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>67.41</t>
+          <t>67.61</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>68.53</t>
+          <t>68.44</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>12.33</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -4968,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-71.91</t>
+          <t>-71.89</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,172 +5028,172 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>136166.6805755396</t>
+          <t>135905.1413199426</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>99071.0</t>
+          <t>45477.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>99915.2</t>
+          <t>100809.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>74730.4</t>
+          <t>78769.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>37063.94</t>
+          <t>38684.38</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>25184</t>
+          <t>22040</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>7046.303976305286</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>15509.56</v>
-      </c>
-      <c r="BD11" t="inlineStr">
+          <t>7515.911547269975</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>6685.066532036464</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>45477</v>
+      </c>
+      <c r="BE11" t="inlineStr">
         <is>
           <t>2025-11-11</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>72.9</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>0.82</t>
-        </is>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
       <c r="BM11" t="inlineStr">
         <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
           <t>117.8366423644483</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>90.00919392228472</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>22.16097965796244</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ11" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>3.64</t>
-        </is>
-      </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
           <t>24.14</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>15.49</t>
-        </is>
-      </c>
       <c r="BV11" t="inlineStr">
         <is>
+          <t>15.03</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
           <t>6.00%</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>2.42%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>48.69</t>
-        </is>
-      </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>青雲-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>72.8</t>
-        </is>
-      </c>
       <c r="CD11" t="inlineStr">
         <is>
           <t>75.5</t>
@@ -5151,25 +5201,30 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
           <t>20.21</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 顯示器模組、記憶體、主機板、顯示卡** 平面顯示器 - 顯示器模組** 觸控面板 - 電子觸控白板、工業用設備</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5188,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3208.0</t>
+          <t>813.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-6.96</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>32.34</t>
+          <t>29.61</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,12 +5338,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>47.74</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-14.81</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>27.12</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>72.83</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>75.72</t>
+          <t>74.74</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>70.44</t>
+          <t>71.16</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>67.31</t>
+          <t>67.52</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>68.57</t>
+          <t>68.49</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>24.10</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-72.78</t>
+          <t>-71.58</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,198 +5464,203 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>136166.6805755396</t>
+          <t>135905.1413199426</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>246220.0</t>
+          <t>59055.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>88846.8</t>
+          <t>99805.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>67134.6</t>
+          <t>77003.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>35428.7</t>
+          <t>38043.2</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>21712</t>
+          <t>22801</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>5507.530535506201</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>16995.21</v>
-      </c>
-      <c r="BD12" t="inlineStr">
+          <t>7666.974277312432</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>11080.66093285174</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>59055</v>
+      </c>
+      <c r="BE12" t="inlineStr">
         <is>
           <t>2025-11-11</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>72.9</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BL12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
       <c r="BM12" t="inlineStr">
         <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
           <t>117.8366423644483</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>90.00919392228472</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>22.16097965796244</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ12" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
           <t>24.14</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>15.49</t>
-        </is>
-      </c>
       <c r="BV12" t="inlineStr">
         <is>
+          <t>15.03</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
           <t>6.00%</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>2.42%</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>48.69</t>
-        </is>
-      </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
           <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>青雲-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>84.7</t>
-        </is>
-      </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
           <t>20.21</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 顯示器模組、記憶體、主機板、顯示卡** 平面顯示器 - 顯示器模組** 觸控面板 - 電子觸控白板、工業用設備</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/電子觸控白板.xlsx
+++ b/Result/checksun_type/電子觸控白板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>339.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-39.08</t>
+          <t>-55.19</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,72 +1019,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>339</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>34.29</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>16.19</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>73.16</t>
+          <t>73.08</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>68.81</t>
+          <t>68.96</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>68.64</t>
+          <t>68.59</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-84.77</t>
+          <t>-91.88</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-86.35</t>
+          <t>-88.90</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>135905.1413199426</t>
+          <t>135761.9419770774</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>18778.0</t>
+          <t>23968.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>49174.8</t>
+          <t>35206.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>80723.8</t>
+          <t>78572.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>51860.5</t>
+          <t>52193.48</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-31549</t>
+          <t>-43366</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>5792.96236735511</t>
+          <t>3780.858284048273</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-4330.624895495712</t>
+          <t>-7285.714174139335</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>18778</v>
+        <v>23968</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-5.35</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>15.34</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>68.6</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>604.0</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>-39.08</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.99</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1455,72 +1455,72 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>339</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>71.06</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>73.26</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>68.69</t>
+          <t>68.81</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>68.64</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-67.37</t>
+          <t>-84.77</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-83.45</t>
+          <t>-86.35</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>135905.1413199426</t>
+          <t>135761.9419770774</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>41249.0</t>
+          <t>18778.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>126334.6</t>
+          <t>49174.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>84751.5</t>
+          <t>80723.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>51658.1</t>
+          <t>51860.5</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>41583</t>
+          <t>-31549</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>7633.614596964351</t>
+          <t>5792.96236735511</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>601.6678202628682</t>
+          <t>-4330.624895495712</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>41249</v>
+        <v>18778</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-5.35</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>15.34</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1713,17 +1713,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>677.0</t>
+          <t>604.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>8.99</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1891,12 +1891,12 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>339</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1906,37 +1906,37 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>72.34</t>
+          <t>71.06</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>73.44</t>
+          <t>73.26</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>68.61</t>
+          <t>68.69</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-43.74</t>
+          <t>-67.37</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-80.67</t>
+          <t>-83.45</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>135905.1413199426</t>
+          <t>135761.9419770774</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>48891.0</t>
+          <t>41249.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>126537.0</t>
+          <t>126334.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>90533.7</t>
+          <t>84751.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>50941.56</t>
+          <t>51658.1</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>36003</t>
+          <t>41583</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>8912.15037454644</t>
+          <t>7633.614596964351</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>5218.704992051455</t>
+          <t>601.6678202628682</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>48891</v>
+        <v>41249</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>15.34</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>607.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>39.77</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>10.07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2327,72 +2327,72 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>339</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>21.09</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>7.33</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>72.91999999999999</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>73.49</t>
+          <t>73.44</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>68.47</t>
+          <t>68.61</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>68.58</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-36.50</t>
+          <t>-43.74</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-78.55</t>
+          <t>-80.67</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>135905.1413199426</t>
+          <t>135761.9419770774</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>43146.0</t>
+          <t>48891.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>126523.4</t>
+          <t>126537.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>110266.6</t>
+          <t>90533.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>50056.24</t>
+          <t>50941.56</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>16256</t>
+          <t>36003</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>9583.685898636437</t>
+          <t>8912.15037454644</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>10809.30434489046</t>
+          <t>5218.704992051455</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>43146</v>
+        <v>48891</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>15.34</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1299.0</t>
+          <t>607.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-7.09</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2763,72 +2763,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>339</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>21.09</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>7.33</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>73.17999999999999</t>
+          <t>72.91999999999999</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>73.49</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>68.47</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>68.55</t>
+          <t>68.58</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-25.43</t>
+          <t>-36.50</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-76.60</t>
+          <t>-78.55</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>135905.1413199426</t>
+          <t>135761.9419770774</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>93810.0</t>
+          <t>43146.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>121939.4</t>
+          <t>126523.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>111374.5</t>
+          <t>110266.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>49406.96</t>
+          <t>50056.24</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>10564</t>
+          <t>16256</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>9360.846181135705</t>
+          <t>9583.685898636437</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>19025.36397948582</t>
+          <t>10809.30434489046</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>93810</v>
+        <v>43146</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>15.34</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5114.0</t>
+          <t>1299.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-8.7</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>76.10</t>
+          <t>19.33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-7.09</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3199,72 +3199,72 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>339</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>48.37</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>73.62</t>
+          <t>73.17999999999999</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>73.16</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>68.19</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>68.51</t>
+          <t>68.55</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-10.21</t>
+          <t>-25.43</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-75.11</t>
+          <t>-76.60</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>135905.1413199426</t>
+          <t>135761.9419770774</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>404577.0</t>
+          <t>93810.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>112272.8</t>
+          <t>121939.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>106038.9</t>
+          <t>111374.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>47927.76</t>
+          <t>49406.96</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>10564</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>7603.661126890231</t>
+          <t>9360.846181135705</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>24654.82902964039</t>
+          <t>19025.36397948582</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>404577</v>
+        <v>93810</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>15.34</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>578.0</t>
+          <t>5114.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-7.83</t>
+          <t>-6.53</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-39.66</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>76.10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3635,62 +3635,62 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>339</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>28.76</t>
+          <t>48.37</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>73.38000000000001</t>
+          <t>73.62</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>72.71</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>68.19</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>68.51</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-12.47</t>
+          <t>-10.21</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-74.47</t>
+          <t>-75.11</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>135905.1413199426</t>
+          <t>135761.9419770774</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>42261.0</t>
+          <t>404577.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>43168.4</t>
+          <t>112272.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>71541.8</t>
+          <t>106038.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>40084.32</t>
+          <t>47927.76</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-28373</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>4503.448780935657</t>
+          <t>7603.661126890231</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1480.071935483087</t>
+          <t>24654.82902964039</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>42261</v>
+        <v>404577</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>15.34</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>578.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-23.93</t>
+          <t>-39.66</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4071,275 +4071,275 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>339</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>28.76</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.92</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
+          <t>73.38000000000001</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>72.71</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>68.4</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-12.47</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>7.72</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-74.47</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>135761.9419770774</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>42261.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>43168.4</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>71541.8</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>40084.32</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>-28373</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>4503.448780935657</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-1480.071935483087</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>42261</v>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>72.9</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>青雲</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>青雲</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>117.8366423644483</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>90.00919392228472</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>22.16097965796244</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>24.14</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>15.34</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>6.00%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>2.42%</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>48.44</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>2540</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>青雲-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
           <t>73.2</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>72.32</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>67.81</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>68.33</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-13.38</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>7.72</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-73.68</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>135905.1413199426</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>48823.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>54530.4</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>71688.6</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>39731.78</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>-17158</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>5591.361638466338</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>56.78639775064221</t>
-        </is>
-      </c>
-      <c r="BD9" t="n">
-        <v>48823</v>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>72.9</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>青雲</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>青雲</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>117.8366423644483</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>90.00919392228472</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>22.16097965796244</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>3.66</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>24.14</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>15.03</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>6.00%</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>2.42%</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>47.65</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>2490</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>青雲-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>72.5</t>
-        </is>
-      </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>21.70</t>
+          <t>-23.93</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4507,72 +4507,72 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>339</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>13.07</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>72.96</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>71.85</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>67.68</t>
+          <t>67.81</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>68.37</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-13.38</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-72.80</t>
+          <t>-73.68</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>135905.1413199426</t>
+          <t>135761.9419770774</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>20226.0</t>
+          <t>48823.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>94009.8</t>
+          <t>54530.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>77244.4</t>
+          <t>71688.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>38919.48</t>
+          <t>39731.78</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>16765</t>
+          <t>-17158</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>6597.648045869192</t>
+          <t>5591.361638466338</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1547.198788164882</t>
+          <t>56.78639775064221</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>20226</v>
+        <v>48823</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>15.34</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>611.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,72 +4822,72 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-2.27</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-1.85</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>21.70</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-08-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>72.7</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-5.36</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-1.99</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>27.98</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
-      </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>339</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4953,62 +4953,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>73.97999999999999</t>
+          <t>72.96</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>71.49</t>
+          <t>71.85</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>67.61</t>
+          <t>67.68</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>68.44</t>
+          <t>68.37</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-71.89</t>
+          <t>-72.80</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,50 +5028,50 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>135905.1413199426</t>
+          <t>135761.9419770774</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>45477.0</t>
+          <t>20226.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>100809.6</t>
+          <t>94009.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>78769.4</t>
+          <t>77244.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>38684.38</t>
+          <t>38919.48</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>22040</t>
+          <t>16765</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>7515.911547269975</t>
+          <t>6597.648045869192</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>6685.066532036464</t>
+          <t>1547.198788164882</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>45477</v>
+        <v>20226</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>15.34</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>813.0</t>
+          <t>611.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.96</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>29.61</t>
+          <t>27.98</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5379,72 +5379,72 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>339</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>17.56</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>74.74</t>
+          <t>73.97999999999999</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>71.16</t>
+          <t>71.49</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>67.52</t>
+          <t>67.61</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>68.49</t>
+          <t>68.44</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-71.58</t>
+          <t>-71.89</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>135905.1413199426</t>
+          <t>135761.9419770774</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>59055.0</t>
+          <t>45477.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>99805.0</t>
+          <t>100809.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>77003.9</t>
+          <t>78769.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>38043.2</t>
+          <t>38684.38</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>22801</t>
+          <t>22040</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>7666.974277312432</t>
+          <t>7515.911547269975</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>11080.66093285174</t>
+          <t>6685.066532036464</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>59055</v>
+        <v>45477</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>15.34</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/電子觸控白板.xlsx
+++ b/Result/checksun_type/電子觸控白板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>339.0</t>
+          <t>464.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-55.19</t>
+          <t>-58.34</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>464</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>34.29</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>16.19</t>
+          <t>37.62</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>73.08</t>
+          <t>73.05</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>68.96</t>
+          <t>69.14</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>68.59</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-91.88</t>
+          <t>-77.02</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-88.90</t>
+          <t>-90.69</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>135761.9419770774</t>
+          <t>135639.7618025751</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>23968.0</t>
+          <t>33572.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>35206.4</t>
+          <t>33291.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>78572.9</t>
+          <t>79907.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>52193.48</t>
+          <t>52563.6</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-43366</t>
+          <t>-46615</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>3780.858284048273</t>
+          <t>1898.905653450633</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-7285.714174139335</t>
+          <t>-8451.833814836384</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>23968</v>
+        <v>33572</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.34</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2540</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>339.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-39.08</t>
+          <t>-55.19</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>464</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>34.29</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>16.19</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>73.16</t>
+          <t>73.08</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>68.81</t>
+          <t>68.96</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>68.64</t>
+          <t>68.59</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-84.77</t>
+          <t>-91.88</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-86.35</t>
+          <t>-88.90</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>135761.9419770774</t>
+          <t>135639.7618025751</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>18778.0</t>
+          <t>23968.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>49174.8</t>
+          <t>35206.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>80723.8</t>
+          <t>78572.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>51860.5</t>
+          <t>52193.48</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-31549</t>
+          <t>-43366</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>5792.96236735511</t>
+          <t>3780.858284048273</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-4330.624895495712</t>
+          <t>-7285.714174139335</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>18778</v>
+        <v>23968</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-5.35</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.34</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2540</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>68.6</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>604.0</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>-39.08</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.99</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>464</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>71.06</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>73.26</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>68.69</t>
+          <t>68.81</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>68.64</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-67.37</t>
+          <t>-84.77</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-83.45</t>
+          <t>-86.35</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>135761.9419770774</t>
+          <t>135639.7618025751</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>41249.0</t>
+          <t>18778.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>126334.6</t>
+          <t>49174.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>84751.5</t>
+          <t>80723.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>51658.1</t>
+          <t>51860.5</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>41583</t>
+          <t>-31549</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>7633.614596964351</t>
+          <t>5792.96236735511</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>601.6678202628682</t>
+          <t>-4330.624895495712</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>41249</v>
+        <v>18778</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-5.35</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.34</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2540</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2149,17 +2149,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>677.0</t>
+          <t>604.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>8.99</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,17 +2322,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>464</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2342,37 +2342,37 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>72.34</t>
+          <t>71.06</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>73.44</t>
+          <t>73.26</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>68.61</t>
+          <t>68.69</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2382,17 +2382,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-43.74</t>
+          <t>-67.37</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-80.67</t>
+          <t>-83.45</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>135761.9419770774</t>
+          <t>135639.7618025751</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>48891.0</t>
+          <t>41249.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>126537.0</t>
+          <t>126334.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>90533.7</t>
+          <t>84751.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>50941.56</t>
+          <t>51658.1</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>36003</t>
+          <t>41583</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>8912.15037454644</t>
+          <t>7633.614596964351</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>5218.704992051455</t>
+          <t>601.6678202628682</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>48891</v>
+        <v>41249</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.34</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2540</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>607.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>39.77</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>10.07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>464</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>21.09</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>7.33</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>72.91999999999999</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>73.49</t>
+          <t>73.44</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>68.47</t>
+          <t>68.61</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>68.58</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-36.50</t>
+          <t>-43.74</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-78.55</t>
+          <t>-80.67</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>135761.9419770774</t>
+          <t>135639.7618025751</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>43146.0</t>
+          <t>48891.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>126523.4</t>
+          <t>126537.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>110266.6</t>
+          <t>90533.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>50056.24</t>
+          <t>50941.56</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>16256</t>
+          <t>36003</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>9583.685898636437</t>
+          <t>8912.15037454644</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>10809.30434489046</t>
+          <t>5218.704992051455</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>43146</v>
+        <v>48891</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.34</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2540</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1299.0</t>
+          <t>607.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-7.09</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>464</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>21.09</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>7.33</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>73.17999999999999</t>
+          <t>72.91999999999999</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>73.49</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>68.47</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>68.55</t>
+          <t>68.58</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-25.43</t>
+          <t>-36.50</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-76.60</t>
+          <t>-78.55</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>135761.9419770774</t>
+          <t>135639.7618025751</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>93810.0</t>
+          <t>43146.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>121939.4</t>
+          <t>126523.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>111374.5</t>
+          <t>110266.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>49406.96</t>
+          <t>50056.24</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>10564</t>
+          <t>16256</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>9360.846181135705</t>
+          <t>9583.685898636437</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>19025.36397948582</t>
+          <t>10809.30434489046</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>93810</v>
+        <v>43146</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.34</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2540</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5114.0</t>
+          <t>1299.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.53</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>76.10</t>
+          <t>19.33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-7.09</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>464</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>48.37</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>73.62</t>
+          <t>73.17999999999999</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>73.16</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>68.19</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>68.51</t>
+          <t>68.55</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-10.21</t>
+          <t>-25.43</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-75.11</t>
+          <t>-76.60</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>135761.9419770774</t>
+          <t>135639.7618025751</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>404577.0</t>
+          <t>93810.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>112272.8</t>
+          <t>121939.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>106038.9</t>
+          <t>111374.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>47927.76</t>
+          <t>49406.96</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>10564</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>7603.661126890231</t>
+          <t>9360.846181135705</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>24654.82902964039</t>
+          <t>19025.36397948582</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>404577</v>
+        <v>93810</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.34</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2540</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>578.0</t>
+          <t>5114.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-39.66</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>76.10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,67 +4066,67 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>464</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>28.76</t>
+          <t>48.37</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>73.38000000000001</t>
+          <t>73.62</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>72.71</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>68.19</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>68.51</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-12.47</t>
+          <t>-10.21</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-74.47</t>
+          <t>-75.11</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>135761.9419770774</t>
+          <t>135639.7618025751</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>42261.0</t>
+          <t>404577.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>43168.4</t>
+          <t>112272.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>71541.8</t>
+          <t>106038.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>40084.32</t>
+          <t>47927.76</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-28373</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>4503.448780935657</t>
+          <t>7603.661126890231</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1480.071935483087</t>
+          <t>24654.82902964039</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>42261</v>
+        <v>404577</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.34</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2540</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>578.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-23.93</t>
+          <t>-39.66</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,280 +4502,280 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>464</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>28.76</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.92</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
+          <t>73.38000000000001</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>72.71</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>68.4</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-12.47</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>7.72</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-74.47</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>135639.7618025751</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>42261.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>43168.4</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>71541.8</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>40084.32</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>-28373</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>4503.448780935657</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-1480.071935483087</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>42261</v>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>72.9</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>青雲</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>青雲</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>117.8366423644483</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>90.00919392228472</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>22.16097965796244</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>24.14</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>15.8</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>6.00%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>2.42%</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>49.24</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>2616</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>青雲-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
           <t>73.2</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>72.32</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>67.81</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>68.33</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-13.38</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>7.72</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-73.68</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>135761.9419770774</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>48823.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>54530.4</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>71688.6</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>39731.78</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>-17158</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>5591.361638466338</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>56.78639775064221</t>
-        </is>
-      </c>
-      <c r="BD10" t="n">
-        <v>48823</v>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>72.9</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>青雲</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>青雲</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>117.8366423644483</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>90.00919392228472</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>22.16097965796244</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>3.66</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>2.8</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>24.14</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>15.34</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>6.00%</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>2.42%</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>48.44</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>2540</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>青雲-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>72.5</t>
-        </is>
-      </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>21.70</t>
+          <t>-23.93</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>464</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>13.07</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>72.96</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>71.85</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>67.68</t>
+          <t>67.81</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>68.37</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-13.38</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-72.80</t>
+          <t>-73.68</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>135761.9419770774</t>
+          <t>135639.7618025751</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>20226.0</t>
+          <t>48823.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>94009.8</t>
+          <t>54530.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>77244.4</t>
+          <t>71688.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>38919.48</t>
+          <t>39731.78</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>16765</t>
+          <t>-17158</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>6597.648045869192</t>
+          <t>5591.361638466338</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>1547.198788164882</t>
+          <t>56.78639775064221</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>20226</v>
+        <v>48823</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.34</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2540</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>611.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,72 +5258,72 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-3.2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>21.70</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-08-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>72.7</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-3.27</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-1.85</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>27.98</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,12 +5374,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>464</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5389,62 +5389,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>73.97999999999999</t>
+          <t>72.96</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>71.49</t>
+          <t>71.85</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>67.61</t>
+          <t>67.68</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>68.44</t>
+          <t>68.37</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-71.89</t>
+          <t>-72.80</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,50 +5464,50 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>135761.9419770774</t>
+          <t>135639.7618025751</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>45477.0</t>
+          <t>20226.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>100809.6</t>
+          <t>94009.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>78769.4</t>
+          <t>77244.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>38684.38</t>
+          <t>38919.48</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>22040</t>
+          <t>16765</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>7515.911547269975</t>
+          <t>6597.648045869192</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>6685.066532036464</t>
+          <t>1547.198788164882</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>45477</v>
+        <v>20226</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.34</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2540</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/電子觸控白板.xlsx
+++ b/Result/checksun_type/電子觸控白板.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>70.2</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>73.05</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>69.14</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>73.05</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>69.14</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>33572.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>33291.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>33291.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>79907.5</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>52563.6</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>52563.6</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-8451.833814836384</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>33572</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>33572.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>69.84</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>73.08</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>68.96</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>73.08</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>68.95999999999999</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>23968.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>35206.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>35206.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>78572.9</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>52193.48</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>52193.48</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-7285.714174139335</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>23968</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>23968.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>69.86</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>73.16</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>68.81</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>73.16</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>68.81</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>18778.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>49174.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>49174.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>80723.8</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>51860.5</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>51860.5</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-4330.624895495712</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>18778</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>18778.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>71.06</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>73.26</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>68.69</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>73.26000000000001</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>68.69</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>41249.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>126334.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>126334.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>84751.5</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>51658.1</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>51658.1</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>601.6678202628682</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>41249</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>41249.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>72.34</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>73.44</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>68.61</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>73.44</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>68.61</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>48891.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>126537.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>126537</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>90533.7</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>50941.56</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>50941.56</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>5218.704992051455</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>48891</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>48891.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>72.91999999999999</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>73.49</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>68.47</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>73.48999999999999</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>68.47</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>43146.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>126523.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>126523.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>110266.6</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>50056.24</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>50056.24</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>10809.30434489046</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>43146</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>43146.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>73.17999999999999</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>73.4</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>68.33</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>68.33</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>93810.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>121939.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>121939.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>111374.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>49406.96</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>49406.96</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>19025.36397948582</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>93810</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>93810.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>73.62</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>73.16</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>68.19</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>73.16</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>68.19</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>404577.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>112272.8</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>112272.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>106038.9</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>47927.76</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>47927.76</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>24654.82902964039</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>404577</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>404577.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>73.38000000000001</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>72.71</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>72.70999999999999</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>68</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>42261.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>43168.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>43168.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>71541.8</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>40084.32</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>40084.32</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-1480.071935483087</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>42261</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>42261.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>73.2</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>72.32</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>67.81</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>72.31999999999999</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>67.81</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>48823.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>54530.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>54530.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>71688.6</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>39731.78</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>39731.78</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>56.78639775064221</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>48823</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>48823.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>72.96</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>71.85</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>67.68</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>71.84999999999999</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>67.68000000000001</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>20226.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>94009.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>94009.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>77244.4</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>38919.48</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>38919.48</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>1547.198788164882</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>20226</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>20226.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>

--- a/Result/checksun_type/電子觸控白板.xlsx
+++ b/Result/checksun_type/電子觸控白板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>464.0</t>
+          <t>606.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-58.34</t>
+          <t>-59.18</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>606</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>75.71</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>37.62</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.20</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.64</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>73.05</v>
+        <v>72.97</v>
       </c>
       <c r="AN2" t="n">
-        <v>69.14</v>
+        <v>69.34</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>68.62</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-77.02</t>
+          <t>-52.47</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-90.69</t>
+          <t>-91.77</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>135639.7618025751</t>
+          <t>135541.6885714286</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>33572.0</t>
+          <t>44659.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>33291.6</v>
+        <v>32445.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>79907.5</t>
+          <t>79491.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>52563.6</v>
+        <v>53294.76</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-46615</t>
+          <t>-47045</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>1898.905653450633</t>
+          <t>341.3360578500112</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-8451.833814836384</t>
+          <t>-8225.29671795341</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>33572.0</t>
+          <t>44659.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.97</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>339.0</t>
+          <t>464.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-55.19</t>
+          <t>-58.34</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>606</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>34.29</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>16.19</t>
+          <t>37.62</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>73.08</v>
+        <v>73.05</v>
       </c>
       <c r="AN3" t="n">
-        <v>68.95999999999999</v>
+        <v>69.14</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>68.59</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-91.88</t>
+          <t>-77.02</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-88.90</t>
+          <t>-90.69</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>135639.7618025751</t>
+          <t>135541.6885714286</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>23968.0</t>
+          <t>33572.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>35206.4</v>
+        <v>33291.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>78572.9</t>
+          <t>79907.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>52193.48</v>
+        <v>52563.6</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-43366</t>
+          <t>-46615</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>3780.858284048273</t>
+          <t>1898.905653450633</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-7285.714174139335</t>
+          <t>-8451.833814836384</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>23968.0</t>
+          <t>33572.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.97</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>339.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-39.08</t>
+          <t>-55.19</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>606</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>34.29</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>16.19</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>73.16</v>
+        <v>73.08</v>
       </c>
       <c r="AN4" t="n">
-        <v>68.81</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>68.64</t>
+          <t>68.59</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-84.77</t>
+          <t>-91.88</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-86.35</t>
+          <t>-88.90</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>135639.7618025751</t>
+          <t>135541.6885714286</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>18778.0</t>
+          <t>23968.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>49174.8</v>
+        <v>35206.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>80723.8</t>
+          <t>78572.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>51860.5</v>
+        <v>52193.48</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-31549</t>
+          <t>-43366</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>5792.96236735511</t>
+          <t>3780.858284048273</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-4330.624895495712</t>
+          <t>-7285.714174139335</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>18778.0</t>
+          <t>23968.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-5.35</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.97</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>68.6</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>604.0</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>-39.08</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.99</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>606</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>71.06</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>73.26000000000001</v>
+        <v>73.16</v>
       </c>
       <c r="AN5" t="n">
-        <v>68.69</v>
+        <v>68.81</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>68.64</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-67.37</t>
+          <t>-84.77</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-83.45</t>
+          <t>-86.35</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>135639.7618025751</t>
+          <t>135541.6885714286</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>41249.0</t>
+          <t>18778.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>126334.6</v>
+        <v>49174.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>84751.5</t>
+          <t>80723.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>51658.1</v>
+        <v>51860.5</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>41583</t>
+          <t>-31549</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>7633.614596964351</t>
+          <t>5792.96236735511</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>601.6678202628682</t>
+          <t>-4330.624895495712</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>41249.0</t>
+          <t>18778.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-5.35</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.97</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2561,17 +2561,17 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>677.0</t>
+          <t>604.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>7.23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>8.99</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,17 +2734,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>606</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2754,34 +2754,34 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>72.34</t>
+          <t>71.06</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>73.44</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="AN6" t="n">
-        <v>68.61</v>
+        <v>68.69</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2790,17 +2790,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-43.74</t>
+          <t>-67.37</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-80.67</t>
+          <t>-83.45</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>135639.7618025751</t>
+          <t>135541.6885714286</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>48891.0</t>
+          <t>41249.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>126537</v>
+        <v>126334.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>90533.7</t>
+          <t>84751.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>50941.56</v>
+        <v>51658.1</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>36003</t>
+          <t>41583</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>8912.15037454644</t>
+          <t>7633.614596964351</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>5218.704992051455</t>
+          <t>601.6678202628682</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>48891.0</t>
+          <t>41249.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.97</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>607.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>39.77</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>10.07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>606</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>21.09</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>7.33</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>72.91999999999999</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>73.48999999999999</v>
+        <v>73.44</v>
       </c>
       <c r="AN7" t="n">
-        <v>68.47</v>
+        <v>68.61</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>68.58</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-36.50</t>
+          <t>-43.74</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-78.55</t>
+          <t>-80.67</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>135639.7618025751</t>
+          <t>135541.6885714286</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>43146.0</t>
+          <t>48891.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>126523.4</v>
+        <v>126537</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>110266.6</t>
+          <t>90533.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>50056.24</v>
+        <v>50941.56</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>16256</t>
+          <t>36003</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>9583.685898636437</t>
+          <t>8912.15037454644</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>10809.30434489046</t>
+          <t>5218.704992051455</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>43146.0</t>
+          <t>48891.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.97</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1299.0</t>
+          <t>607.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-7.09</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>606</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>21.09</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>7.33</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>73.17999999999999</t>
+          <t>72.91999999999999</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="AN8" t="n">
-        <v>68.33</v>
+        <v>68.47</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>68.55</t>
+          <t>68.58</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-25.43</t>
+          <t>-36.50</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-76.60</t>
+          <t>-78.55</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>135639.7618025751</t>
+          <t>135541.6885714286</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>93810.0</t>
+          <t>43146.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>121939.4</v>
+        <v>126523.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>111374.5</t>
+          <t>110266.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>49406.96</v>
+        <v>50056.24</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>10564</t>
+          <t>16256</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>9360.846181135705</t>
+          <t>9583.685898636437</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>19025.36397948582</t>
+          <t>10809.30434489046</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>93810.0</t>
+          <t>43146.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.97</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5114.0</t>
+          <t>1299.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>76.10</t>
+          <t>19.33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-7.09</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>606</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>48.37</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>73.62</t>
+          <t>73.17999999999999</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>73.16</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="AN9" t="n">
-        <v>68.19</v>
+        <v>68.33</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>68.51</t>
+          <t>68.55</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-10.21</t>
+          <t>-25.43</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-75.11</t>
+          <t>-76.60</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>135639.7618025751</t>
+          <t>135541.6885714286</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>404577.0</t>
+          <t>93810.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>112272.8</v>
+        <v>121939.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>106038.9</t>
+          <t>111374.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>47927.76</v>
+        <v>49406.96</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>10564</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>7603.661126890231</t>
+          <t>9360.846181135705</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>24654.82902964039</t>
+          <t>19025.36397948582</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>404577.0</t>
+          <t>93810.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.97</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>578.0</t>
+          <t>5114.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-39.66</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>76.10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,63 +4454,63 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>606</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>28.76</t>
+          <t>48.37</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>73.38000000000001</t>
+          <t>73.62</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>72.70999999999999</v>
+        <v>73.16</v>
       </c>
       <c r="AN10" t="n">
-        <v>68</v>
+        <v>68.19</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>68.51</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-12.47</t>
+          <t>-10.21</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-74.47</t>
+          <t>-75.11</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>135639.7618025751</t>
+          <t>135541.6885714286</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>42261.0</t>
+          <t>404577.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>43168.4</v>
+        <v>112272.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>71541.8</t>
+          <t>106038.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>40084.32</v>
+        <v>47927.76</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-28373</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>4503.448780935657</t>
+          <t>7603.661126890231</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1480.071935483087</t>
+          <t>24654.82902964039</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>42261.0</t>
+          <t>404577.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.97</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>578.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-23.93</t>
+          <t>-39.66</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,274 +4884,274 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>606</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>28.76</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.92</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
+          <t>73.38000000000001</t>
+        </is>
+      </c>
+      <c r="AM11" t="n">
+        <v>72.70999999999999</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>68</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>68.4</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-12.47</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>7.72</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-74.47</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>135541.6885714286</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>42261.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="n">
+        <v>43168.4</v>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>71541.8</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>40084.32</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>-28373</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>4503.448780935657</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-1480.071935483087</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>42261.0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>72.9</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>青雲</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>青雲</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>117.8366423644483</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>90.00919392228472</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>22.16097965796244</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>24.14</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>15.97</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>6.00%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>2.42%</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>49.59</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>2645</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>青雲-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
           <t>73.2</t>
         </is>
       </c>
-      <c r="AM11" t="n">
-        <v>72.31999999999999</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>67.81</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>68.33</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>-13.38</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>7.72</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-73.68</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>135639.7618025751</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>48823.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="n">
-        <v>54530.4</v>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>71688.6</t>
-        </is>
-      </c>
-      <c r="AZ11" t="n">
-        <v>39731.78</v>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>-17158</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>5591.361638466338</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>56.78639775064221</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>48823.0</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>72.9</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>青雲</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>青雲</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>117.8366423644483</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>90.00919392228472</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>22.16097965796244</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>3.66</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>2.72</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>24.14</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>15.8</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>6.00%</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>2.42%</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>49.24</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>2616</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>青雲-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>72.5</t>
-        </is>
-      </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>21.70</t>
+          <t>-23.93</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>606</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>13.07</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>72.96</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>71.84999999999999</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="AN12" t="n">
-        <v>67.68000000000001</v>
+        <v>67.81</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>68.37</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-13.38</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-72.80</t>
+          <t>-73.68</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>135639.7618025751</t>
+          <t>135541.6885714286</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>20226.0</t>
+          <t>48823.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>94009.8</v>
+        <v>54530.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>77244.4</t>
+          <t>71688.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>38919.48</v>
+        <v>39731.78</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>16765</t>
+          <t>-17158</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>6597.648045869192</t>
+          <t>5591.361638466338</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>1547.198788164882</t>
+          <t>56.78639775064221</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>20226.0</t>
+          <t>48823.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.97</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/電子觸控白板.xlsx
+++ b/Result/checksun_type/電子觸控白板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>606.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-59.18</t>
+          <t>-64.13</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>75.71</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>79.37</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>70.64</t>
+          <t>71.67999999999999</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>72.97</v>
+        <v>72.88</v>
       </c>
       <c r="AN2" t="n">
-        <v>69.34</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>68.62</t>
+          <t>68.65</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-52.47</t>
+          <t>-32.33</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-91.77</t>
+          <t>-92.39</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>135541.6885714286</t>
+          <t>135384.862339515</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>44659.0</t>
+          <t>17071.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>32445.2</v>
+        <v>27609.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>79491.1</t>
+          <t>76972.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>53294.76</v>
+        <v>52850.06</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-47045</t>
+          <t>-49362</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>341.3360578500112</t>
+          <t>-1238.898463694067</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-8225.29671795341</t>
+          <t>-9930.188332186495</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>44659.0</t>
+          <t>17071.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.97</t>
+          <t>15.95</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>464.0</t>
+          <t>606.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-58.34</t>
+          <t>-59.18</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>75.71</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>37.62</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.20</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.64</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>73.05</v>
+        <v>72.97</v>
       </c>
       <c r="AN3" t="n">
-        <v>69.14</v>
+        <v>69.34</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>68.62</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-77.02</t>
+          <t>-52.47</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-90.69</t>
+          <t>-91.77</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>135541.6885714286</t>
+          <t>135384.862339515</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>33572.0</t>
+          <t>44659.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>33291.6</v>
+        <v>32445.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>79907.5</t>
+          <t>79491.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>52563.6</v>
+        <v>53294.76</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-46615</t>
+          <t>-47045</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>1898.905653450633</t>
+          <t>341.3360578500112</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-8451.833814836384</t>
+          <t>-8225.29671795341</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>33572.0</t>
+          <t>44659.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.97</t>
+          <t>15.95</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>339.0</t>
+          <t>464.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-55.19</t>
+          <t>-58.34</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>34.29</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>16.19</t>
+          <t>37.62</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>73.08</v>
+        <v>73.05</v>
       </c>
       <c r="AN4" t="n">
-        <v>68.95999999999999</v>
+        <v>69.14</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>68.59</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-91.88</t>
+          <t>-77.02</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-88.90</t>
+          <t>-90.69</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>135541.6885714286</t>
+          <t>135384.862339515</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>23968.0</t>
+          <t>33572.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>35206.4</v>
+        <v>33291.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>78572.9</t>
+          <t>79907.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>52193.48</v>
+        <v>52563.6</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-43366</t>
+          <t>-46615</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>3780.858284048273</t>
+          <t>1898.905653450633</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-7285.714174139335</t>
+          <t>-8451.833814836384</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>23968.0</t>
+          <t>33572.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.97</t>
+          <t>15.95</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>339.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-39.08</t>
+          <t>-55.19</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>34.29</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>16.19</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>73.16</v>
+        <v>73.08</v>
       </c>
       <c r="AN5" t="n">
-        <v>68.81</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>68.64</t>
+          <t>68.59</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-84.77</t>
+          <t>-91.88</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-86.35</t>
+          <t>-88.90</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>135541.6885714286</t>
+          <t>135384.862339515</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>18778.0</t>
+          <t>23968.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>49174.8</v>
+        <v>35206.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>80723.8</t>
+          <t>78572.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>51860.5</v>
+        <v>52193.48</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-31549</t>
+          <t>-43366</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>5792.96236735511</t>
+          <t>3780.858284048273</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-4330.624895495712</t>
+          <t>-7285.714174139335</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>18778.0</t>
+          <t>23968.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-5.35</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.97</t>
+          <t>15.95</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>68.6</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>604.0</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>-39.08</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.99</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>71.06</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>73.26000000000001</v>
+        <v>73.16</v>
       </c>
       <c r="AN6" t="n">
-        <v>68.69</v>
+        <v>68.81</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>68.64</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-67.37</t>
+          <t>-84.77</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-83.45</t>
+          <t>-86.35</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>135541.6885714286</t>
+          <t>135384.862339515</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>41249.0</t>
+          <t>18778.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>126334.6</v>
+        <v>49174.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>84751.5</t>
+          <t>80723.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>51658.1</v>
+        <v>51860.5</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>41583</t>
+          <t>-31549</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>7633.614596964351</t>
+          <t>5792.96236735511</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>601.6678202628682</t>
+          <t>-4330.624895495712</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>41249.0</t>
+          <t>18778.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-5.35</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.97</t>
+          <t>15.95</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2991,17 +2991,17 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>677.0</t>
+          <t>604.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>8.99</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,17 +3164,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,34 +3184,34 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>72.34</t>
+          <t>71.06</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>73.44</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="AN7" t="n">
-        <v>68.61</v>
+        <v>68.69</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3220,17 +3220,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-43.74</t>
+          <t>-67.37</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-80.67</t>
+          <t>-83.45</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>135541.6885714286</t>
+          <t>135384.862339515</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>48891.0</t>
+          <t>41249.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>126537</v>
+        <v>126334.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>90533.7</t>
+          <t>84751.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>50941.56</v>
+        <v>51658.1</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>36003</t>
+          <t>41583</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>8912.15037454644</t>
+          <t>7633.614596964351</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>5218.704992051455</t>
+          <t>601.6678202628682</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>48891.0</t>
+          <t>41249.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.97</t>
+          <t>15.95</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>607.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>39.77</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>10.07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>21.09</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>7.33</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>72.91999999999999</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>73.48999999999999</v>
+        <v>73.44</v>
       </c>
       <c r="AN8" t="n">
-        <v>68.47</v>
+        <v>68.61</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>68.58</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-36.50</t>
+          <t>-43.74</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-78.55</t>
+          <t>-80.67</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>135541.6885714286</t>
+          <t>135384.862339515</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>43146.0</t>
+          <t>48891.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>126523.4</v>
+        <v>126537</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>110266.6</t>
+          <t>90533.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>50056.24</v>
+        <v>50941.56</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>16256</t>
+          <t>36003</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>9583.685898636437</t>
+          <t>8912.15037454644</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>10809.30434489046</t>
+          <t>5218.704992051455</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>43146.0</t>
+          <t>48891.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.97</t>
+          <t>15.95</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1299.0</t>
+          <t>607.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-7.09</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>21.09</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>7.33</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>73.17999999999999</t>
+          <t>72.91999999999999</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>73.40000000000001</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="AN9" t="n">
-        <v>68.33</v>
+        <v>68.47</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>68.55</t>
+          <t>68.58</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-25.43</t>
+          <t>-36.50</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-76.60</t>
+          <t>-78.55</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>135541.6885714286</t>
+          <t>135384.862339515</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>93810.0</t>
+          <t>43146.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>121939.4</v>
+        <v>126523.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>111374.5</t>
+          <t>110266.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>49406.96</v>
+        <v>50056.24</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>10564</t>
+          <t>16256</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>9360.846181135705</t>
+          <t>9583.685898636437</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>19025.36397948582</t>
+          <t>10809.30434489046</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>93810.0</t>
+          <t>43146.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.97</t>
+          <t>15.95</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5114.0</t>
+          <t>1299.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>76.10</t>
+          <t>19.33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-7.09</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>48.37</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>73.62</t>
+          <t>73.17999999999999</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>73.16</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="AN10" t="n">
-        <v>68.19</v>
+        <v>68.33</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>68.51</t>
+          <t>68.55</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-10.21</t>
+          <t>-25.43</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-75.11</t>
+          <t>-76.60</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>135541.6885714286</t>
+          <t>135384.862339515</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>404577.0</t>
+          <t>93810.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>112272.8</v>
+        <v>121939.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>106038.9</t>
+          <t>111374.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>47927.76</v>
+        <v>49406.96</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>10564</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>7603.661126890231</t>
+          <t>9360.846181135705</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>24654.82902964039</t>
+          <t>19025.36397948582</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>404577.0</t>
+          <t>93810.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,17 +4641,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.97</t>
+          <t>15.95</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>578.0</t>
+          <t>5114.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-39.66</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>76.10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,63 +4884,63 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>28.76</t>
+          <t>48.37</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>73.38000000000001</t>
+          <t>73.62</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>72.70999999999999</v>
+        <v>73.16</v>
       </c>
       <c r="AN11" t="n">
-        <v>68</v>
+        <v>68.19</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>68.51</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-12.47</t>
+          <t>-10.21</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-74.47</t>
+          <t>-75.11</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>135541.6885714286</t>
+          <t>135384.862339515</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>42261.0</t>
+          <t>404577.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>43168.4</v>
+        <v>112272.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>71541.8</t>
+          <t>106038.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>40084.32</v>
+        <v>47927.76</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-28373</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>4503.448780935657</t>
+          <t>7603.661126890231</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1480.071935483087</t>
+          <t>24654.82902964039</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>42261.0</t>
+          <t>404577.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.97</t>
+          <t>15.95</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>578.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-23.93</t>
+          <t>-39.66</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,274 +5314,274 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>28.76</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.92</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
+          <t>73.38000000000001</t>
+        </is>
+      </c>
+      <c r="AM12" t="n">
+        <v>72.70999999999999</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>68</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>68.4</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>-12.47</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>7.72</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-74.47</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>135384.862339515</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>42261.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="n">
+        <v>43168.4</v>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>71541.8</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>40084.32</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>-28373</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>4503.448780935657</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-1480.071935483087</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>42261.0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>72.9</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>青雲</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>青雲</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>117.8366423644483</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>90.00919392228472</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>22.16097965796244</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>24.14</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>15.95</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>6.00%</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>2.42%</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>2641</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>青雲-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
           <t>73.2</t>
         </is>
       </c>
-      <c r="AM12" t="n">
-        <v>72.31999999999999</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>67.81</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>68.33</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>-13.38</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>7.72</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-73.68</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>135541.6885714286</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>48823.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="n">
-        <v>54530.4</v>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>71688.6</t>
-        </is>
-      </c>
-      <c r="AZ12" t="n">
-        <v>39731.78</v>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>-17158</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>5591.361638466338</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>56.78639775064221</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>48823.0</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>72.9</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>青雲</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>青雲</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>117.8366423644483</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>90.00919392228472</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>22.16097965796244</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>3.66</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>2.69</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>24.14</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>15.97</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>6.00%</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>2.42%</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>49.59</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>2645</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>青雲-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>72.5</t>
-        </is>
-      </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/電子觸控白板.xlsx
+++ b/Result/checksun_type/電子觸控白板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>284.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-64.13</t>
+          <t>-27.46</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,68 +1019,68 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>284</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>92.45</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>79.37</t>
+          <t>88.76</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>71.67999999999999</t>
+          <t>72.46000000000001</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>72.88</v>
+        <v>72.67</v>
       </c>
       <c r="AN2" t="n">
-        <v>69.48999999999999</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>68.65</t>
+          <t>68.66</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-32.33</t>
+          <t>-20.53</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-92.39</t>
+          <t>-92.76</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>135384.862339515</t>
+          <t>135236.1303418803</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>17071.0</t>
+          <t>20650.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>27609.6</v>
+        <v>27984</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>76972.1</t>
+          <t>38579.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>52850.06</v>
+        <v>53075.12</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-49362</t>
+          <t>-10595</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1238.898463694067</t>
+          <t>-2680.134508332671</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-9930.188332186495</t>
+          <t>-10606.93275384499</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>17071.0</t>
+          <t>20650.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.95</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>606.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-59.18</t>
+          <t>-64.13</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,68 +1449,68 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>284</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>75.71</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>79.37</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>70.64</t>
+          <t>71.67999999999999</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>72.97</v>
+        <v>72.88</v>
       </c>
       <c r="AN3" t="n">
-        <v>69.34</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>68.62</t>
+          <t>68.65</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-52.47</t>
+          <t>-32.33</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-91.77</t>
+          <t>-92.39</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>135384.862339515</t>
+          <t>135236.1303418803</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>44659.0</t>
+          <t>17071.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>32445.2</v>
+        <v>27609.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>79491.1</t>
+          <t>76972.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>53294.76</v>
+        <v>52850.06</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-47045</t>
+          <t>-49362</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>341.3360578500112</t>
+          <t>-1238.898463694067</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-8225.29671795341</t>
+          <t>-9930.188332186495</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>44659.0</t>
+          <t>17071.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.95</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>464.0</t>
+          <t>606.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-58.34</t>
+          <t>-59.18</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,68 +1879,68 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>284</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>75.71</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>37.62</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.20</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.64</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>73.05</v>
+        <v>72.97</v>
       </c>
       <c r="AN4" t="n">
-        <v>69.14</v>
+        <v>69.34</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>68.62</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-77.02</t>
+          <t>-52.47</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-90.69</t>
+          <t>-91.77</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>135384.862339515</t>
+          <t>135236.1303418803</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>33572.0</t>
+          <t>44659.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>33291.6</v>
+        <v>32445.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>79907.5</t>
+          <t>79491.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>52563.6</v>
+        <v>53294.76</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-46615</t>
+          <t>-47045</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>1898.905653450633</t>
+          <t>341.3360578500112</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-8451.833814836384</t>
+          <t>-8225.29671795341</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>33572.0</t>
+          <t>44659.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.95</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>339.0</t>
+          <t>464.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-55.19</t>
+          <t>-58.34</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,68 +2309,68 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>284</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>34.29</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>16.19</t>
+          <t>37.62</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>73.08</v>
+        <v>73.05</v>
       </c>
       <c r="AN5" t="n">
-        <v>68.95999999999999</v>
+        <v>69.14</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>68.59</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-91.88</t>
+          <t>-77.02</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-88.90</t>
+          <t>-90.69</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>135384.862339515</t>
+          <t>135236.1303418803</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>23968.0</t>
+          <t>33572.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>35206.4</v>
+        <v>33291.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>78572.9</t>
+          <t>79907.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>52193.48</v>
+        <v>52563.6</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-43366</t>
+          <t>-46615</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>3780.858284048273</t>
+          <t>1898.905653450633</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-7285.714174139335</t>
+          <t>-8451.833814836384</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>23968.0</t>
+          <t>33572.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.95</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>339.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-39.08</t>
+          <t>-55.19</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,68 +2739,68 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>284</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>34.29</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>16.19</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>73.16</v>
+        <v>73.08</v>
       </c>
       <c r="AN6" t="n">
-        <v>68.81</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>68.64</t>
+          <t>68.59</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-84.77</t>
+          <t>-91.88</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-86.35</t>
+          <t>-88.90</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>135384.862339515</t>
+          <t>135236.1303418803</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>18778.0</t>
+          <t>23968.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>49174.8</v>
+        <v>35206.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>80723.8</t>
+          <t>78572.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>51860.5</v>
+        <v>52193.48</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-31549</t>
+          <t>-43366</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>5792.96236735511</t>
+          <t>3780.858284048273</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-4330.624895495712</t>
+          <t>-7285.714174139335</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>18778.0</t>
+          <t>23968.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-5.35</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.95</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>68.6</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>604.0</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>-39.08</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.99</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,68 +3169,68 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>284</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>71.06</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>73.26000000000001</v>
+        <v>73.16</v>
       </c>
       <c r="AN7" t="n">
-        <v>68.69</v>
+        <v>68.81</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>68.64</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-67.37</t>
+          <t>-84.77</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-83.45</t>
+          <t>-86.35</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>135384.862339515</t>
+          <t>135236.1303418803</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>41249.0</t>
+          <t>18778.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>126334.6</v>
+        <v>49174.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>84751.5</t>
+          <t>80723.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>51658.1</v>
+        <v>51860.5</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>41583</t>
+          <t>-31549</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>7633.614596964351</t>
+          <t>5792.96236735511</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>601.6678202628682</t>
+          <t>-4330.624895495712</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>41249.0</t>
+          <t>18778.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-5.35</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.95</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3421,17 +3421,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>677.0</t>
+          <t>604.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>8.99</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,12 +3599,12 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>284</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3614,34 +3614,34 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>72.34</t>
+          <t>71.06</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>73.44</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="AN8" t="n">
-        <v>68.61</v>
+        <v>68.69</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3650,17 +3650,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-43.74</t>
+          <t>-67.37</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-80.67</t>
+          <t>-83.45</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>135384.862339515</t>
+          <t>135236.1303418803</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>48891.0</t>
+          <t>41249.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>126537</v>
+        <v>126334.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>90533.7</t>
+          <t>84751.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>50941.56</v>
+        <v>51658.1</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>36003</t>
+          <t>41583</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>8912.15037454644</t>
+          <t>7633.614596964351</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>5218.704992051455</t>
+          <t>601.6678202628682</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>48891.0</t>
+          <t>41249.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.95</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>607.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>39.77</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>10.07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,68 +4029,68 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>284</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>21.09</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>7.33</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>72.91999999999999</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>73.48999999999999</v>
+        <v>73.44</v>
       </c>
       <c r="AN9" t="n">
-        <v>68.47</v>
+        <v>68.61</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>68.58</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-36.50</t>
+          <t>-43.74</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-78.55</t>
+          <t>-80.67</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>135384.862339515</t>
+          <t>135236.1303418803</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>43146.0</t>
+          <t>48891.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>126523.4</v>
+        <v>126537</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>110266.6</t>
+          <t>90533.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>50056.24</v>
+        <v>50941.56</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>16256</t>
+          <t>36003</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>9583.685898636437</t>
+          <t>8912.15037454644</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>10809.30434489046</t>
+          <t>5218.704992051455</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>43146.0</t>
+          <t>48891.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.95</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1299.0</t>
+          <t>607.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-7.09</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,68 +4459,68 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>284</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>21.09</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>7.33</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>73.17999999999999</t>
+          <t>72.91999999999999</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>73.40000000000001</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="AN10" t="n">
-        <v>68.33</v>
+        <v>68.47</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>68.55</t>
+          <t>68.58</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-25.43</t>
+          <t>-36.50</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-76.60</t>
+          <t>-78.55</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>135384.862339515</t>
+          <t>135236.1303418803</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>93810.0</t>
+          <t>43146.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>121939.4</v>
+        <v>126523.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>111374.5</t>
+          <t>110266.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>49406.96</v>
+        <v>50056.24</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>10564</t>
+          <t>16256</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>9360.846181135705</t>
+          <t>9583.685898636437</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>19025.36397948582</t>
+          <t>10809.30434489046</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>93810.0</t>
+          <t>43146.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.95</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5114.0</t>
+          <t>1299.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>76.10</t>
+          <t>19.33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-7.09</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,68 +4889,68 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>284</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>48.37</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>73.62</t>
+          <t>73.17999999999999</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>73.16</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="AN11" t="n">
-        <v>68.19</v>
+        <v>68.33</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>68.51</t>
+          <t>68.55</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-10.21</t>
+          <t>-25.43</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-75.11</t>
+          <t>-76.60</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>135384.862339515</t>
+          <t>135236.1303418803</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>404577.0</t>
+          <t>93810.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>112272.8</v>
+        <v>121939.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>106038.9</t>
+          <t>111374.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>47927.76</v>
+        <v>49406.96</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>10564</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>7603.661126890231</t>
+          <t>9360.846181135705</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>24654.82902964039</t>
+          <t>19025.36397948582</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>404577.0</t>
+          <t>93810.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.95</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>578.0</t>
+          <t>5114.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-39.66</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>76.10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,58 +5319,58 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>284</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>28.76</t>
+          <t>48.37</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>73.38000000000001</t>
+          <t>73.62</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>72.70999999999999</v>
+        <v>73.16</v>
       </c>
       <c r="AN12" t="n">
-        <v>68</v>
+        <v>68.19</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>68.51</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-12.47</t>
+          <t>-10.21</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-74.47</t>
+          <t>-75.11</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>135384.862339515</t>
+          <t>135236.1303418803</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>42261.0</t>
+          <t>404577.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>43168.4</v>
+        <v>112272.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>71541.8</t>
+          <t>106038.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>40084.32</v>
+        <v>47927.76</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-28373</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>4503.448780935657</t>
+          <t>7603.661126890231</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1480.071935483087</t>
+          <t>24654.82902964039</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>42261.0</t>
+          <t>404577.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.95</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/電子觸控白板.xlsx
+++ b/Result/checksun_type/電子觸控白板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>284.0</t>
+          <t>295.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-27.46</t>
+          <t>-12.43</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>295</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>92.45</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>88.76</t>
+          <t>82.39</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>72.46000000000001</t>
+          <t>72.58000000000001</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>72.67</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AN2" t="n">
-        <v>69.65000000000001</v>
+        <v>69.77</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>68.66</t>
+          <t>68.67</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-20.53</t>
+          <t>-36.70</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-92.76</t>
+          <t>-93.37</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>135236.1303418803</t>
+          <t>135088.9160739687</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>20650.0</t>
+          <t>21163.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>27984</v>
+        <v>27423</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>38579.4</t>
+          <t>31314.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>53075.12</v>
+        <v>53359.16</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-10595</t>
+          <t>-3891</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2680.134508332671</t>
+          <t>-3925.806973229156</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-10606.93275384499</t>
+          <t>-10777.00553015982</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>20650.0</t>
+          <t>21163.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>15.47</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2562</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>284.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-64.13</t>
+          <t>-27.46</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>295</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>92.45</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>79.37</t>
+          <t>88.76</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>71.67999999999999</t>
+          <t>72.46000000000001</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>72.88</v>
+        <v>72.67</v>
       </c>
       <c r="AN3" t="n">
-        <v>69.48999999999999</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>68.65</t>
+          <t>68.66</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-32.33</t>
+          <t>-20.53</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-92.39</t>
+          <t>-92.76</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>135236.1303418803</t>
+          <t>135088.9160739687</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>17071.0</t>
+          <t>20650.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>27609.6</v>
+        <v>27984</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>76972.1</t>
+          <t>38579.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>52850.06</v>
+        <v>53075.12</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-49362</t>
+          <t>-10595</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1238.898463694067</t>
+          <t>-2680.134508332671</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-9930.188332186495</t>
+          <t>-10606.93275384499</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>17071.0</t>
+          <t>20650.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>15.47</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2562</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>606.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-59.18</t>
+          <t>-64.13</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>295</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>75.71</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>79.37</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>70.64</t>
+          <t>71.67999999999999</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>72.97</v>
+        <v>72.88</v>
       </c>
       <c r="AN4" t="n">
-        <v>69.34</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>68.62</t>
+          <t>68.65</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-52.47</t>
+          <t>-32.33</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-91.77</t>
+          <t>-92.39</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>135236.1303418803</t>
+          <t>135088.9160739687</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>44659.0</t>
+          <t>17071.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>32445.2</v>
+        <v>27609.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>79491.1</t>
+          <t>76972.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>53294.76</v>
+        <v>52850.06</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-47045</t>
+          <t>-49362</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>341.3360578500112</t>
+          <t>-1238.898463694067</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-8225.29671795341</t>
+          <t>-9930.188332186495</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>44659.0</t>
+          <t>17071.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>15.47</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2562</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>464.0</t>
+          <t>606.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-58.34</t>
+          <t>-59.18</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>295</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>75.71</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>37.62</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.20</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.64</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>73.05</v>
+        <v>72.97</v>
       </c>
       <c r="AN5" t="n">
-        <v>69.14</v>
+        <v>69.34</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>68.62</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-77.02</t>
+          <t>-52.47</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-90.69</t>
+          <t>-91.77</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>135236.1303418803</t>
+          <t>135088.9160739687</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>33572.0</t>
+          <t>44659.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>33291.6</v>
+        <v>32445.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>79907.5</t>
+          <t>79491.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>52563.6</v>
+        <v>53294.76</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-46615</t>
+          <t>-47045</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>1898.905653450633</t>
+          <t>341.3360578500112</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-8451.833814836384</t>
+          <t>-8225.29671795341</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>33572.0</t>
+          <t>44659.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>15.47</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2562</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>339.0</t>
+          <t>464.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-55.19</t>
+          <t>-58.34</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>295</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>34.29</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>16.19</t>
+          <t>37.62</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>73.08</v>
+        <v>73.05</v>
       </c>
       <c r="AN6" t="n">
-        <v>68.95999999999999</v>
+        <v>69.14</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>68.59</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-91.88</t>
+          <t>-77.02</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-88.90</t>
+          <t>-90.69</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>135236.1303418803</t>
+          <t>135088.9160739687</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>23968.0</t>
+          <t>33572.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>35206.4</v>
+        <v>33291.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>78572.9</t>
+          <t>79907.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>52193.48</v>
+        <v>52563.6</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-43366</t>
+          <t>-46615</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>3780.858284048273</t>
+          <t>1898.905653450633</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-7285.714174139335</t>
+          <t>-8451.833814836384</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>23968.0</t>
+          <t>33572.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>15.47</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2562</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>339.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-39.08</t>
+          <t>-55.19</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>295</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>34.29</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>16.19</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>73.16</v>
+        <v>73.08</v>
       </c>
       <c r="AN7" t="n">
-        <v>68.81</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>68.64</t>
+          <t>68.59</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-84.77</t>
+          <t>-91.88</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-86.35</t>
+          <t>-88.90</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>135236.1303418803</t>
+          <t>135088.9160739687</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>18778.0</t>
+          <t>23968.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>49174.8</v>
+        <v>35206.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>80723.8</t>
+          <t>78572.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>51860.5</v>
+        <v>52193.48</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-31549</t>
+          <t>-43366</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>5792.96236735511</t>
+          <t>3780.858284048273</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-4330.624895495712</t>
+          <t>-7285.714174139335</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>18778.0</t>
+          <t>23968.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-5.35</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>15.47</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2562</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>68.6</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>604.0</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>-39.08</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.99</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>295</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>71.06</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>73.26000000000001</v>
+        <v>73.16</v>
       </c>
       <c r="AN8" t="n">
-        <v>68.69</v>
+        <v>68.81</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>68.64</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-67.37</t>
+          <t>-84.77</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-83.45</t>
+          <t>-86.35</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>135236.1303418803</t>
+          <t>135088.9160739687</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>41249.0</t>
+          <t>18778.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>126334.6</v>
+        <v>49174.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>84751.5</t>
+          <t>80723.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>51658.1</v>
+        <v>51860.5</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>41583</t>
+          <t>-31549</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>7633.614596964351</t>
+          <t>5792.96236735511</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>601.6678202628682</t>
+          <t>-4330.624895495712</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>41249.0</t>
+          <t>18778.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-5.35</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>15.47</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2562</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3851,17 +3851,17 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>677.0</t>
+          <t>604.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>8.99</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,17 +4024,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>295</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4044,34 +4044,34 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>72.34</t>
+          <t>71.06</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>73.44</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="AN9" t="n">
-        <v>68.61</v>
+        <v>68.69</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4080,17 +4080,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-43.74</t>
+          <t>-67.37</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-80.67</t>
+          <t>-83.45</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>135236.1303418803</t>
+          <t>135088.9160739687</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>48891.0</t>
+          <t>41249.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>126537</v>
+        <v>126334.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>90533.7</t>
+          <t>84751.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>50941.56</v>
+        <v>51658.1</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>36003</t>
+          <t>41583</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>8912.15037454644</t>
+          <t>7633.614596964351</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>5218.704992051455</t>
+          <t>601.6678202628682</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>48891.0</t>
+          <t>41249.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>15.47</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2562</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>607.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>39.77</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>10.07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>295</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>21.09</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>7.33</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>72.91999999999999</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>73.48999999999999</v>
+        <v>73.44</v>
       </c>
       <c r="AN10" t="n">
-        <v>68.47</v>
+        <v>68.61</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>68.58</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-36.50</t>
+          <t>-43.74</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-78.55</t>
+          <t>-80.67</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>135236.1303418803</t>
+          <t>135088.9160739687</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>43146.0</t>
+          <t>48891.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>126523.4</v>
+        <v>126537</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>110266.6</t>
+          <t>90533.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>50056.24</v>
+        <v>50941.56</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>16256</t>
+          <t>36003</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>9583.685898636437</t>
+          <t>8912.15037454644</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>10809.30434489046</t>
+          <t>5218.704992051455</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>43146.0</t>
+          <t>48891.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>15.47</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2562</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1299.0</t>
+          <t>607.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-7.09</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>295</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>21.09</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>7.33</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>73.17999999999999</t>
+          <t>72.91999999999999</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>73.40000000000001</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="AN11" t="n">
-        <v>68.33</v>
+        <v>68.47</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>68.55</t>
+          <t>68.58</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-25.43</t>
+          <t>-36.50</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-76.60</t>
+          <t>-78.55</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>135236.1303418803</t>
+          <t>135088.9160739687</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>93810.0</t>
+          <t>43146.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>121939.4</v>
+        <v>126523.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>111374.5</t>
+          <t>110266.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>49406.96</v>
+        <v>50056.24</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>10564</t>
+          <t>16256</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>9360.846181135705</t>
+          <t>9583.685898636437</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>19025.36397948582</t>
+          <t>10809.30434489046</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>93810.0</t>
+          <t>43146.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>15.47</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2562</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5114.0</t>
+          <t>1299.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>76.10</t>
+          <t>19.33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-7.09</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>295</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>48.37</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>73.62</t>
+          <t>73.17999999999999</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>73.16</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="AN12" t="n">
-        <v>68.19</v>
+        <v>68.33</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>68.51</t>
+          <t>68.55</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-10.21</t>
+          <t>-25.43</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-75.11</t>
+          <t>-76.60</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>135236.1303418803</t>
+          <t>135088.9160739687</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>404577.0</t>
+          <t>93810.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>112272.8</v>
+        <v>121939.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>106038.9</t>
+          <t>111374.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>47927.76</v>
+        <v>49406.96</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>10564</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>7603.661126890231</t>
+          <t>9360.846181135705</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>24654.82902964039</t>
+          <t>19025.36397948582</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>404577.0</t>
+          <t>93810.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>15.47</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2562</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/電子觸控白板.xlsx
+++ b/Result/checksun_type/電子觸控白板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>295.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-12.43</t>
+          <t>-18.07</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>82.39</t>
+          <t>72.33</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>72.58000000000001</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>72.40000000000001</v>
+        <v>72.12</v>
       </c>
       <c r="AN2" t="n">
-        <v>69.77</v>
+        <v>69.84</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>68.67</t>
+          <t>68.69</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-36.70</t>
+          <t>-40.98</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-93.37</t>
+          <t>-93.98</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>135088.9160739687</t>
+          <t>134922.5049715909</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>21163.0</t>
+          <t>11957.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>27423</v>
+        <v>23100</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>31314.7</t>
+          <t>28195.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>53359.16</v>
+        <v>52497.52</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-3891</t>
+          <t>-5095</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3925.806973229156</t>
+          <t>-5062.92610585947</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-10777.00553015982</t>
+          <t>-11317.0813353262</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>21163.0</t>
+          <t>11957.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.47</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>284.0</t>
+          <t>295.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,102 +1338,102 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.81</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-12.43</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-08-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>72.3</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>69.6</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-2.34</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>10.63</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4.39</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>-2.68</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-3.38</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-27.46</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>69.6</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>10.63</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>4.23</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0.70</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>92.45</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>88.76</t>
+          <t>82.39</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>72.46000000000001</t>
+          <t>72.58000000000001</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>72.67</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AN3" t="n">
-        <v>69.65000000000001</v>
+        <v>69.77</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>68.66</t>
+          <t>68.67</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-20.53</t>
+          <t>-36.70</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-92.76</t>
+          <t>-93.37</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>135088.9160739687</t>
+          <t>134922.5049715909</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>20650.0</t>
+          <t>21163.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>27984</v>
+        <v>27423</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>38579.4</t>
+          <t>31314.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>53075.12</v>
+        <v>53359.16</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-10595</t>
+          <t>-3891</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-2680.134508332671</t>
+          <t>-3925.806973229156</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-10606.93275384499</t>
+          <t>-10777.00553015982</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>20650.0</t>
+          <t>21163.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.47</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1701,17 +1701,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>284.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-64.13</t>
+          <t>-27.46</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>92.45</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>79.37</t>
+          <t>88.76</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>71.67999999999999</t>
+          <t>72.46000000000001</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>72.88</v>
+        <v>72.67</v>
       </c>
       <c r="AN4" t="n">
-        <v>69.48999999999999</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>68.65</t>
+          <t>68.66</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-32.33</t>
+          <t>-20.53</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-92.39</t>
+          <t>-92.76</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>135088.9160739687</t>
+          <t>134922.5049715909</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>17071.0</t>
+          <t>20650.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>27609.6</v>
+        <v>27984</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>76972.1</t>
+          <t>38579.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>52850.06</v>
+        <v>53075.12</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-49362</t>
+          <t>-10595</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1238.898463694067</t>
+          <t>-2680.134508332671</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-9930.188332186495</t>
+          <t>-10606.93275384499</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>17071.0</t>
+          <t>20650.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.47</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>606.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-59.18</t>
+          <t>-64.13</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>75.71</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>79.37</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>70.64</t>
+          <t>71.67999999999999</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>72.97</v>
+        <v>72.88</v>
       </c>
       <c r="AN5" t="n">
-        <v>69.34</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>68.62</t>
+          <t>68.65</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-52.47</t>
+          <t>-32.33</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-91.77</t>
+          <t>-92.39</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>135088.9160739687</t>
+          <t>134922.5049715909</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>44659.0</t>
+          <t>17071.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>32445.2</v>
+        <v>27609.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>79491.1</t>
+          <t>76972.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>53294.76</v>
+        <v>52850.06</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-47045</t>
+          <t>-49362</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>341.3360578500112</t>
+          <t>-1238.898463694067</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-8225.29671795341</t>
+          <t>-9930.188332186495</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>44659.0</t>
+          <t>17071.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.47</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>464.0</t>
+          <t>606.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-58.34</t>
+          <t>-59.18</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>75.71</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>37.62</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.20</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.64</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>73.05</v>
+        <v>72.97</v>
       </c>
       <c r="AN6" t="n">
-        <v>69.14</v>
+        <v>69.34</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>68.62</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-77.02</t>
+          <t>-52.47</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-90.69</t>
+          <t>-91.77</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>135088.9160739687</t>
+          <t>134922.5049715909</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>33572.0</t>
+          <t>44659.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>33291.6</v>
+        <v>32445.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>79907.5</t>
+          <t>79491.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>52563.6</v>
+        <v>53294.76</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-46615</t>
+          <t>-47045</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>1898.905653450633</t>
+          <t>341.3360578500112</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-8451.833814836384</t>
+          <t>-8225.29671795341</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>33572.0</t>
+          <t>44659.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.47</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>339.0</t>
+          <t>464.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-55.19</t>
+          <t>-58.34</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>34.29</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>16.19</t>
+          <t>37.62</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>73.08</v>
+        <v>73.05</v>
       </c>
       <c r="AN7" t="n">
-        <v>68.95999999999999</v>
+        <v>69.14</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>68.59</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-91.88</t>
+          <t>-77.02</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-88.90</t>
+          <t>-90.69</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>135088.9160739687</t>
+          <t>134922.5049715909</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23968.0</t>
+          <t>33572.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>35206.4</v>
+        <v>33291.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>78572.9</t>
+          <t>79907.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>52193.48</v>
+        <v>52563.6</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-43366</t>
+          <t>-46615</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>3780.858284048273</t>
+          <t>1898.905653450633</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-7285.714174139335</t>
+          <t>-8451.833814836384</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>23968.0</t>
+          <t>33572.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.47</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>339.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-39.08</t>
+          <t>-55.19</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>34.29</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>16.19</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>73.16</v>
+        <v>73.08</v>
       </c>
       <c r="AN8" t="n">
-        <v>68.81</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>68.64</t>
+          <t>68.59</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-84.77</t>
+          <t>-91.88</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-86.35</t>
+          <t>-88.90</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>135088.9160739687</t>
+          <t>134922.5049715909</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>18778.0</t>
+          <t>23968.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>49174.8</v>
+        <v>35206.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>80723.8</t>
+          <t>78572.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>51860.5</v>
+        <v>52193.48</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-31549</t>
+          <t>-43366</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>5792.96236735511</t>
+          <t>3780.858284048273</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-4330.624895495712</t>
+          <t>-7285.714174139335</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>18778.0</t>
+          <t>23968.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-5.35</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.47</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>68.6</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>604.0</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>-39.08</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.99</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>71.06</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>73.26000000000001</v>
+        <v>73.16</v>
       </c>
       <c r="AN9" t="n">
-        <v>68.69</v>
+        <v>68.81</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>68.64</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-67.37</t>
+          <t>-84.77</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-83.45</t>
+          <t>-86.35</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>135088.9160739687</t>
+          <t>134922.5049715909</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>41249.0</t>
+          <t>18778.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>126334.6</v>
+        <v>49174.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>84751.5</t>
+          <t>80723.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>51658.1</v>
+        <v>51860.5</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>41583</t>
+          <t>-31549</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>7633.614596964351</t>
+          <t>5792.96236735511</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>601.6678202628682</t>
+          <t>-4330.624895495712</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>41249.0</t>
+          <t>18778.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-5.35</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.47</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4281,17 +4281,17 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>677.0</t>
+          <t>604.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>8.99</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,17 +4454,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4474,34 +4474,34 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>72.34</t>
+          <t>71.06</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>73.44</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="AN10" t="n">
-        <v>68.61</v>
+        <v>68.69</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4510,17 +4510,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-43.74</t>
+          <t>-67.37</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-80.67</t>
+          <t>-83.45</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>135088.9160739687</t>
+          <t>134922.5049715909</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>48891.0</t>
+          <t>41249.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>126537</v>
+        <v>126334.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>90533.7</t>
+          <t>84751.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>50941.56</v>
+        <v>51658.1</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>36003</t>
+          <t>41583</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>8912.15037454644</t>
+          <t>7633.614596964351</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>5218.704992051455</t>
+          <t>601.6678202628682</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>48891.0</t>
+          <t>41249.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.47</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>607.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>39.77</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>10.07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>21.09</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>7.33</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>72.91999999999999</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>73.48999999999999</v>
+        <v>73.44</v>
       </c>
       <c r="AN11" t="n">
-        <v>68.47</v>
+        <v>68.61</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>68.58</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-36.50</t>
+          <t>-43.74</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-78.55</t>
+          <t>-80.67</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>135088.9160739687</t>
+          <t>134922.5049715909</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>43146.0</t>
+          <t>48891.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>126523.4</v>
+        <v>126537</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>110266.6</t>
+          <t>90533.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>50056.24</v>
+        <v>50941.56</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>16256</t>
+          <t>36003</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>9583.685898636437</t>
+          <t>8912.15037454644</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>10809.30434489046</t>
+          <t>5218.704992051455</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>43146.0</t>
+          <t>48891.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.47</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1299.0</t>
+          <t>607.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-7.09</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>21.09</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>7.33</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>73.17999999999999</t>
+          <t>72.91999999999999</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>73.40000000000001</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="AN12" t="n">
-        <v>68.33</v>
+        <v>68.47</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>68.55</t>
+          <t>68.58</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-25.43</t>
+          <t>-36.50</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-76.60</t>
+          <t>-78.55</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>135088.9160739687</t>
+          <t>134922.5049715909</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>93810.0</t>
+          <t>43146.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>121939.4</v>
+        <v>126523.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>111374.5</t>
+          <t>110266.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>49406.96</v>
+        <v>50056.24</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>10564</t>
+          <t>16256</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>9360.846181135705</t>
+          <t>9583.685898636437</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>19025.36397948582</t>
+          <t>10809.30434489046</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>93810.0</t>
+          <t>43146.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.47</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/電子觸控白板.xlsx
+++ b/Result/checksun_type/電子觸控白板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-18.07</t>
+          <t>-25.64</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,22 +993,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -1019,146 +1019,146 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>72.09</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>72.33</t>
+          <t>65.54</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>72.16</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>72.09</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>69.89</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>68.72</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-36.20</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>7.72</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-94.48</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>134784.685106383</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>25173.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>19202.8</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>25824.0</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>50729.46</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-6621</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-5887.246299659477</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-10421.00736555951</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>25173.0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>72.9</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
           <t>-1.10</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>3.26</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>72.4</t>
-        </is>
-      </c>
-      <c r="AM2" t="n">
-        <v>72.12</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>69.84</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>68.69</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>-40.98</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>7.72</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-93.98</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>134922.5049715909</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>11957.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>23100</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>28195.8</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>52497.52</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-5095</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-5062.92610585947</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>-11317.0813353262</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>11957.0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>72.9</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>-1.78</t>
-        </is>
-      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>青雲</t>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>15.71</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2601</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>295.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-12.43</t>
+          <t>-18.07</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,68 +1449,68 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>82.39</t>
+          <t>72.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>72.58000000000001</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>72.40000000000001</v>
+        <v>72.12</v>
       </c>
       <c r="AN3" t="n">
-        <v>69.77</v>
+        <v>69.84</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>68.67</t>
+          <t>68.69</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-36.70</t>
+          <t>-40.98</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-93.37</t>
+          <t>-93.98</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>134922.5049715909</t>
+          <t>134784.685106383</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>21163.0</t>
+          <t>11957.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>27423</v>
+        <v>23100</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>31314.7</t>
+          <t>28195.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>53359.16</v>
+        <v>52497.52</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-3891</t>
+          <t>-5095</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3925.806973229156</t>
+          <t>-5062.92610585947</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-10777.00553015982</t>
+          <t>-11317.0813353262</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>21163.0</t>
+          <t>11957.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>15.71</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2601</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>284.0</t>
+          <t>295.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-27.46</t>
+          <t>-12.43</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,68 +1879,68 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>92.45</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>88.76</t>
+          <t>82.39</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>72.46000000000001</t>
+          <t>72.58000000000001</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>72.67</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AN4" t="n">
-        <v>69.65000000000001</v>
+        <v>69.77</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>68.66</t>
+          <t>68.67</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-20.53</t>
+          <t>-36.70</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-92.76</t>
+          <t>-93.37</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>134922.5049715909</t>
+          <t>134784.685106383</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>20650.0</t>
+          <t>21163.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>27984</v>
+        <v>27423</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>38579.4</t>
+          <t>31314.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>53075.12</v>
+        <v>53359.16</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-10595</t>
+          <t>-3891</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-2680.134508332671</t>
+          <t>-3925.806973229156</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-10606.93275384499</t>
+          <t>-10777.00553015982</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>20650.0</t>
+          <t>21163.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>15.71</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2601</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>284.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-64.13</t>
+          <t>-27.46</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,68 +2309,68 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>92.45</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>79.37</t>
+          <t>88.76</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>71.67999999999999</t>
+          <t>72.46000000000001</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>72.88</v>
+        <v>72.67</v>
       </c>
       <c r="AN5" t="n">
-        <v>69.48999999999999</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>68.65</t>
+          <t>68.66</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-32.33</t>
+          <t>-20.53</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-92.39</t>
+          <t>-92.76</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>134922.5049715909</t>
+          <t>134784.685106383</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>17071.0</t>
+          <t>20650.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>27609.6</v>
+        <v>27984</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>76972.1</t>
+          <t>38579.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>52850.06</v>
+        <v>53075.12</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-49362</t>
+          <t>-10595</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1238.898463694067</t>
+          <t>-2680.134508332671</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-9930.188332186495</t>
+          <t>-10606.93275384499</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>17071.0</t>
+          <t>20650.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>15.71</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2601</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>606.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-59.18</t>
+          <t>-64.13</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,68 +2739,68 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>75.71</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>79.37</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>70.64</t>
+          <t>71.67999999999999</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>72.97</v>
+        <v>72.88</v>
       </c>
       <c r="AN6" t="n">
-        <v>69.34</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>68.62</t>
+          <t>68.65</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-52.47</t>
+          <t>-32.33</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-91.77</t>
+          <t>-92.39</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>134922.5049715909</t>
+          <t>134784.685106383</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>44659.0</t>
+          <t>17071.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>32445.2</v>
+        <v>27609.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>79491.1</t>
+          <t>76972.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>53294.76</v>
+        <v>52850.06</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-47045</t>
+          <t>-49362</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>341.3360578500112</t>
+          <t>-1238.898463694067</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-8225.29671795341</t>
+          <t>-9930.188332186495</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>44659.0</t>
+          <t>17071.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>15.71</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2601</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>464.0</t>
+          <t>606.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-58.34</t>
+          <t>-59.18</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,68 +3169,68 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>75.71</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>37.62</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.20</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.64</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>73.05</v>
+        <v>72.97</v>
       </c>
       <c r="AN7" t="n">
-        <v>69.14</v>
+        <v>69.34</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>68.62</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-77.02</t>
+          <t>-52.47</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-90.69</t>
+          <t>-91.77</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>134922.5049715909</t>
+          <t>134784.685106383</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>33572.0</t>
+          <t>44659.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>33291.6</v>
+        <v>32445.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>79907.5</t>
+          <t>79491.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>52563.6</v>
+        <v>53294.76</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-46615</t>
+          <t>-47045</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>1898.905653450633</t>
+          <t>341.3360578500112</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-8451.833814836384</t>
+          <t>-8225.29671795341</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>33572.0</t>
+          <t>44659.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>15.71</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2601</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>339.0</t>
+          <t>464.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-55.19</t>
+          <t>-58.34</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,68 +3599,68 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>34.29</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>16.19</t>
+          <t>37.62</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>73.08</v>
+        <v>73.05</v>
       </c>
       <c r="AN8" t="n">
-        <v>68.95999999999999</v>
+        <v>69.14</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>68.59</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-91.88</t>
+          <t>-77.02</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-88.90</t>
+          <t>-90.69</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>134922.5049715909</t>
+          <t>134784.685106383</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>23968.0</t>
+          <t>33572.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>35206.4</v>
+        <v>33291.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>78572.9</t>
+          <t>79907.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>52193.48</v>
+        <v>52563.6</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-43366</t>
+          <t>-46615</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>3780.858284048273</t>
+          <t>1898.905653450633</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-7285.714174139335</t>
+          <t>-8451.833814836384</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>23968.0</t>
+          <t>33572.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>15.71</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2601</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>339.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-39.08</t>
+          <t>-55.19</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,68 +4029,68 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>34.29</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>16.19</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>73.16</v>
+        <v>73.08</v>
       </c>
       <c r="AN9" t="n">
-        <v>68.81</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>68.64</t>
+          <t>68.59</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-84.77</t>
+          <t>-91.88</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-86.35</t>
+          <t>-88.90</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>134922.5049715909</t>
+          <t>134784.685106383</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>18778.0</t>
+          <t>23968.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>49174.8</v>
+        <v>35206.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>80723.8</t>
+          <t>78572.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>51860.5</v>
+        <v>52193.48</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-31549</t>
+          <t>-43366</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>5792.96236735511</t>
+          <t>3780.858284048273</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-4330.624895495712</t>
+          <t>-7285.714174139335</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>18778.0</t>
+          <t>23968.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-5.35</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>15.71</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2601</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>68.6</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>604.0</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>-39.08</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.99</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,68 +4459,68 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>71.06</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>73.26000000000001</v>
+        <v>73.16</v>
       </c>
       <c r="AN10" t="n">
-        <v>68.69</v>
+        <v>68.81</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>68.64</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-67.37</t>
+          <t>-84.77</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-83.45</t>
+          <t>-86.35</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>134922.5049715909</t>
+          <t>134784.685106383</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>41249.0</t>
+          <t>18778.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>126334.6</v>
+        <v>49174.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>84751.5</t>
+          <t>80723.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>51658.1</v>
+        <v>51860.5</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>41583</t>
+          <t>-31549</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>7633.614596964351</t>
+          <t>5792.96236735511</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>601.6678202628682</t>
+          <t>-4330.624895495712</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>41249.0</t>
+          <t>18778.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-5.35</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>15.71</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2601</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4711,17 +4711,17 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>677.0</t>
+          <t>604.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>8.99</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4904,34 +4904,34 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>72.34</t>
+          <t>71.06</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>73.44</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="AN11" t="n">
-        <v>68.61</v>
+        <v>68.69</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -4940,17 +4940,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-43.74</t>
+          <t>-67.37</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-80.67</t>
+          <t>-83.45</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>134922.5049715909</t>
+          <t>134784.685106383</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>48891.0</t>
+          <t>41249.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>126537</v>
+        <v>126334.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>90533.7</t>
+          <t>84751.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>50941.56</v>
+        <v>51658.1</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>36003</t>
+          <t>41583</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>8912.15037454644</t>
+          <t>7633.614596964351</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>5218.704992051455</t>
+          <t>601.6678202628682</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>48891.0</t>
+          <t>41249.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>15.71</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2601</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>607.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>39.77</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>10.07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,68 +5319,68 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>21.09</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>7.33</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>72.91999999999999</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>73.48999999999999</v>
+        <v>73.44</v>
       </c>
       <c r="AN12" t="n">
-        <v>68.47</v>
+        <v>68.61</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>68.58</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-36.50</t>
+          <t>-43.74</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-78.55</t>
+          <t>-80.67</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>134922.5049715909</t>
+          <t>134784.685106383</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>43146.0</t>
+          <t>48891.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>126523.4</v>
+        <v>126537</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>110266.6</t>
+          <t>90533.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>50056.24</v>
+        <v>50941.56</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>16256</t>
+          <t>36003</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>9583.685898636437</t>
+          <t>8912.15037454644</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>10809.30434489046</t>
+          <t>5218.704992051455</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>43146.0</t>
+          <t>48891.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>15.71</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2601</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/電子觸控白板.xlsx
+++ b/Result/checksun_type/電子觸控白板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>643.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-25.64</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,95 +993,87 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>643</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>72.09</t>
+          <t>41.38</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>65.54</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0.10</t>
-        </is>
+          <t>60.47</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-0.21</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>72.16</t>
+          <t>71.84</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>72.09</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="AN2" t="n">
-        <v>69.89</v>
+        <v>69.97</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>68.72</t>
+          <t>68.74</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-36.20</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.43</t>
-        </is>
+          <t>-41.23</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.39</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1090,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-94.48</t>
+          <t>-95.00</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>134784.685106383</t>
+          <t>134691.690509915</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>25173.0</t>
+          <t>46087.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>19202.8</v>
+        <v>25006</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>25824.0</t>
+          <t>26307.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>50729.46</v>
+        <v>50970.78</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-6621</t>
+          <t>-1301</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-5887.246299659477</t>
+          <t>-6206.851546263225</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-10421.00736555951</t>
+          <t>-7964.680402583843</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>25173.0</t>
+          <t>46087.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.71</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1276,12 +1268,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-18.07</t>
+          <t>-25.64</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,172 +1415,164 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>643</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>72.09</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>72.33</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
+          <t>65.54</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>72.16</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>72.09</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>69.89</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>68.72</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>-36.20</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>7.72</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-94.48</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>134691.690509915</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>25173.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>19202.8</v>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>25824.0</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
+        <v>50729.46</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-6621</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-5887.246299659477</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-10421.00736555951</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>25173.0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>72.9</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
         <is>
           <t>-1.10</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>3.26</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>72.4</t>
-        </is>
-      </c>
-      <c r="AM3" t="n">
-        <v>72.12</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>69.84</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>68.69</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>-40.98</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>7.72</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-93.98</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>134784.685106383</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>11957.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="n">
-        <v>23100</v>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>28195.8</t>
-        </is>
-      </c>
-      <c r="AZ3" t="n">
-        <v>52497.52</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>-5095</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-5062.92610585947</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>-11317.0813353262</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>11957.0</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>72.9</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>-1.78</t>
-        </is>
-      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>青雲</t>
@@ -1631,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.71</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>295.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-12.43</t>
+          <t>-18.07</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,74 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>643</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>82.39</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>-2.18</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
+          <t>72.33</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.39</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>72.58000000000001</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>72.40000000000001</v>
+        <v>72.12</v>
       </c>
       <c r="AN4" t="n">
-        <v>69.77</v>
+        <v>69.84</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>68.67</t>
+          <t>68.69</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-36.70</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
+          <t>-40.98</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.46</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1950,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-93.37</t>
+          <t>-93.98</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>134784.685106383</t>
+          <t>134691.690509915</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>21163.0</t>
+          <t>11957.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>27423</v>
+        <v>23100</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>31314.7</t>
+          <t>28195.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>53359.16</v>
+        <v>52497.52</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-3891</t>
+          <t>-5095</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3925.806973229156</t>
+          <t>-5062.92610585947</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-10777.00553015982</t>
+          <t>-11317.0813353262</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>21163.0</t>
+          <t>11957.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.71</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>284.0</t>
+          <t>295.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-27.46</t>
+          <t>-12.43</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,74 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>643</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>92.45</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>88.76</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-0.29</t>
-        </is>
+          <t>82.39</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.26</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>72.46000000000001</t>
+          <t>72.58000000000001</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>72.67</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AN5" t="n">
-        <v>69.65000000000001</v>
+        <v>69.77</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>68.66</t>
+          <t>68.67</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-20.53</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>0.44</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
+          <t>-36.70</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.51</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-92.76</t>
+          <t>-93.37</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>134784.685106383</t>
+          <t>134691.690509915</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>20650.0</t>
+          <t>21163.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>27984</v>
+        <v>27423</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>38579.4</t>
+          <t>31314.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>53075.12</v>
+        <v>53359.16</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-10595</t>
+          <t>-3891</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-2680.134508332671</t>
+          <t>-3925.806973229156</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-10606.93275384499</t>
+          <t>-10777.00553015982</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>20650.0</t>
+          <t>21163.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.71</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2561,17 +2529,17 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>284.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-64.13</t>
+          <t>-27.46</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,74 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>643</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>92.45</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>79.37</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-1.64</t>
-        </is>
+          <t>88.76</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0.29</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>71.67999999999999</t>
+          <t>72.46000000000001</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>72.88</v>
+        <v>72.67</v>
       </c>
       <c r="AN6" t="n">
-        <v>69.48999999999999</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>68.65</t>
+          <t>68.66</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-32.33</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.59</t>
-        </is>
+          <t>-20.53</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.5600000000000001</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2810,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-92.39</t>
+          <t>-92.76</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>134784.685106383</t>
+          <t>134691.690509915</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>17071.0</t>
+          <t>20650.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>27609.6</v>
+        <v>27984</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>76972.1</t>
+          <t>38579.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>52850.06</v>
+        <v>53075.12</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-49362</t>
+          <t>-10595</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1238.898463694067</t>
+          <t>-2680.134508332671</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-9930.188332186495</t>
+          <t>-10606.93275384499</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>17071.0</t>
+          <t>20650.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.71</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>606.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-59.18</t>
+          <t>-64.13</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,74 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>643</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>75.71</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>58.1</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>3.77</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-3.20</t>
-        </is>
+          <t>79.37</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-1.64</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>70.64</t>
+          <t>71.67999999999999</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>72.97</v>
+        <v>72.88</v>
       </c>
       <c r="AN7" t="n">
-        <v>69.34</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>68.62</t>
+          <t>68.65</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-52.47</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>0.30</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.64</t>
-        </is>
+          <t>-32.33</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.59</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3240,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-91.77</t>
+          <t>-92.39</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>134784.685106383</t>
+          <t>134691.690509915</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>44659.0</t>
+          <t>17071.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>32445.2</v>
+        <v>27609.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>79491.1</t>
+          <t>76972.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>53294.76</v>
+        <v>52850.06</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-47045</t>
+          <t>-49362</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>341.3360578500112</t>
+          <t>-1238.898463694067</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-8225.29671795341</t>
+          <t>-9930.188332186495</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>44659.0</t>
+          <t>17071.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3303,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.71</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>464.0</t>
+          <t>606.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-58.34</t>
+          <t>-59.18</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,74 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>643</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>75.71</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>37.62</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>3.28</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-3.91</t>
-        </is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-3.2</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.64</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>73.05</v>
+        <v>72.97</v>
       </c>
       <c r="AN8" t="n">
-        <v>69.14</v>
+        <v>69.34</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>68.62</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-77.02</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
+          <t>-52.47</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.64</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3670,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-90.69</t>
+          <t>-91.77</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>134784.685106383</t>
+          <t>134691.690509915</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>33572.0</t>
+          <t>44659.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>33291.6</v>
+        <v>32445.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>79907.5</t>
+          <t>79491.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>52563.6</v>
+        <v>53294.76</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-46615</t>
+          <t>-47045</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>1898.905653450633</t>
+          <t>341.3360578500112</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-8451.833814836384</t>
+          <t>-8225.29671795341</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>33572.0</t>
+          <t>44659.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.71</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>339.0</t>
+          <t>464.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-55.19</t>
+          <t>-58.34</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,74 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>643</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>34.29</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>16.19</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0.80</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-4.43</t>
-        </is>
+          <t>37.62</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-3.91</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>73.08</v>
+        <v>73.05</v>
       </c>
       <c r="AN9" t="n">
-        <v>68.95999999999999</v>
+        <v>69.14</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>68.59</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-91.88</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.86</t>
-        </is>
+          <t>-77.02</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.72</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4100,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-88.90</t>
+          <t>-90.69</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>134784.685106383</t>
+          <t>134691.690509915</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>23968.0</t>
+          <t>33572.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>35206.4</v>
+        <v>33291.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>78572.9</t>
+          <t>79907.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>52193.48</v>
+        <v>52563.6</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-43366</t>
+          <t>-46615</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>3780.858284048273</t>
+          <t>1898.905653450633</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-7285.714174139335</t>
+          <t>-8451.833814836384</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>23968.0</t>
+          <t>33572.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.71</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>339.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-39.08</t>
+          <t>-55.19</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,74 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>643</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>34.29</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>9.21</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>-1.23</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-4.50</t>
-        </is>
+          <t>16.19</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-4.43</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>73.16</v>
+        <v>73.08</v>
       </c>
       <c r="AN10" t="n">
-        <v>68.81</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>68.64</t>
+          <t>68.59</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-84.77</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
+          <t>-91.88</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.86</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4530,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-86.35</t>
+          <t>-88.90</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>134784.685106383</t>
+          <t>134691.690509915</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>18778.0</t>
+          <t>23968.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>49174.8</v>
+        <v>35206.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>80723.8</t>
+          <t>78572.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>51860.5</v>
+        <v>52193.48</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-31549</t>
+          <t>-43366</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>5792.96236735511</t>
+          <t>3780.858284048273</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-4330.624895495712</t>
+          <t>-7285.714174139335</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>18778.0</t>
+          <t>23968.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-5.35</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4651,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.71</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>68.6</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>604.0</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>-39.08</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.99</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,74 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>643</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>5.93</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-4.31</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-3.01</t>
-        </is>
+          <t>9.21</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-4.5</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>71.06</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>73.26000000000001</v>
+        <v>73.16</v>
       </c>
       <c r="AN11" t="n">
-        <v>68.69</v>
+        <v>68.81</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>68.64</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-67.37</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>0.42</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
+          <t>-84.77</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.05</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4960,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-83.45</t>
+          <t>-86.35</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>134784.685106383</t>
+          <t>134691.690509915</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>41249.0</t>
+          <t>18778.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>126334.6</v>
+        <v>49174.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>84751.5</t>
+          <t>80723.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>51658.1</v>
+        <v>51860.5</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>41583</t>
+          <t>-31549</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>7633.614596964351</t>
+          <t>5792.96236735511</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>601.6678202628682</t>
+          <t>-4330.624895495712</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>41249.0</t>
+          <t>18778.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-5.35</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.71</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5141,17 +5061,17 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>677.0</t>
+          <t>604.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>8.99</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,17 +5234,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>643</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5332,36 +5252,32 @@
           <t>5.93</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>-1.71</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>-1.49</t>
-        </is>
+      <c r="AH12" t="n">
+        <v>-4.31</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-3.01</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>72.34</t>
+          <t>71.06</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>73.44</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="AN12" t="n">
-        <v>68.61</v>
+        <v>68.69</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5370,18 +5286,14 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-43.74</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
+          <t>-67.37</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.28</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5390,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-80.67</t>
+          <t>-83.45</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>134784.685106383</t>
+          <t>134691.690509915</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>48891.0</t>
+          <t>41249.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>126537</v>
+        <v>126334.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>90533.7</t>
+          <t>84751.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>50941.56</v>
+        <v>51658.1</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>36003</t>
+          <t>41583</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>8912.15037454644</t>
+          <t>7633.614596964351</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>5218.704992051455</t>
+          <t>601.6678202628682</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>48891.0</t>
+          <t>41249.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.71</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/電子觸控白板.xlsx
+++ b/Result/checksun_type/電子觸控白板.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>價_量;【b1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>643.0</t>
+          <t>3696.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,167 +913,167 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>2025-11-03 00:00:00</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>2025-11-11 00:00:00</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>77.0</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>72.7</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>69.6</t>
-        </is>
-      </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>55.00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>3696</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>41.38</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>60.47</t>
+          <t>71.16</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.33</v>
+        <v>6.62</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.21</v>
+        <v>0.83</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>71.84</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>71.98999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="AN2" t="n">
-        <v>69.97</v>
+        <v>70.19</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>68.74</t>
+          <t>68.84</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-41.23</t>
+          <t>50.94</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.23</v>
+        <v>0.67</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,58 +1082,58 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-95.00</t>
+          <t>-94.27</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>134691.690509915</t>
+          <t>135091.0693069307</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>46087.0</t>
+          <t>278035.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>25006</v>
+        <v>76483</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>26307.8</t>
+          <t>52233.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>50970.78</v>
+        <v>56172.26</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1301</t>
+          <t>24249</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-6206.851546263225</t>
+          <t>-3505.802772751387</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-7964.680402583843</t>
+          <t>11349.96548156372</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>46087.0</t>
+          <t>278035.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1253,27 +1253,27 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
+          <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>643.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-25.64</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1350,54 +1350,54 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>2025-11-03 00:00:00</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>2025-11-11 00:00:00</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>77.0</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>72.7</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>69.6</t>
-        </is>
-      </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1405,97 +1405,97 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>3696</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>72.09</t>
+          <t>41.38</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>65.54</t>
+          <t>60.47</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-0.08</v>
+        <v>-0.33</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.1</v>
+        <v>-0.21</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>72.16</t>
+          <t>71.84</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>72.09</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="AN3" t="n">
-        <v>69.89</v>
+        <v>69.97</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>68.72</t>
+          <t>68.74</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-36.20</t>
+          <t>-41.23</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,53 +1504,53 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-94.48</t>
+          <t>-95.00</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>134691.690509915</t>
+          <t>135091.0693069307</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>25173.0</t>
+          <t>46087.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>19202.8</v>
+        <v>25006</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>25824.0</t>
+          <t>26307.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>50729.46</v>
+        <v>50970.78</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-6621</t>
+          <t>-1301</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-5887.246299659477</t>
+          <t>-6206.851546263225</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-10421.00736555951</t>
+          <t>-7964.680402583843</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>25173.0</t>
+          <t>46087.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
+          <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-18.07</t>
+          <t>-25.64</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1772,54 +1772,54 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>2025-11-03 00:00:00</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>2025-11-11 00:00:00</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>77.0</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>72.7</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>69.6</t>
-        </is>
-      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1827,97 +1827,97 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>3696</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>72.09</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>72.33</t>
+          <t>65.54</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-1.1</v>
+        <v>-0.08</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.39</v>
+        <v>0.1</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.16</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>72.12</v>
+        <v>72.09</v>
       </c>
       <c r="AN4" t="n">
-        <v>69.84</v>
+        <v>69.89</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>68.69</t>
+          <t>68.72</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-40.98</t>
+          <t>-36.20</t>
         </is>
       </c>
       <c r="AQ4" t="n">
         <v>0.27</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,53 +1926,53 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-93.98</t>
+          <t>-94.48</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>134691.690509915</t>
+          <t>135091.0693069307</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>11957.0</t>
+          <t>25173.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>23100</v>
+        <v>19202.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>28195.8</t>
+          <t>25824.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>52497.52</v>
+        <v>50729.46</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-5095</t>
+          <t>-6621</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-5062.92610585947</t>
+          <t>-5887.246299659477</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-11317.0813353262</t>
+          <t>-10421.00736555951</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>11957.0</t>
+          <t>25173.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
+          <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>295.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-12.43</t>
+          <t>-18.07</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2194,54 +2194,54 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>2025-11-03 00:00:00</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>2025-11-11 00:00:00</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>77.0</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>72.7</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>69.6</t>
-        </is>
-      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2249,27 +2249,27 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>3696</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>82.39</t>
+          <t>72.33</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-2.18</v>
+        <v>-1.1</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.26</v>
+        <v>0.39</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>72.58000000000001</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>72.40000000000001</v>
+        <v>72.12</v>
       </c>
       <c r="AN5" t="n">
-        <v>69.77</v>
+        <v>69.84</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>68.67</t>
+          <t>68.69</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-36.70</t>
+          <t>-40.98</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.51</v>
+        <v>0.46</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,53 +2348,53 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-93.37</t>
+          <t>-93.98</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>134691.690509915</t>
+          <t>135091.0693069307</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>21163.0</t>
+          <t>11957.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>27423</v>
+        <v>23100</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>31314.7</t>
+          <t>28195.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>53359.16</v>
+        <v>52497.52</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-3891</t>
+          <t>-5095</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3925.806973229156</t>
+          <t>-5062.92610585947</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-10777.00553015982</t>
+          <t>-11317.0813353262</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>21163.0</t>
+          <t>11957.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2519,27 +2519,27 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
+          <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>284.0</t>
+          <t>295.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-27.46</t>
+          <t>-12.43</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2616,54 +2616,54 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>2025-11-03 00:00:00</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>2025-11-11 00:00:00</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>77.0</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>72.7</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>69.6</t>
-        </is>
-      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2671,27 +2671,27 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>3696</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>92.45</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>88.76</t>
+          <t>82.39</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.61</v>
+        <v>-2.18</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.29</v>
+        <v>0.26</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>72.46000000000001</t>
+          <t>72.58000000000001</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>72.67</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AN6" t="n">
-        <v>69.65000000000001</v>
+        <v>69.77</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>68.66</t>
+          <t>68.67</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-20.53</t>
+          <t>-36.70</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.44</v>
+        <v>0.32</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,53 +2770,53 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-92.76</t>
+          <t>-93.37</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>134691.690509915</t>
+          <t>135091.0693069307</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>20650.0</t>
+          <t>21163.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>27984</v>
+        <v>27423</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>38579.4</t>
+          <t>31314.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>53075.12</v>
+        <v>53359.16</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-10595</t>
+          <t>-3891</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-2680.134508332671</t>
+          <t>-3925.806973229156</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-10606.93275384499</t>
+          <t>-10777.00553015982</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>20650.0</t>
+          <t>21163.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
+          <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>284.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-64.13</t>
+          <t>-27.46</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3038,54 +3038,54 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>2025-11-03 00:00:00</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2025-11-11 00:00:00</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>77.0</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>72.7</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>69.6</t>
-        </is>
-      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>0</t>
@@ -3093,27 +3093,27 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>3696</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>92.45</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>79.37</t>
+          <t>88.76</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>2.12</v>
+        <v>0.61</v>
       </c>
       <c r="AI7" t="n">
-        <v>-1.64</v>
+        <v>-0.29</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>71.67999999999999</t>
+          <t>72.46000000000001</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>72.88</v>
+        <v>72.67</v>
       </c>
       <c r="AN7" t="n">
-        <v>69.48999999999999</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>68.65</t>
+          <t>68.66</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-32.33</t>
+          <t>-20.53</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,53 +3192,53 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-92.39</t>
+          <t>-92.76</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>134691.690509915</t>
+          <t>135091.0693069307</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>17071.0</t>
+          <t>20650.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>27609.6</v>
+        <v>27984</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>76972.1</t>
+          <t>38579.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>52850.06</v>
+        <v>53075.12</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-49362</t>
+          <t>-10595</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1238.898463694067</t>
+          <t>-2680.134508332671</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-9930.188332186495</t>
+          <t>-10606.93275384499</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>17071.0</t>
+          <t>20650.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3363,27 +3363,27 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
+          <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>606.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-59.18</t>
+          <t>-64.13</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3460,54 +3460,54 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>2025-11-03 00:00:00</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>2025-11-11 00:00:00</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>77.0</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>72.7</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>69.6</t>
-        </is>
-      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3515,27 +3515,27 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>3696</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>75.71</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>79.37</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>3.77</v>
+        <v>2.12</v>
       </c>
       <c r="AI8" t="n">
-        <v>-3.2</v>
+        <v>-1.64</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>70.64</t>
+          <t>71.67999999999999</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>72.97</v>
+        <v>72.88</v>
       </c>
       <c r="AN8" t="n">
-        <v>69.34</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>68.62</t>
+          <t>68.65</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-52.47</t>
+          <t>-32.33</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.64</v>
+        <v>0.59</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-91.77</t>
+          <t>-92.39</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>134691.690509915</t>
+          <t>135091.0693069307</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>44659.0</t>
+          <t>17071.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>32445.2</v>
+        <v>27609.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>79491.1</t>
+          <t>76972.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>53294.76</v>
+        <v>52850.06</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-47045</t>
+          <t>-49362</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>341.3360578500112</t>
+          <t>-1238.898463694067</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-8225.29671795341</t>
+          <t>-9930.188332186495</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>44659.0</t>
+          <t>17071.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3785,27 +3785,27 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
+          <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>464.0</t>
+          <t>606.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-58.34</t>
+          <t>-59.18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3882,54 +3882,54 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>2025-11-03 00:00:00</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>2025-11-11 00:00:00</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
       <c r="Q9" t="inlineStr">
         <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>77.0</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>72.7</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>69.6</t>
-        </is>
-      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>0</t>
@@ -3937,27 +3937,27 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>3696</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>75.71</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>37.62</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>3.28</v>
+        <v>3.77</v>
       </c>
       <c r="AI9" t="n">
-        <v>-3.91</v>
+        <v>-3.2</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.64</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>73.05</v>
+        <v>72.97</v>
       </c>
       <c r="AN9" t="n">
-        <v>69.14</v>
+        <v>69.34</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>68.62</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-77.02</t>
+          <t>-52.47</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>0.17</v>
+        <v>0.3</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,53 +4036,53 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-90.69</t>
+          <t>-91.77</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>134691.690509915</t>
+          <t>135091.0693069307</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>33572.0</t>
+          <t>44659.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>33291.6</v>
+        <v>32445.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>79907.5</t>
+          <t>79491.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>52563.6</v>
+        <v>53294.76</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-46615</t>
+          <t>-47045</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1898.905653450633</t>
+          <t>341.3360578500112</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-8451.833814836384</t>
+          <t>-8225.29671795341</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>33572.0</t>
+          <t>44659.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4207,27 +4207,27 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
+          <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>339.0</t>
+          <t>464.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-55.19</t>
+          <t>-58.34</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4304,54 +4304,54 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>2025-11-03 00:00:00</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>2025-11-11 00:00:00</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>77.0</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>72.7</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>69.6</t>
-        </is>
-      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>0</t>
@@ -4359,27 +4359,27 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>3696</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>34.29</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>16.19</t>
+          <t>37.62</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.8</v>
+        <v>3.28</v>
       </c>
       <c r="AI10" t="n">
-        <v>-4.43</v>
+        <v>-3.91</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>73.08</v>
+        <v>73.05</v>
       </c>
       <c r="AN10" t="n">
-        <v>68.95999999999999</v>
+        <v>69.14</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>68.59</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-91.88</t>
+          <t>-77.02</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.86</v>
+        <v>0.72</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,53 +4458,53 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-88.90</t>
+          <t>-90.69</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>134691.690509915</t>
+          <t>135091.0693069307</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>23968.0</t>
+          <t>33572.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>35206.4</v>
+        <v>33291.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>78572.9</t>
+          <t>79907.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>52193.48</v>
+        <v>52563.6</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-43366</t>
+          <t>-46615</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>3780.858284048273</t>
+          <t>1898.905653450633</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-7285.714174139335</t>
+          <t>-8451.833814836384</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>23968.0</t>
+          <t>33572.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,22 +4569,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4629,27 +4629,27 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
+          <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>339.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-39.08</t>
+          <t>-55.19</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4726,54 +4726,54 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>2025-11-03 00:00:00</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>2025-11-11 00:00:00</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>77.0</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>72.7</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>69.6</t>
-        </is>
-      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>0</t>
@@ -4781,27 +4781,27 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>3696</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>34.29</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>16.19</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-1.23</v>
+        <v>0.8</v>
       </c>
       <c r="AI11" t="n">
-        <v>-4.5</v>
+        <v>-4.43</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>73.16</v>
+        <v>73.08</v>
       </c>
       <c r="AN11" t="n">
-        <v>68.81</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>68.64</t>
+          <t>68.59</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-84.77</t>
+          <t>-91.88</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>0.16</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.05</v>
+        <v>0.86</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,53 +4880,53 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-86.35</t>
+          <t>-88.90</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>134691.690509915</t>
+          <t>135091.0693069307</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>18778.0</t>
+          <t>23968.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>49174.8</v>
+        <v>35206.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>80723.8</t>
+          <t>78572.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>51860.5</v>
+        <v>52193.48</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-31549</t>
+          <t>-43366</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>5792.96236735511</t>
+          <t>3780.858284048273</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-4330.624895495712</t>
+          <t>-7285.714174139335</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>18778.0</t>
+          <t>23968.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-5.35</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5051,27 +5051,27 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
+          <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>68.6</t>
-        </is>
-      </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>604.0</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>-39.08</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5148,54 +5148,54 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>2025-11-03 00:00:00</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>2025-11-11 00:00:00</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-08-07 00:00:00</t>
-        </is>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>77.0</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>72.7</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>69.6</t>
-        </is>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>0</t>
@@ -5203,27 +5203,27 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.99</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>3696</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-4.31</v>
+        <v>-1.23</v>
       </c>
       <c r="AI12" t="n">
-        <v>-3.01</v>
+        <v>-4.5</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>71.06</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>73.26000000000001</v>
+        <v>73.16</v>
       </c>
       <c r="AN12" t="n">
-        <v>68.69</v>
+        <v>68.81</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>68.64</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-67.37</t>
+          <t>-84.77</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>0.42</v>
+        <v>0.16</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,53 +5302,53 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-83.45</t>
+          <t>-86.35</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>134691.690509915</t>
+          <t>135091.0693069307</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>41249.0</t>
+          <t>18778.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>126334.6</v>
+        <v>49174.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>84751.5</t>
+          <t>80723.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>51658.1</v>
+        <v>51860.5</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>41583</t>
+          <t>-31549</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>7633.614596964351</t>
+          <t>5792.96236735511</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>601.6678202628682</t>
+          <t>-4330.624895495712</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>41249.0</t>
+          <t>18778.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-5.35</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
+          <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -5483,17 +5483,17 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/電子觸控白板.xlsx
+++ b/Result/checksun_type/電子觸控白板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3696.0</t>
+          <t>1658.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,74 +898,74 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-0.93</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>55.98</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>77.6</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>46.43</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>77.6</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>77.6</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>77.0</t>
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>55.00</t>
+          <t>24.67</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>48.48</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>71.16</t>
+          <t>63.29</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>6.62</v>
+        <v>1.06</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.83</v>
+        <v>1.61</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>73.41999999999999</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>72.18000000000001</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="AN2" t="n">
-        <v>70.19</v>
+        <v>70.37</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>68.84</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>46.64</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-94.27</t>
+          <t>-93.51</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,48 +1092,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>135091.0693069307</t>
+          <t>135164.2902542373</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>278035.0</t>
+          <t>124621.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>76483</v>
+        <v>97174.60000000001</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>52233.5</t>
+          <t>62298.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>56172.26</v>
+        <v>58392.04</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>24249</t>
+          <t>34875</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3505.802772751387</t>
+          <t>-954.076428723801</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>11349.96548156372</t>
+          <t>13080.41846342792</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>278035.0</t>
+          <t>124621.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>16.17</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>643.0</t>
+          <t>3696.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,27 +1330,27 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1415,87 +1415,87 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>55.00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>41.38</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>60.47</t>
+          <t>71.16</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-0.33</v>
+        <v>6.62</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.21</v>
+        <v>0.83</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>71.84</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>71.98999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="AN3" t="n">
-        <v>69.97</v>
+        <v>70.19</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>68.74</t>
+          <t>68.84</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-41.23</t>
+          <t>50.94</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0.23</v>
+        <v>0.67</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-95.00</t>
+          <t>-94.27</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,48 +1514,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>135091.0693069307</t>
+          <t>135164.2902542373</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>46087.0</t>
+          <t>278035.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>25006</v>
+        <v>76483</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>26307.8</t>
+          <t>52233.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>50970.78</v>
+        <v>56172.26</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1301</t>
+          <t>24249</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-6206.851546263225</t>
+          <t>-3505.802772751387</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-7964.680402583843</t>
+          <t>11349.96548156372</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>46087.0</t>
+          <t>278035.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>16.17</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>643.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-25.64</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1837,87 +1837,87 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>72.09</t>
+          <t>41.38</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>65.54</t>
+          <t>60.47</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.08</v>
+        <v>-0.33</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.1</v>
+        <v>-0.21</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>72.16</t>
+          <t>71.84</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>72.09</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="AN4" t="n">
-        <v>69.89</v>
+        <v>69.97</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>68.72</t>
+          <t>68.74</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-36.20</t>
+          <t>-41.23</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-94.48</t>
+          <t>-95.00</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>135091.0693069307</t>
+          <t>135164.2902542373</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>25173.0</t>
+          <t>46087.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>19202.8</v>
+        <v>25006</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>25824.0</t>
+          <t>26307.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>50729.46</v>
+        <v>50970.78</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-6621</t>
+          <t>-1301</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-5887.246299659477</t>
+          <t>-6206.851546263225</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-10421.00736555951</t>
+          <t>-7964.680402583843</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>25173.0</t>
+          <t>46087.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>16.17</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-18.07</t>
+          <t>-25.64</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2259,87 +2259,87 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>72.09</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>72.33</t>
+          <t>65.54</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-1.1</v>
+        <v>-0.08</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.39</v>
+        <v>0.1</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.16</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>72.12</v>
+        <v>72.09</v>
       </c>
       <c r="AN5" t="n">
-        <v>69.84</v>
+        <v>69.89</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>68.69</t>
+          <t>68.72</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-40.98</t>
+          <t>-36.20</t>
         </is>
       </c>
       <c r="AQ5" t="n">
         <v>0.27</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-93.98</t>
+          <t>-94.48</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>135091.0693069307</t>
+          <t>135164.2902542373</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>11957.0</t>
+          <t>25173.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>23100</v>
+        <v>19202.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>28195.8</t>
+          <t>25824.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>52497.52</v>
+        <v>50729.46</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-5095</t>
+          <t>-6621</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-5062.92610585947</t>
+          <t>-5887.246299659477</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-11317.0813353262</t>
+          <t>-10421.00736555951</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>11957.0</t>
+          <t>25173.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>16.17</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>295.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-12.43</t>
+          <t>-18.07</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>82.39</t>
+          <t>72.33</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-2.18</v>
+        <v>-1.1</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.26</v>
+        <v>0.39</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>72.58000000000001</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>72.40000000000001</v>
+        <v>72.12</v>
       </c>
       <c r="AN6" t="n">
-        <v>69.77</v>
+        <v>69.84</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>68.67</t>
+          <t>68.69</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-36.70</t>
+          <t>-40.98</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.51</v>
+        <v>0.46</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-93.37</t>
+          <t>-93.98</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>135091.0693069307</t>
+          <t>135164.2902542373</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>21163.0</t>
+          <t>11957.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>27423</v>
+        <v>23100</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>31314.7</t>
+          <t>28195.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>53359.16</v>
+        <v>52497.52</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-3891</t>
+          <t>-5095</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3925.806973229156</t>
+          <t>-5062.92610585947</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-10777.00553015982</t>
+          <t>-11317.0813353262</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>21163.0</t>
+          <t>11957.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>16.17</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>284.0</t>
+          <t>295.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-27.46</t>
+          <t>-12.43</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>92.45</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>88.76</t>
+          <t>82.39</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.61</v>
+        <v>-2.18</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.29</v>
+        <v>0.26</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>72.46000000000001</t>
+          <t>72.58000000000001</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>72.67</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AN7" t="n">
-        <v>69.65000000000001</v>
+        <v>69.77</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>68.66</t>
+          <t>68.67</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-20.53</t>
+          <t>-36.70</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.44</v>
+        <v>0.32</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-92.76</t>
+          <t>-93.37</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>135091.0693069307</t>
+          <t>135164.2902542373</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>20650.0</t>
+          <t>21163.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>27984</v>
+        <v>27423</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>38579.4</t>
+          <t>31314.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>53075.12</v>
+        <v>53359.16</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-10595</t>
+          <t>-3891</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-2680.134508332671</t>
+          <t>-3925.806973229156</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-10606.93275384499</t>
+          <t>-10777.00553015982</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>20650.0</t>
+          <t>21163.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>16.17</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3373,17 +3373,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>284.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-64.13</t>
+          <t>-27.46</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>92.45</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>79.37</t>
+          <t>88.76</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>2.12</v>
+        <v>0.61</v>
       </c>
       <c r="AI8" t="n">
-        <v>-1.64</v>
+        <v>-0.29</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>71.67999999999999</t>
+          <t>72.46000000000001</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>72.88</v>
+        <v>72.67</v>
       </c>
       <c r="AN8" t="n">
-        <v>69.48999999999999</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>68.65</t>
+          <t>68.66</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-32.33</t>
+          <t>-20.53</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-92.39</t>
+          <t>-92.76</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>135091.0693069307</t>
+          <t>135164.2902542373</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>17071.0</t>
+          <t>20650.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>27609.6</v>
+        <v>27984</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>76972.1</t>
+          <t>38579.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>52850.06</v>
+        <v>53075.12</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-49362</t>
+          <t>-10595</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1238.898463694067</t>
+          <t>-2680.134508332671</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-9930.188332186495</t>
+          <t>-10606.93275384499</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>17071.0</t>
+          <t>20650.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>16.17</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>606.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-59.18</t>
+          <t>-64.13</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>75.71</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>79.37</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>3.77</v>
+        <v>2.12</v>
       </c>
       <c r="AI9" t="n">
-        <v>-3.2</v>
+        <v>-1.64</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>70.64</t>
+          <t>71.67999999999999</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>72.97</v>
+        <v>72.88</v>
       </c>
       <c r="AN9" t="n">
-        <v>69.34</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>68.62</t>
+          <t>68.65</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-52.47</t>
+          <t>-32.33</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.64</v>
+        <v>0.59</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-91.77</t>
+          <t>-92.39</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>135091.0693069307</t>
+          <t>135164.2902542373</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>44659.0</t>
+          <t>17071.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>32445.2</v>
+        <v>27609.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>79491.1</t>
+          <t>76972.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>53294.76</v>
+        <v>52850.06</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-47045</t>
+          <t>-49362</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>341.3360578500112</t>
+          <t>-1238.898463694067</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-8225.29671795341</t>
+          <t>-9930.188332186495</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>44659.0</t>
+          <t>17071.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>16.17</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>464.0</t>
+          <t>606.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-58.34</t>
+          <t>-59.18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>75.71</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>37.62</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>3.28</v>
+        <v>3.77</v>
       </c>
       <c r="AI10" t="n">
-        <v>-3.91</v>
+        <v>-3.2</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.64</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>73.05</v>
+        <v>72.97</v>
       </c>
       <c r="AN10" t="n">
-        <v>69.14</v>
+        <v>69.34</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>68.62</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-77.02</t>
+          <t>-52.47</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>0.17</v>
+        <v>0.3</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-90.69</t>
+          <t>-91.77</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>135091.0693069307</t>
+          <t>135164.2902542373</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>33572.0</t>
+          <t>44659.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>33291.6</v>
+        <v>32445.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>79907.5</t>
+          <t>79491.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>52563.6</v>
+        <v>53294.76</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-46615</t>
+          <t>-47045</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1898.905653450633</t>
+          <t>341.3360578500112</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-8451.833814836384</t>
+          <t>-8225.29671795341</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>33572.0</t>
+          <t>44659.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>16.17</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>339.0</t>
+          <t>464.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-55.19</t>
+          <t>-58.34</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>34.29</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>16.19</t>
+          <t>37.62</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.8</v>
+        <v>3.28</v>
       </c>
       <c r="AI11" t="n">
-        <v>-4.43</v>
+        <v>-3.91</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>73.08</v>
+        <v>73.05</v>
       </c>
       <c r="AN11" t="n">
-        <v>68.95999999999999</v>
+        <v>69.14</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>68.59</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-91.88</t>
+          <t>-77.02</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.86</v>
+        <v>0.72</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-88.90</t>
+          <t>-90.69</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>135091.0693069307</t>
+          <t>135164.2902542373</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>23968.0</t>
+          <t>33572.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>35206.4</v>
+        <v>33291.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>78572.9</t>
+          <t>79907.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>52193.48</v>
+        <v>52563.6</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-43366</t>
+          <t>-46615</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>3780.858284048273</t>
+          <t>1898.905653450633</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-7285.714174139335</t>
+          <t>-8451.833814836384</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>23968.0</t>
+          <t>33572.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>16.17</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>339.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-39.08</t>
+          <t>-55.19</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>34.29</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>16.19</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-1.23</v>
+        <v>0.8</v>
       </c>
       <c r="AI12" t="n">
-        <v>-4.5</v>
+        <v>-4.43</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>73.16</v>
+        <v>73.08</v>
       </c>
       <c r="AN12" t="n">
-        <v>68.81</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>68.64</t>
+          <t>68.59</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-84.77</t>
+          <t>-91.88</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>0.16</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.05</v>
+        <v>0.86</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-86.35</t>
+          <t>-88.90</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>135091.0693069307</t>
+          <t>135164.2902542373</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>18778.0</t>
+          <t>23968.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>49174.8</v>
+        <v>35206.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>80723.8</t>
+          <t>78572.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>51860.5</v>
+        <v>52193.48</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-31549</t>
+          <t>-43366</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>5792.96236735511</t>
+          <t>3780.858284048273</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-4330.624895495712</t>
+          <t>-7285.714174139335</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>18778.0</t>
+          <t>23968.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-5.35</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>16.17</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>68.6</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/電子觸控白板.xlsx
+++ b/Result/checksun_type/電子觸控白板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1658.0</t>
+          <t>742.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>55.98</t>
+          <t>64.16</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>742</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.48</t>
+          <t>46.97</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>63.29</t>
+          <t>65.15</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>1.06</v>
+        <v>0.24</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.61</v>
+        <v>2.16</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>73.41999999999999</t>
+          <t>73.92</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>72.26000000000001</v>
+        <v>72.36</v>
       </c>
       <c r="AN2" t="n">
-        <v>70.37</v>
+        <v>70.55</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>68.94</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>38.86</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-93.51</t>
+          <t>-92.81</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,48 +1092,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>135164.2902542373</t>
+          <t>135090.071932299</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>124621.0</t>
+          <t>55029.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>97174.60000000001</v>
+        <v>105789</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>62298.8</t>
+          <t>64444.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>58392.04</v>
+        <v>59232.94</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>34875</t>
+          <t>41344</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-954.076428723801</t>
+          <t>538.1391894101968</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>13080.41846342792</t>
+          <t>8745.325089147183</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>124621.0</t>
+          <t>55029.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>16.17</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>74.1</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>74.2</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3696.0</t>
+          <t>1658.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,74 +1320,74 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.88</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>55.98</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>77.6</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-4.58</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-0.93</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>46.43</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>77.6</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>77.6</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
           <t>77.0</t>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>55.00</t>
+          <t>24.67</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>742</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>48.48</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>71.16</t>
+          <t>63.29</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>6.62</v>
+        <v>1.06</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.83</v>
+        <v>1.61</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>73.41999999999999</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>72.18000000000001</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="AN3" t="n">
-        <v>70.19</v>
+        <v>70.37</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>68.84</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>46.64</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-94.27</t>
+          <t>-93.51</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,48 +1514,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>135164.2902542373</t>
+          <t>135090.071932299</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>278035.0</t>
+          <t>124621.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>76483</v>
+        <v>97174.60000000001</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>52233.5</t>
+          <t>62298.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>56172.26</v>
+        <v>58392.04</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>24249</t>
+          <t>34875</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3505.802772751387</t>
+          <t>-954.076428723801</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>11349.96548156372</t>
+          <t>13080.41846342792</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>278035.0</t>
+          <t>124621.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>16.17</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1717,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>643.0</t>
+          <t>3696.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,22 +1752,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1837,87 +1837,87 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>55.00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>742</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>41.38</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>60.47</t>
+          <t>71.16</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.33</v>
+        <v>6.62</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.21</v>
+        <v>0.83</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>71.84</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>71.98999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="AN4" t="n">
-        <v>69.97</v>
+        <v>70.19</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>68.74</t>
+          <t>68.84</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-41.23</t>
+          <t>50.94</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0.23</v>
+        <v>0.67</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-95.00</t>
+          <t>-94.27</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,48 +1936,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>135164.2902542373</t>
+          <t>135090.071932299</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>46087.0</t>
+          <t>278035.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>25006</v>
+        <v>76483</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>26307.8</t>
+          <t>52233.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>50970.78</v>
+        <v>56172.26</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1301</t>
+          <t>24249</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-6206.851546263225</t>
+          <t>-3505.802772751387</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-7964.680402583843</t>
+          <t>11349.96548156372</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>46087.0</t>
+          <t>278035.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>16.17</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>643.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-25.64</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2259,87 +2259,87 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>742</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>72.09</t>
+          <t>41.38</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>65.54</t>
+          <t>60.47</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.08</v>
+        <v>-0.33</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.1</v>
+        <v>-0.21</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>72.16</t>
+          <t>71.84</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>72.09</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="AN5" t="n">
-        <v>69.89</v>
+        <v>69.97</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>68.72</t>
+          <t>68.74</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-36.20</t>
+          <t>-41.23</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-94.48</t>
+          <t>-95.00</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>135164.2902542373</t>
+          <t>135090.071932299</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>25173.0</t>
+          <t>46087.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>19202.8</v>
+        <v>25006</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>25824.0</t>
+          <t>26307.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>50729.46</v>
+        <v>50970.78</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-6621</t>
+          <t>-1301</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-5887.246299659477</t>
+          <t>-6206.851546263225</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-10421.00736555951</t>
+          <t>-7964.680402583843</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>25173.0</t>
+          <t>46087.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>16.17</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-18.07</t>
+          <t>-25.64</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2681,87 +2681,87 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>742</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>72.09</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>72.33</t>
+          <t>65.54</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-1.1</v>
+        <v>-0.08</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.39</v>
+        <v>0.1</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.16</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>72.12</v>
+        <v>72.09</v>
       </c>
       <c r="AN6" t="n">
-        <v>69.84</v>
+        <v>69.89</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>68.69</t>
+          <t>68.72</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-40.98</t>
+          <t>-36.20</t>
         </is>
       </c>
       <c r="AQ6" t="n">
         <v>0.27</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-93.98</t>
+          <t>-94.48</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>135164.2902542373</t>
+          <t>135090.071932299</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>11957.0</t>
+          <t>25173.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>23100</v>
+        <v>19202.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>28195.8</t>
+          <t>25824.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>52497.52</v>
+        <v>50729.46</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-5095</t>
+          <t>-6621</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-5062.92610585947</t>
+          <t>-5887.246299659477</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-11317.0813353262</t>
+          <t>-10421.00736555951</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>11957.0</t>
+          <t>25173.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>16.17</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>295.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-12.43</t>
+          <t>-18.07</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>742</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>82.39</t>
+          <t>72.33</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-2.18</v>
+        <v>-1.1</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.26</v>
+        <v>0.39</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>72.58000000000001</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.12</v>
       </c>
       <c r="AN7" t="n">
-        <v>69.77</v>
+        <v>69.84</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>68.67</t>
+          <t>68.69</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-36.70</t>
+          <t>-40.98</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.51</v>
+        <v>0.46</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-93.37</t>
+          <t>-93.98</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>135164.2902542373</t>
+          <t>135090.071932299</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>21163.0</t>
+          <t>11957.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>27423</v>
+        <v>23100</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>31314.7</t>
+          <t>28195.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>53359.16</v>
+        <v>52497.52</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-3891</t>
+          <t>-5095</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3925.806973229156</t>
+          <t>-5062.92610585947</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-10777.00553015982</t>
+          <t>-11317.0813353262</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>21163.0</t>
+          <t>11957.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>16.17</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>284.0</t>
+          <t>295.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-27.46</t>
+          <t>-12.43</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>742</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>92.45</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>88.76</t>
+          <t>82.39</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.61</v>
+        <v>-2.18</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.29</v>
+        <v>0.26</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>72.46000000000001</t>
+          <t>72.58000000000001</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>72.67</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AN8" t="n">
-        <v>69.65000000000001</v>
+        <v>69.77</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>68.66</t>
+          <t>68.67</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-20.53</t>
+          <t>-36.70</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.44</v>
+        <v>0.32</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-92.76</t>
+          <t>-93.37</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>135164.2902542373</t>
+          <t>135090.071932299</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>20650.0</t>
+          <t>21163.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>27984</v>
+        <v>27423</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>38579.4</t>
+          <t>31314.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>53075.12</v>
+        <v>53359.16</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-10595</t>
+          <t>-3891</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-2680.134508332671</t>
+          <t>-3925.806973229156</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-10606.93275384499</t>
+          <t>-10777.00553015982</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>20650.0</t>
+          <t>21163.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>16.17</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3795,17 +3795,17 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>284.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-64.13</t>
+          <t>-27.46</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>742</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>92.45</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>79.37</t>
+          <t>88.76</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>2.12</v>
+        <v>0.61</v>
       </c>
       <c r="AI9" t="n">
-        <v>-1.64</v>
+        <v>-0.29</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>71.67999999999999</t>
+          <t>72.46000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>72.88</v>
+        <v>72.67</v>
       </c>
       <c r="AN9" t="n">
-        <v>69.48999999999999</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>68.65</t>
+          <t>68.66</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-32.33</t>
+          <t>-20.53</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-92.39</t>
+          <t>-92.76</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>135164.2902542373</t>
+          <t>135090.071932299</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>17071.0</t>
+          <t>20650.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>27609.6</v>
+        <v>27984</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>76972.1</t>
+          <t>38579.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>52850.06</v>
+        <v>53075.12</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-49362</t>
+          <t>-10595</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1238.898463694067</t>
+          <t>-2680.134508332671</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-9930.188332186495</t>
+          <t>-10606.93275384499</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>17071.0</t>
+          <t>20650.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>16.17</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>606.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-59.18</t>
+          <t>-64.13</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>742</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>75.71</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>79.37</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>3.77</v>
+        <v>2.12</v>
       </c>
       <c r="AI10" t="n">
-        <v>-3.2</v>
+        <v>-1.64</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>70.64</t>
+          <t>71.67999999999999</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>72.97</v>
+        <v>72.88</v>
       </c>
       <c r="AN10" t="n">
-        <v>69.34</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>68.62</t>
+          <t>68.65</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-52.47</t>
+          <t>-32.33</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.64</v>
+        <v>0.59</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-91.77</t>
+          <t>-92.39</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>135164.2902542373</t>
+          <t>135090.071932299</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>44659.0</t>
+          <t>17071.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>32445.2</v>
+        <v>27609.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>79491.1</t>
+          <t>76972.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>53294.76</v>
+        <v>52850.06</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-47045</t>
+          <t>-49362</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>341.3360578500112</t>
+          <t>-1238.898463694067</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-8225.29671795341</t>
+          <t>-9930.188332186495</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>44659.0</t>
+          <t>17071.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>16.17</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>464.0</t>
+          <t>606.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-58.34</t>
+          <t>-59.18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>742</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>75.71</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>37.62</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>3.28</v>
+        <v>3.77</v>
       </c>
       <c r="AI11" t="n">
-        <v>-3.91</v>
+        <v>-3.2</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.64</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>73.05</v>
+        <v>72.97</v>
       </c>
       <c r="AN11" t="n">
-        <v>69.14</v>
+        <v>69.34</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>68.62</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-77.02</t>
+          <t>-52.47</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>0.17</v>
+        <v>0.3</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-90.69</t>
+          <t>-91.77</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>135164.2902542373</t>
+          <t>135090.071932299</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>33572.0</t>
+          <t>44659.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>33291.6</v>
+        <v>32445.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>79907.5</t>
+          <t>79491.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>52563.6</v>
+        <v>53294.76</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-46615</t>
+          <t>-47045</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>1898.905653450633</t>
+          <t>341.3360578500112</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-8451.833814836384</t>
+          <t>-8225.29671795341</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>33572.0</t>
+          <t>44659.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>16.17</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>339.0</t>
+          <t>464.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-55.19</t>
+          <t>-58.34</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>742</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>34.29</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>16.19</t>
+          <t>37.62</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>0.8</v>
+        <v>3.28</v>
       </c>
       <c r="AI12" t="n">
-        <v>-4.43</v>
+        <v>-3.91</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>73.08</v>
+        <v>73.05</v>
       </c>
       <c r="AN12" t="n">
-        <v>68.95999999999999</v>
+        <v>69.14</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>68.59</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-91.88</t>
+          <t>-77.02</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.86</v>
+        <v>0.72</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-88.90</t>
+          <t>-90.69</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>135164.2902542373</t>
+          <t>135090.071932299</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>23968.0</t>
+          <t>33572.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>35206.4</v>
+        <v>33291.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>78572.9</t>
+          <t>79907.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>52193.48</v>
+        <v>52563.6</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-43366</t>
+          <t>-46615</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>3780.858284048273</t>
+          <t>1898.905653450633</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-7285.714174139335</t>
+          <t>-8451.833814836384</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>23968.0</t>
+          <t>33572.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>16.17</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/電子觸控白板.xlsx
+++ b/Result/checksun_type/電子觸控白板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>742.0</t>
+          <t>788.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>64.16</t>
+          <t>70.88</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,87 +993,87 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>788</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.97</t>
+          <t>53.03</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>65.15</t>
+          <t>49.49</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0.24</v>
+        <v>0.13</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.16</v>
+        <v>2.78</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>73.92</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>72.36</v>
+        <v>72.39</v>
       </c>
       <c r="AN2" t="n">
-        <v>70.55</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>68.94</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>35.10</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-92.81</t>
+          <t>-92.12</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,48 +1092,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>135090.071932299</t>
+          <t>135025.7049295775</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>55029.0</t>
+          <t>59593.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>105789</v>
+        <v>112673</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>64444.5</t>
+          <t>65937.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>59232.94</v>
+        <v>60058.06</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>41344</t>
+          <t>46735</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>538.1391894101968</t>
+          <t>1352.95263718124</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>8745.325089147183</t>
+          <t>5834.426599921979</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>55029.0</t>
+          <t>59593.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>16.23</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1658.0</t>
+          <t>742.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>55.98</t>
+          <t>64.16</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>788</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>48.48</t>
+          <t>46.97</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>63.29</t>
+          <t>65.15</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>1.06</v>
+        <v>0.24</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.61</v>
+        <v>2.16</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>73.41999999999999</t>
+          <t>73.92</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>72.26000000000001</v>
+        <v>72.36</v>
       </c>
       <c r="AN3" t="n">
-        <v>70.37</v>
+        <v>70.55</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>68.94</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>38.86</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-93.51</t>
+          <t>-92.81</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,48 +1514,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>135090.071932299</t>
+          <t>135025.7049295775</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>124621.0</t>
+          <t>55029.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>97174.60000000001</v>
+        <v>105789</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>62298.8</t>
+          <t>64444.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>58392.04</v>
+        <v>59232.94</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>34875</t>
+          <t>41344</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-954.076428723801</t>
+          <t>538.1391894101968</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>13080.41846342792</t>
+          <t>8745.325089147183</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>124621.0</t>
+          <t>55029.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>16.23</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>74.1</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>74.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3696.0</t>
+          <t>1658.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,74 +1742,74 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-2.03</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>55.98</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-12-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>77.6</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-4.72</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-1.88</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>46.43</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-12-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>77.6</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>77.6</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
           <t>77.0</t>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>55.00</t>
+          <t>24.67</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>788</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>48.48</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>71.16</t>
+          <t>63.29</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>6.62</v>
+        <v>1.06</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.83</v>
+        <v>1.61</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>73.41999999999999</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>72.18000000000001</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="AN4" t="n">
-        <v>70.19</v>
+        <v>70.37</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>68.84</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>46.64</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-94.27</t>
+          <t>-93.51</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,48 +1936,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>135090.071932299</t>
+          <t>135025.7049295775</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>278035.0</t>
+          <t>124621.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>76483</v>
+        <v>97174.60000000001</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>52233.5</t>
+          <t>62298.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>56172.26</v>
+        <v>58392.04</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>24249</t>
+          <t>34875</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3505.802772751387</t>
+          <t>-954.076428723801</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>11349.96548156372</t>
+          <t>13080.41846342792</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>278035.0</t>
+          <t>124621.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>16.23</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>643.0</t>
+          <t>3696.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,22 +2174,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2259,87 +2259,87 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>55.00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>788</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>41.38</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>60.47</t>
+          <t>71.16</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.33</v>
+        <v>6.62</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.21</v>
+        <v>0.83</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>71.84</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>71.98999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="AN5" t="n">
-        <v>69.97</v>
+        <v>70.19</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>68.74</t>
+          <t>68.84</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-41.23</t>
+          <t>50.94</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.23</v>
+        <v>0.67</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-95.00</t>
+          <t>-94.27</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,48 +2358,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>135090.071932299</t>
+          <t>135025.7049295775</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>46087.0</t>
+          <t>278035.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>25006</v>
+        <v>76483</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>26307.8</t>
+          <t>52233.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>50970.78</v>
+        <v>56172.26</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1301</t>
+          <t>24249</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-6206.851546263225</t>
+          <t>-3505.802772751387</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-7964.680402583843</t>
+          <t>11349.96548156372</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>46087.0</t>
+          <t>278035.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>16.23</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>643.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-25.64</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2681,87 +2681,87 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>788</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>72.09</t>
+          <t>41.38</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>65.54</t>
+          <t>60.47</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-0.08</v>
+        <v>-0.33</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.1</v>
+        <v>-0.21</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>72.16</t>
+          <t>71.84</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>72.09</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="AN6" t="n">
-        <v>69.89</v>
+        <v>69.97</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>68.72</t>
+          <t>68.74</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-36.20</t>
+          <t>-41.23</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-94.48</t>
+          <t>-95.00</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>135090.071932299</t>
+          <t>135025.7049295775</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>25173.0</t>
+          <t>46087.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>19202.8</v>
+        <v>25006</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>25824.0</t>
+          <t>26307.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>50729.46</v>
+        <v>50970.78</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-6621</t>
+          <t>-1301</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-5887.246299659477</t>
+          <t>-6206.851546263225</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-10421.00736555951</t>
+          <t>-7964.680402583843</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>25173.0</t>
+          <t>46087.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,22 +2881,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>16.23</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2956,12 +2956,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-18.07</t>
+          <t>-25.64</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3103,87 +3103,87 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>788</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>72.09</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>72.33</t>
+          <t>65.54</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-1.1</v>
+        <v>-0.08</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.39</v>
+        <v>0.1</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.16</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>72.12</v>
+        <v>72.09</v>
       </c>
       <c r="AN7" t="n">
-        <v>69.84</v>
+        <v>69.89</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>68.69</t>
+          <t>68.72</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-40.98</t>
+          <t>-36.20</t>
         </is>
       </c>
       <c r="AQ7" t="n">
         <v>0.27</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-93.98</t>
+          <t>-94.48</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>135090.071932299</t>
+          <t>135025.7049295775</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>11957.0</t>
+          <t>25173.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>23100</v>
+        <v>19202.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>28195.8</t>
+          <t>25824.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>52497.52</v>
+        <v>50729.46</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-5095</t>
+          <t>-6621</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-5062.92610585947</t>
+          <t>-5887.246299659477</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-11317.0813353262</t>
+          <t>-10421.00736555951</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>11957.0</t>
+          <t>25173.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>16.23</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>295.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-12.43</t>
+          <t>-18.07</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>788</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>82.39</t>
+          <t>72.33</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-2.18</v>
+        <v>-1.1</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.26</v>
+        <v>0.39</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>72.58000000000001</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.12</v>
       </c>
       <c r="AN8" t="n">
-        <v>69.77</v>
+        <v>69.84</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>68.67</t>
+          <t>68.69</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-36.70</t>
+          <t>-40.98</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.51</v>
+        <v>0.46</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-93.37</t>
+          <t>-93.98</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>135090.071932299</t>
+          <t>135025.7049295775</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>21163.0</t>
+          <t>11957.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>27423</v>
+        <v>23100</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>31314.7</t>
+          <t>28195.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>53359.16</v>
+        <v>52497.52</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-3891</t>
+          <t>-5095</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3925.806973229156</t>
+          <t>-5062.92610585947</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-10777.00553015982</t>
+          <t>-11317.0813353262</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>21163.0</t>
+          <t>11957.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>16.23</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>284.0</t>
+          <t>295.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-27.46</t>
+          <t>-12.43</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>788</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>92.45</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>88.76</t>
+          <t>82.39</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.61</v>
+        <v>-2.18</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.29</v>
+        <v>0.26</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>72.46000000000001</t>
+          <t>72.58000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>72.67</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AN9" t="n">
-        <v>69.65000000000001</v>
+        <v>69.77</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>68.66</t>
+          <t>68.67</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-20.53</t>
+          <t>-36.70</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>0.44</v>
+        <v>0.32</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-92.76</t>
+          <t>-93.37</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>135090.071932299</t>
+          <t>135025.7049295775</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>20650.0</t>
+          <t>21163.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>27984</v>
+        <v>27423</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>38579.4</t>
+          <t>31314.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>53075.12</v>
+        <v>53359.16</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-10595</t>
+          <t>-3891</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-2680.134508332671</t>
+          <t>-3925.806973229156</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-10606.93275384499</t>
+          <t>-10777.00553015982</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>20650.0</t>
+          <t>21163.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>16.23</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4217,17 +4217,17 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>284.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-64.13</t>
+          <t>-27.46</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>788</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>92.45</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>79.37</t>
+          <t>88.76</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>2.12</v>
+        <v>0.61</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1.64</v>
+        <v>-0.29</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>71.67999999999999</t>
+          <t>72.46000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>72.88</v>
+        <v>72.67</v>
       </c>
       <c r="AN10" t="n">
-        <v>69.48999999999999</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>68.65</t>
+          <t>68.66</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-32.33</t>
+          <t>-20.53</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-92.39</t>
+          <t>-92.76</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>135090.071932299</t>
+          <t>135025.7049295775</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>17071.0</t>
+          <t>20650.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>27609.6</v>
+        <v>27984</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>76972.1</t>
+          <t>38579.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>52850.06</v>
+        <v>53075.12</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-49362</t>
+          <t>-10595</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1238.898463694067</t>
+          <t>-2680.134508332671</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-9930.188332186495</t>
+          <t>-10606.93275384499</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>17071.0</t>
+          <t>20650.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,22 +4569,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>16.23</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>606.0</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-59.18</t>
+          <t>-64.13</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>788</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>75.71</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>79.37</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>3.77</v>
+        <v>2.12</v>
       </c>
       <c r="AI11" t="n">
-        <v>-3.2</v>
+        <v>-1.64</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>70.64</t>
+          <t>71.67999999999999</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>72.97</v>
+        <v>72.88</v>
       </c>
       <c r="AN11" t="n">
-        <v>69.34</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>68.62</t>
+          <t>68.65</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-52.47</t>
+          <t>-32.33</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.64</v>
+        <v>0.59</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-91.77</t>
+          <t>-92.39</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>135090.071932299</t>
+          <t>135025.7049295775</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>44659.0</t>
+          <t>17071.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>32445.2</v>
+        <v>27609.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>79491.1</t>
+          <t>76972.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>53294.76</v>
+        <v>52850.06</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-47045</t>
+          <t>-49362</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>341.3360578500112</t>
+          <t>-1238.898463694067</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-8225.29671795341</t>
+          <t>-9930.188332186495</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>44659.0</t>
+          <t>17071.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>16.23</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>464.0</t>
+          <t>606.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-58.34</t>
+          <t>-59.18</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>788</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>75.71</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>37.62</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>3.28</v>
+        <v>3.77</v>
       </c>
       <c r="AI12" t="n">
-        <v>-3.91</v>
+        <v>-3.2</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.64</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>73.05</v>
+        <v>72.97</v>
       </c>
       <c r="AN12" t="n">
-        <v>69.14</v>
+        <v>69.34</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>68.62</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-77.02</t>
+          <t>-52.47</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>0.17</v>
+        <v>0.3</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-90.69</t>
+          <t>-91.77</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>135090.071932299</t>
+          <t>135025.7049295775</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>33572.0</t>
+          <t>44659.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>33291.6</v>
+        <v>32445.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>79907.5</t>
+          <t>79491.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>52563.6</v>
+        <v>53294.76</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-46615</t>
+          <t>-47045</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>1898.905653450633</t>
+          <t>341.3360578500112</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-8451.833814836384</t>
+          <t>-8225.29671795341</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>33572.0</t>
+          <t>44659.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>16.23</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/電子觸控白板.xlsx
+++ b/Result/checksun_type/電子觸控白板.xlsx
@@ -913,7 +913,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>555.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -953,12 +953,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>63.81</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-7.35</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,22 +1068,22 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1094,63 +1094,63 @@
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>555</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>36.01</t>
         </is>
       </c>
       <c r="AP2" t="n">
-        <v>-0.85</v>
+        <v>-2.57</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.54</v>
+        <v>2.18</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>74.94</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>72.38</v>
+        <v>72.22</v>
       </c>
       <c r="AV2" t="n">
-        <v>71.02</v>
+        <v>71.2</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>69.06</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>0.84</v>
+        <v>0.65</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.65</v>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-91.53</t>
+          <t>-91.55</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1172,43 +1172,43 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>134938.3734177215</t>
+          <t>134833.5063202247</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>48622.0</t>
+          <t>40182.0</t>
         </is>
       </c>
       <c r="BF2" t="n">
-        <v>113180</v>
+        <v>65609.39999999999</v>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>69093.0</t>
+          <t>71046.2</t>
         </is>
       </c>
       <c r="BH2" t="n">
-        <v>60910.4</v>
+        <v>61587.24</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>44087</t>
+          <t>-5436</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>1579.900230302015</t>
+          <t>1339.913882168724</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>2828.111992466278</t>
+          <t>19.98896743562364</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>48622.0</t>
+          <t>40182.0</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1273,22 +1273,22 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>16.19</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>50.14</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2594</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1333,27 +1333,27 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>788.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1410,17 +1410,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>70.88</t>
+          <t>63.81</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1530,22 +1530,22 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1556,66 +1556,66 @@
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>555</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>53.03</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>49.49</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AP3" t="n">
-        <v>0.13</v>
+        <v>-0.85</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.78</v>
+        <v>3.54</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.94</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>72.39</v>
+        <v>72.38</v>
       </c>
       <c r="AV3" t="n">
-        <v>70.79000000000001</v>
+        <v>71.02</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>69.06</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>35.10</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-92.12</t>
+          <t>-91.53</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1634,43 +1634,43 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>134938.3734177215</t>
+          <t>134833.5063202247</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>59593.0</t>
+          <t>48622.0</t>
         </is>
       </c>
       <c r="BF3" t="n">
-        <v>112673</v>
+        <v>113180</v>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>65937.9</t>
+          <t>69093.0</t>
         </is>
       </c>
       <c r="BH3" t="n">
-        <v>60058.06</v>
+        <v>60910.4</v>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>46735</t>
+          <t>44087</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>1352.95263718124</t>
+          <t>1579.900230302015</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>5834.426599921979</t>
+          <t>2828.111992466278</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>59593.0</t>
+          <t>48622.0</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1735,22 +1735,22 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>16.19</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>50.14</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2594</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1795,27 +1795,27 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>742.0</t>
+          <t>788.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1872,17 +1872,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>64.16</t>
+          <t>70.88</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1992,92 +1992,92 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>555</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>46.97</t>
+          <t>53.03</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>65.15</t>
+          <t>49.49</t>
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>0.24</v>
+        <v>0.13</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.16</v>
+        <v>2.78</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>73.92</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>72.36</v>
+        <v>72.39</v>
       </c>
       <c r="AV4" t="n">
-        <v>70.55</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>68.94</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>35.10</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-92.81</t>
+          <t>-92.12</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -2096,43 +2096,43 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>134938.3734177215</t>
+          <t>134833.5063202247</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>55029.0</t>
+          <t>59593.0</t>
         </is>
       </c>
       <c r="BF4" t="n">
-        <v>105789</v>
+        <v>112673</v>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>64444.5</t>
+          <t>65937.9</t>
         </is>
       </c>
       <c r="BH4" t="n">
-        <v>59232.94</v>
+        <v>60058.06</v>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>41344</t>
+          <t>46735</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>538.1391894101968</t>
+          <t>1352.95263718124</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>8745.325089147183</t>
+          <t>5834.426599921979</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>55029.0</t>
+          <t>59593.0</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2197,22 +2197,22 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>16.19</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>50.14</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2594</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2257,27 +2257,27 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1658.0</t>
+          <t>742.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2334,17 +2334,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>55.98</t>
+          <t>64.16</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2454,22 +2454,22 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2480,66 +2480,66 @@
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>555</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>48.48</t>
+          <t>46.97</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>63.29</t>
+          <t>65.15</t>
         </is>
       </c>
       <c r="AP5" t="n">
-        <v>1.06</v>
+        <v>0.24</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.61</v>
+        <v>2.16</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>73.41999999999999</t>
+          <t>73.92</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>72.26000000000001</v>
+        <v>72.36</v>
       </c>
       <c r="AV5" t="n">
-        <v>70.37</v>
+        <v>70.55</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>68.94</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>38.86</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-93.51</t>
+          <t>-92.81</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2558,43 +2558,43 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>134938.3734177215</t>
+          <t>134833.5063202247</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>124621.0</t>
+          <t>55029.0</t>
         </is>
       </c>
       <c r="BF5" t="n">
-        <v>97174.60000000001</v>
+        <v>105789</v>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>62298.8</t>
+          <t>64444.5</t>
         </is>
       </c>
       <c r="BH5" t="n">
-        <v>58392.04</v>
+        <v>59232.94</v>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>34875</t>
+          <t>41344</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>-954.076428723801</t>
+          <t>538.1391894101968</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>13080.41846342792</t>
+          <t>8745.325089147183</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>124621.0</t>
+          <t>55029.0</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>16.19</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>50.14</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2594</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2719,27 +2719,27 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="CO5" t="inlineStr">
+        <is>
           <t>74.1</t>
-        </is>
-      </c>
-      <c r="CO5" t="inlineStr">
-        <is>
-          <t>74.2</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3696.0</t>
+          <t>1658.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2786,74 +2786,74 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-3.2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-1.19</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>55.98</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-12-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>77.6</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-4.44</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>46.43</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-12-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>71.9</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>77.6</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>77.6</t>
-        </is>
-      </c>
       <c r="T6" t="inlineStr">
         <is>
           <t>77.0</t>
@@ -2866,12 +2866,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2916,22 +2916,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>55.00</t>
+          <t>24.67</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2942,66 +2942,66 @@
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>555</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>48.48</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>71.16</t>
+          <t>63.29</t>
         </is>
       </c>
       <c r="AP6" t="n">
-        <v>6.62</v>
+        <v>1.06</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.83</v>
+        <v>1.61</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>73.41999999999999</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>72.18000000000001</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="AV6" t="n">
-        <v>70.19</v>
+        <v>70.37</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>68.84</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>46.64</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-94.27</t>
+          <t>-93.51</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -3020,43 +3020,43 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>134938.3734177215</t>
+          <t>134833.5063202247</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>278035.0</t>
+          <t>124621.0</t>
         </is>
       </c>
       <c r="BF6" t="n">
-        <v>76483</v>
+        <v>97174.60000000001</v>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>52233.5</t>
+          <t>62298.8</t>
         </is>
       </c>
       <c r="BH6" t="n">
-        <v>56172.26</v>
+        <v>58392.04</v>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>24249</t>
+          <t>34875</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>-3505.802772751387</t>
+          <t>-954.076428723801</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>11349.96548156372</t>
+          <t>13080.41846342792</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>278035.0</t>
+          <t>124621.0</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3121,22 +3121,22 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>16.19</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>50.14</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2594</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3181,27 +3181,27 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
@@ -3223,7 +3223,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>643.0</t>
+          <t>3696.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3258,27 +3258,27 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>-7.93</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3378,92 +3378,92 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>55.00</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>555</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>41.38</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>60.47</t>
+          <t>71.16</t>
         </is>
       </c>
       <c r="AP7" t="n">
-        <v>-0.33</v>
+        <v>6.62</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.21</v>
+        <v>0.83</v>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>71.84</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>71.98999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="AV7" t="n">
-        <v>69.97</v>
+        <v>70.19</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>68.74</t>
+          <t>68.84</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-41.23</t>
+          <t>50.94</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>0.23</v>
+        <v>0.67</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-95.00</t>
+          <t>-94.27</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -3482,48 +3482,48 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>134938.3734177215</t>
+          <t>134833.5063202247</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>46087.0</t>
+          <t>278035.0</t>
         </is>
       </c>
       <c r="BF7" t="n">
-        <v>25006</v>
+        <v>76483</v>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>26307.8</t>
+          <t>52233.5</t>
         </is>
       </c>
       <c r="BH7" t="n">
-        <v>50970.78</v>
+        <v>56172.26</v>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>-1301</t>
+          <t>24249</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-6206.851546263225</t>
+          <t>-3505.802772751387</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-7964.680402583843</t>
+          <t>11349.96548156372</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>46087.0</t>
+          <t>278035.0</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3583,22 +3583,22 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>16.19</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>50.14</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2594</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3643,27 +3643,27 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>643.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3720,17 +3720,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-25.64</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3770,32 +3770,32 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
+          <t>71.9</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3840,92 +3840,92 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>555</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>72.09</t>
+          <t>41.38</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>65.54</t>
+          <t>60.47</t>
         </is>
       </c>
       <c r="AP8" t="n">
-        <v>-0.08</v>
+        <v>-0.33</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.1</v>
+        <v>-0.21</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>72.16</t>
+          <t>71.84</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>72.09</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="AV8" t="n">
-        <v>69.89</v>
+        <v>69.97</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>68.72</t>
+          <t>68.74</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-36.20</t>
+          <t>-41.23</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-94.48</t>
+          <t>-95.00</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3944,43 +3944,43 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>134938.3734177215</t>
+          <t>134833.5063202247</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>25173.0</t>
+          <t>46087.0</t>
         </is>
       </c>
       <c r="BF8" t="n">
-        <v>19202.8</v>
+        <v>25006</v>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>25824.0</t>
+          <t>26307.8</t>
         </is>
       </c>
       <c r="BH8" t="n">
-        <v>50729.46</v>
+        <v>50970.78</v>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>-6621</t>
+          <t>-1301</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-5887.246299659477</t>
+          <t>-6206.851546263225</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-10421.00736555951</t>
+          <t>-7964.680402583843</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>25173.0</t>
+          <t>46087.0</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4045,22 +4045,22 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>16.19</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>50.14</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2594</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4182,17 +4182,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-18.07</t>
+          <t>-25.64</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4232,32 +4232,32 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
+          <t>71.9</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4302,92 +4302,92 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>555</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>72.09</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>72.33</t>
+          <t>65.54</t>
         </is>
       </c>
       <c r="AP9" t="n">
-        <v>-1.1</v>
+        <v>-0.08</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.39</v>
+        <v>0.1</v>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.16</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>72.12</v>
+        <v>72.09</v>
       </c>
       <c r="AV9" t="n">
-        <v>69.84</v>
+        <v>69.89</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>68.69</t>
+          <t>68.72</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-40.98</t>
+          <t>-36.20</t>
         </is>
       </c>
       <c r="AY9" t="n">
         <v>0.27</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-93.98</t>
+          <t>-94.48</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4406,43 +4406,43 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>134938.3734177215</t>
+          <t>134833.5063202247</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>11957.0</t>
+          <t>25173.0</t>
         </is>
       </c>
       <c r="BF9" t="n">
-        <v>23100</v>
+        <v>19202.8</v>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>28195.8</t>
+          <t>25824.0</t>
         </is>
       </c>
       <c r="BH9" t="n">
-        <v>52497.52</v>
+        <v>50729.46</v>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-5095</t>
+          <t>-6621</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-5062.92610585947</t>
+          <t>-5887.246299659477</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-11317.0813353262</t>
+          <t>-10421.00736555951</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>11957.0</t>
+          <t>25173.0</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>16.19</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>50.14</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2594</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4567,27 +4567,27 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>295.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4644,17 +4644,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-12.43</t>
+          <t>-18.07</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4694,32 +4694,32 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
+          <t>71.9</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4764,22 +4764,22 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -4790,66 +4790,66 @@
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>555</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>82.39</t>
+          <t>72.33</t>
         </is>
       </c>
       <c r="AP10" t="n">
-        <v>-2.18</v>
+        <v>-1.1</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.26</v>
+        <v>0.39</v>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>72.58000000000001</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>72.40000000000001</v>
+        <v>72.12</v>
       </c>
       <c r="AV10" t="n">
-        <v>69.77</v>
+        <v>69.84</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>68.67</t>
+          <t>68.69</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-36.70</t>
+          <t>-40.98</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.51</v>
+        <v>0.46</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-93.37</t>
+          <t>-93.98</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -4868,43 +4868,43 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>134938.3734177215</t>
+          <t>134833.5063202247</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>21163.0</t>
+          <t>11957.0</t>
         </is>
       </c>
       <c r="BF10" t="n">
-        <v>27423</v>
+        <v>23100</v>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>31314.7</t>
+          <t>28195.8</t>
         </is>
       </c>
       <c r="BH10" t="n">
-        <v>53359.16</v>
+        <v>52497.52</v>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>-3891</t>
+          <t>-5095</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>-3925.806973229156</t>
+          <t>-5062.92610585947</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-10777.00553015982</t>
+          <t>-11317.0813353262</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>21163.0</t>
+          <t>11957.0</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4979,12 +4979,12 @@
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>16.19</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>50.14</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2594</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5029,27 +5029,27 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>284.0</t>
+          <t>295.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5106,17 +5106,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-27.46</t>
+          <t>-12.43</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5156,32 +5156,32 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
+          <t>71.9</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -5252,66 +5252,66 @@
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>555</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>92.45</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>88.76</t>
+          <t>82.39</t>
         </is>
       </c>
       <c r="AP11" t="n">
-        <v>0.61</v>
+        <v>-2.18</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.29</v>
+        <v>0.26</v>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>72.46000000000001</t>
+          <t>72.58000000000001</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>72.67</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AV11" t="n">
-        <v>69.65000000000001</v>
+        <v>69.77</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>68.66</t>
+          <t>68.67</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-20.53</t>
+          <t>-36.70</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>0.44</v>
+        <v>0.32</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-92.76</t>
+          <t>-93.37</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -5330,43 +5330,43 @@
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>134938.3734177215</t>
+          <t>134833.5063202247</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>20650.0</t>
+          <t>21163.0</t>
         </is>
       </c>
       <c r="BF11" t="n">
-        <v>27984</v>
+        <v>27423</v>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>38579.4</t>
+          <t>31314.7</t>
         </is>
       </c>
       <c r="BH11" t="n">
-        <v>53075.12</v>
+        <v>53359.16</v>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>-10595</t>
+          <t>-3891</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>-2680.134508332671</t>
+          <t>-3925.806973229156</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>-10606.93275384499</t>
+          <t>-10777.00553015982</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>20650.0</t>
+          <t>21163.0</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>16.19</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5471,12 +5471,12 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>50.14</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2594</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
@@ -5501,17 +5501,17 @@
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CO11" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CP11" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>284.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-64.13</t>
+          <t>-27.46</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5618,32 +5618,32 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
+          <t>71.9</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5688,22 +5688,22 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5714,66 +5714,66 @@
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>555</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>92.45</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>79.37</t>
+          <t>88.76</t>
         </is>
       </c>
       <c r="AP12" t="n">
-        <v>2.12</v>
+        <v>0.61</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-1.64</v>
+        <v>-0.29</v>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>71.67999999999999</t>
+          <t>72.46000000000001</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>72.88</v>
+        <v>72.67</v>
       </c>
       <c r="AV12" t="n">
-        <v>69.48999999999999</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>68.65</t>
+          <t>68.66</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-32.33</t>
+          <t>-20.53</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-92.39</t>
+          <t>-92.76</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -5792,43 +5792,43 @@
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>134938.3734177215</t>
+          <t>134833.5063202247</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>17071.0</t>
+          <t>20650.0</t>
         </is>
       </c>
       <c r="BF12" t="n">
-        <v>27609.6</v>
+        <v>27984</v>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>76972.1</t>
+          <t>38579.4</t>
         </is>
       </c>
       <c r="BH12" t="n">
-        <v>52850.06</v>
+        <v>53075.12</v>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>-49362</t>
+          <t>-10595</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>-1238.898463694067</t>
+          <t>-2680.134508332671</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>-9930.188332186495</t>
+          <t>-10606.93275384499</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>17071.0</t>
+          <t>20650.0</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>16.19</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>50.14</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2594</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -5953,27 +5953,27 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">

--- a/Result/checksun_type/電子觸控白板.xlsx
+++ b/Result/checksun_type/電子觸控白板.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR12"/>
+  <dimension ref="A1:CV12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,345 +566,365 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>MA_death_cross_d</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d收盤價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2收盤價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>MACD_hist_diff</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>MACD_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -1048,325 +1068,345 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>-0.19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>2025/08/06</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>70.2</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>2025/07/29</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>68.1</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>71.9</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>8.26</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>-1.67</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr">
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>36.01</t>
         </is>
       </c>
-      <c r="AP2" t="n">
+      <c r="AT2" t="n">
         <v>-2.57</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AU2" t="n">
         <v>2.18</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>1.44</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>3.03</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>73.8</t>
         </is>
       </c>
-      <c r="AU2" t="n">
+      <c r="AY2" t="n">
         <v>72.22</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AZ2" t="n">
         <v>71.2</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>69.1</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>-0.84</t>
         </is>
       </c>
-      <c r="AY2" t="n">
+      <c r="BC2" t="n">
         <v>0.65</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BD2" t="n">
         <v>0.65</v>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>7.72</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>-91.55</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>134833.5063202247</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>40182.0</t>
         </is>
       </c>
-      <c r="BF2" t="n">
+      <c r="BJ2" t="n">
         <v>65609.39999999999</v>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>71046.2</t>
         </is>
       </c>
-      <c r="BH2" t="n">
+      <c r="BL2" t="n">
         <v>61587.24</v>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>-5436</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>1339.913882168724</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>19.98896743562364</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>40182.0</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>72.9</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>-1.37</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>117.8366423644483</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>90.00919392228472</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>22.16097965796244</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>3.56</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>2.74</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>24.14</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>15.66</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>6.00%</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>2.42%</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>50.14</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>2594</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>青雲-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>73.3</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>73.3</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>71.7</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>71.9</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>20.21</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 顯示器模組、記憶體、主機板、顯示卡** 平面顯示器 - 顯示器模組** 觸控面板 - 電子觸控白板、工業用設備</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1510,325 +1550,345 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>2025/08/06</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>70.2</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2025/07/29</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>68.1</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>71.9</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>9.60</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>-3.23</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr">
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="AP3" t="n">
+      <c r="AT3" t="n">
         <v>-0.85</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AU3" t="n">
         <v>3.54</v>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>1.92</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>2.83</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>74.94</t>
         </is>
       </c>
-      <c r="AU3" t="n">
+      <c r="AY3" t="n">
         <v>72.38</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AZ3" t="n">
         <v>71.02</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>69.06</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>27.93</t>
         </is>
       </c>
-      <c r="AY3" t="n">
+      <c r="BC3" t="n">
         <v>0.84</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BD3" t="n">
         <v>0.65</v>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>7.72</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>-91.53</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>134833.5063202247</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>48622.0</t>
         </is>
       </c>
-      <c r="BF3" t="n">
+      <c r="BJ3" t="n">
         <v>113180</v>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>69093.0</t>
         </is>
       </c>
-      <c r="BH3" t="n">
+      <c r="BL3" t="n">
         <v>60910.4</v>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>44087</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>1579.900230302015</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>2828.111992466278</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>48622.0</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>72.9</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>1.92</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>117.8366423644483</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>90.00919392228472</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>22.16097965796244</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>價漲量縮</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>3.68</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>2.74</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>24.14</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>15.66</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>6.00%</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>2.42%</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>50.14</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>2594</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>青雲-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>76.0</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>76.8</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>74.2</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>74.3</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>20.21</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 顯示器模組、記憶體、主機板、顯示卡** 平面顯示器 - 顯示器模組** 觸控面板 - 電子觸控白板、工業用設備</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1972,325 +2032,345 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>2025/08/06</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>70.2</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>2025/07/29</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>68.1</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>71.9</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>11.73</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>-2.95</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>53.03</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>49.49</t>
         </is>
       </c>
-      <c r="AP4" t="n">
+      <c r="AT4" t="n">
         <v>0.13</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AU4" t="n">
         <v>2.78</v>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>2.25</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>2.60</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>74.4</t>
         </is>
       </c>
-      <c r="AU4" t="n">
+      <c r="AY4" t="n">
         <v>72.39</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AZ4" t="n">
         <v>70.79000000000001</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>35.10</t>
         </is>
       </c>
-      <c r="AY4" t="n">
+      <c r="BC4" t="n">
         <v>0.82</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BD4" t="n">
         <v>0.61</v>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>7.72</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>-92.12</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>134833.5063202247</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>59593.0</t>
         </is>
       </c>
-      <c r="BF4" t="n">
+      <c r="BJ4" t="n">
         <v>112673</v>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>65937.9</t>
         </is>
       </c>
-      <c r="BH4" t="n">
+      <c r="BL4" t="n">
         <v>60058.06</v>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>46735</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>1352.95263718124</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>5834.426599921979</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>59593.0</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>72.9</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>2.19</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>117.8366423644483</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>90.00919392228472</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>22.16097965796244</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>價跌量縮</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>3.69</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>2.74</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>24.14</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>15.66</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>6.00%</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>2.42%</t>
         </is>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>50.14</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>2594</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>青雲-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>74.7</t>
         </is>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>76.7</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>74.5</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>74.5</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>20.21</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CU4" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 顯示器模組、記憶體、主機板、顯示卡** 平面顯示器 - 顯示器模組** 觸控面板 - 電子觸控白板、工業用設備</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2434,325 +2514,345 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
           <t>2025/08/06</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>70.2</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2025/07/29</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>68.1</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>71.9</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>11.04</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>-0.52</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr">
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>46.97</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>65.15</t>
         </is>
       </c>
-      <c r="AP5" t="n">
+      <c r="AT5" t="n">
         <v>0.24</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AU5" t="n">
         <v>2.16</v>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
         <is>
           <t>2.56</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>2.34</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>73.92</t>
         </is>
       </c>
-      <c r="AU5" t="n">
+      <c r="AY5" t="n">
         <v>72.36</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AZ5" t="n">
         <v>70.55</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>68.94</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>38.86</t>
         </is>
       </c>
-      <c r="AY5" t="n">
+      <c r="BC5" t="n">
         <v>0.77</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BD5" t="n">
         <v>0.55</v>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>7.72</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>-92.81</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>134833.5063202247</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>55029.0</t>
         </is>
       </c>
-      <c r="BF5" t="n">
+      <c r="BJ5" t="n">
         <v>105789</v>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>64444.5</t>
         </is>
       </c>
-      <c r="BH5" t="n">
+      <c r="BL5" t="n">
         <v>59232.94</v>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>41344</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>538.1391894101968</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>8745.325089147183</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>55029.0</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>72.9</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>1.65</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>117.8366423644483</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>90.00919392228472</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>22.16097965796244</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>3.67</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
         <is>
           <t>2.74</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>24.14</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>15.66</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>6.00%</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>2.42%</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>50.14</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>2594</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CM5" t="inlineStr">
         <is>
           <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>青雲-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>75.0</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>75.4</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>73.2</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>74.1</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>20.21</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CU5" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 顯示器模組、記憶體、主機板、顯示卡** 平面顯示器 - 顯示器模組** 觸控面板 - 電子觸控白板、工業用設備</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2896,325 +2996,345 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>2025/08/06</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>70.2</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>2025/07/29</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>68.1</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>71.9</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>24.67</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>-4.45</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr">
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>48.48</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>63.29</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="AT6" t="n">
         <v>1.06</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AU6" t="n">
         <v>1.61</v>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
         <is>
           <t>2.68</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>2.14</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>73.41999999999999</t>
         </is>
       </c>
-      <c r="AU6" t="n">
+      <c r="AY6" t="n">
         <v>72.26000000000001</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AZ6" t="n">
         <v>70.37</v>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>68.9</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>46.64</t>
         </is>
       </c>
-      <c r="AY6" t="n">
+      <c r="BC6" t="n">
         <v>0.73</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BD6" t="n">
         <v>0.5</v>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>7.72</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>-93.51</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>134833.5063202247</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>124621.0</t>
         </is>
       </c>
-      <c r="BF6" t="n">
+      <c r="BJ6" t="n">
         <v>97174.60000000001</v>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>62298.8</t>
         </is>
       </c>
-      <c r="BH6" t="n">
+      <c r="BL6" t="n">
         <v>58392.04</v>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>34875</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>-954.076428723801</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>13080.41846342792</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>124621.0</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
         <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BR6" t="inlineStr">
         <is>
           <t>72.9</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>1.78</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BZ6" t="inlineStr">
         <is>
           <t>117.8366423644483</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="CA6" t="inlineStr">
         <is>
           <t>90.00919392228472</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>22.16097965796244</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>價跌量增</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>3.67</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>2.74</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CG6" t="inlineStr">
         <is>
           <t>24.14</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
         <is>
           <t>15.66</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>6.00%</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>2.42%</t>
         </is>
       </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>50.14</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>2594</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>青雲-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
-      <c r="CL6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>77.6</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>77.6</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>74.1</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>74.2</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>20.21</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CU6" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 顯示器模組、記憶體、主機板、顯示卡** 平面顯示器 - 顯示器模組** 觸控面板 - 電子觸控白板、工業用設備</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3358,325 +3478,345 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
           <t>2025/08/06</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>70.2</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2025/07/29</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>68.1</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0.38</t>
-        </is>
-      </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>71.9</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>55.00</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>6.82</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr">
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>71.16</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="AT7" t="n">
         <v>6.62</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AU7" t="n">
         <v>0.83</v>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>2.83</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>1.97</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>72.78</t>
         </is>
       </c>
-      <c r="AU7" t="n">
+      <c r="AY7" t="n">
         <v>72.18000000000001</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AZ7" t="n">
         <v>70.19</v>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>68.84</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>50.94</t>
         </is>
       </c>
-      <c r="AY7" t="n">
+      <c r="BC7" t="n">
         <v>0.67</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BD7" t="n">
         <v>0.44</v>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>7.72</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>-94.27</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>134833.5063202247</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>278035.0</t>
         </is>
       </c>
-      <c r="BF7" t="n">
+      <c r="BJ7" t="n">
         <v>76483</v>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>52233.5</t>
         </is>
       </c>
-      <c r="BH7" t="n">
+      <c r="BL7" t="n">
         <v>56172.26</v>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>24249</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>-3505.802772751387</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>11349.96548156372</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>278035.0</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>72.9</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>6.45</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>117.8366423644483</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="CA7" t="inlineStr">
         <is>
           <t>90.00919392228472</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>22.16097965796244</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>價漲量增</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>3.84</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
         <is>
           <t>2.74</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CG7" t="inlineStr">
         <is>
           <t>24.14</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
         <is>
           <t>15.66</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>6.00%</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>2.42%</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>50.14</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>2594</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>青雲-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
-      <c r="CL7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>73.0</t>
         </is>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>78.0</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>72.3</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>77.6</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>20.21</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CU7" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 顯示器模組、記憶體、主機板、顯示卡** 平面顯示器 - 顯示器模組** 觸控面板 - 電子觸控白板、工業用設備</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3820,325 +3960,345 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
           <t>2025/08/06</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>70.2</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>2025/07/29</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>68.1</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>71.9</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>9.57</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>0.88</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr">
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>41.38</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>60.47</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="AT8" t="n">
         <v>-0.33</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AU8" t="n">
         <v>-0.21</v>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>2.89</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>1.79</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>71.84</t>
         </is>
       </c>
-      <c r="AU8" t="n">
+      <c r="AY8" t="n">
         <v>71.98999999999999</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AZ8" t="n">
         <v>69.97</v>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>68.74</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>-41.23</t>
         </is>
       </c>
-      <c r="AY8" t="n">
+      <c r="BC8" t="n">
         <v>0.23</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BD8" t="n">
         <v>0.39</v>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>7.72</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>-95.00</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>134833.5063202247</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>46087.0</t>
         </is>
       </c>
-      <c r="BF8" t="n">
+      <c r="BJ8" t="n">
         <v>25006</v>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>26307.8</t>
         </is>
       </c>
-      <c r="BH8" t="n">
+      <c r="BL8" t="n">
         <v>50970.78</v>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>-1301</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>-6206.851546263225</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-7964.680402583843</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>46087.0</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BR8" t="inlineStr">
         <is>
           <t>72.9</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>-1.78</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>117.8366423644483</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>90.00919392228472</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>22.16097965796244</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>3.54</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>2.74</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
         <is>
           <t>24.14</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>15.66</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>6.00%</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>2.42%</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>50.14</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
         <is>
           <t>2594</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CM8" t="inlineStr">
         <is>
           <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>青雲-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
-      <c r="CL8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>71.5</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>72.5</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>70.1</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>71.6</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>20.21</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CU8" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 顯示器模組、記憶體、主機板、顯示卡** 平面顯示器 - 顯示器模組** 觸控面板 - 電子觸控白板、工業用設備</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4282,325 +4442,345 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
           <t>2025/08/06</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>70.2</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>2025/07/29</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>68.1</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>71.9</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>5.21</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1.57</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr">
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>72.09</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>65.54</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="AT9" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AU9" t="n">
         <v>0.1</v>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>3.14</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>1.70</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>72.16</t>
         </is>
       </c>
-      <c r="AU9" t="n">
+      <c r="AY9" t="n">
         <v>72.09</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AZ9" t="n">
         <v>69.89</v>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>68.72</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>-36.20</t>
         </is>
       </c>
-      <c r="AY9" t="n">
+      <c r="BC9" t="n">
         <v>0.27</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BD9" t="n">
         <v>0.43</v>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>7.72</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>-94.48</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>134833.5063202247</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>25173.0</t>
         </is>
       </c>
-      <c r="BF9" t="n">
+      <c r="BJ9" t="n">
         <v>19202.8</v>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>25824.0</t>
         </is>
       </c>
-      <c r="BH9" t="n">
+      <c r="BL9" t="n">
         <v>50729.46</v>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>-6621</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>-5887.246299659477</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-10421.00736555951</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>25173.0</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BR9" t="inlineStr">
         <is>
           <t>72.9</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>-1.10</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>117.8366423644483</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
         <is>
           <t>90.00919392228472</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>22.16097965796244</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>3.57</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
         <is>
           <t>2.74</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CG9" t="inlineStr">
         <is>
           <t>24.14</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
         <is>
           <t>15.66</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>6.00%</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>2.42%</t>
         </is>
       </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>50.14</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
         <is>
           <t>2594</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
         <is>
           <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>青雲-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CK9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
-      <c r="CL9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>71.5</t>
         </is>
       </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>72.5</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>70.6</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>72.1</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>20.21</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CU9" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 顯示器模組、記憶體、主機板、顯示卡** 平面顯示器 - 顯示器模組** 觸控面板 - 電子觸控白板、工業用設備</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4744,325 +4924,345 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>2025/08/06</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>70.2</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>2025/07/29</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>68.1</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>71.9</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>2.47</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>-1.68</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr">
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>67.92</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>72.33</t>
         </is>
       </c>
-      <c r="AP10" t="n">
+      <c r="AT10" t="n">
         <v>-1.1</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AU10" t="n">
         <v>0.39</v>
       </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>3.26</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>1.67</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>72.4</t>
         </is>
       </c>
-      <c r="AU10" t="n">
+      <c r="AY10" t="n">
         <v>72.12</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AZ10" t="n">
         <v>69.84</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>68.69</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>-40.98</t>
         </is>
       </c>
-      <c r="AY10" t="n">
+      <c r="BC10" t="n">
         <v>0.27</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BD10" t="n">
         <v>0.46</v>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>7.72</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>-93.98</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BH10" t="inlineStr">
         <is>
           <t>134833.5063202247</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>11957.0</t>
         </is>
       </c>
-      <c r="BF10" t="n">
+      <c r="BJ10" t="n">
         <v>23100</v>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>28195.8</t>
         </is>
       </c>
-      <c r="BH10" t="n">
+      <c r="BL10" t="n">
         <v>52497.52</v>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>-5095</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>-5062.92610585947</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-11317.0813353262</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>11957.0</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
+      <c r="BQ10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BR10" t="inlineStr">
         <is>
           <t>72.9</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>-1.78</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>117.8366423644483</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>90.00919392228472</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>22.16097965796244</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>3.54</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
         <is>
           <t>2.74</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CG10" t="inlineStr">
         <is>
           <t>24.14</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
         <is>
           <t>15.66</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>6.00%</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>2.42%</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>50.14</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>2594</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
         <is>
           <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>青雲-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>71.7</t>
         </is>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>73.0</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>71.4</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>71.6</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>20.21</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CU10" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 顯示器模組、記憶體、主機板、顯示卡** 平面顯示器 - 顯示器模組** 觸控面板 - 電子觸控白板、工業用設備</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5206,325 +5406,345 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
           <t>2025/08/06</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>70.2</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>2025/07/29</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>68.1</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>71.9</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>4.39</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>-2.68</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr">
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AR11" t="inlineStr">
         <is>
           <t>56.6</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>82.39</t>
         </is>
       </c>
-      <c r="AP11" t="n">
+      <c r="AT11" t="n">
         <v>-2.18</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AU11" t="n">
         <v>0.26</v>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>3.76</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>1.61</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>72.58000000000001</t>
         </is>
       </c>
-      <c r="AU11" t="n">
+      <c r="AY11" t="n">
         <v>72.40000000000001</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AZ11" t="n">
         <v>69.77</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>68.67</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>-36.70</t>
         </is>
       </c>
-      <c r="AY11" t="n">
+      <c r="BC11" t="n">
         <v>0.32</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BD11" t="n">
         <v>0.51</v>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>7.72</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>-93.37</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>134833.5063202247</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>21163.0</t>
         </is>
       </c>
-      <c r="BF11" t="n">
+      <c r="BJ11" t="n">
         <v>27423</v>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>31314.7</t>
         </is>
       </c>
-      <c r="BH11" t="n">
+      <c r="BL11" t="n">
         <v>53359.16</v>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>-3891</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>-3925.806973229156</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-10777.00553015982</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>21163.0</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BR11" t="inlineStr">
         <is>
           <t>72.9</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>-2.61</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>117.8366423644483</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
         <is>
           <t>90.00919392228472</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>22.16097965796244</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>3.51</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
         <is>
           <t>2.74</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CG11" t="inlineStr">
         <is>
           <t>24.14</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>15.66</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>6.00%</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>2.42%</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>50.14</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>2594</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
         <is>
           <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CN11" t="inlineStr">
         <is>
           <t>青雲-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
-      <c r="CL11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>72.9</t>
         </is>
       </c>
-      <c r="CM11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>72.9</t>
         </is>
       </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>71.0</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CS11" t="inlineStr">
         <is>
           <t>71.0</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>20.21</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CU11" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 顯示器模組、記憶體、主機板、顯示卡** 平面顯示器 - 顯示器模組** 觸控面板 - 電子觸控白板、工業用設備</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5668,325 +5888,345 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>2025/08/06</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>70.2</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>2025/07/29</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>68.1</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
       <c r="AG12" t="inlineStr">
         <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>71.9</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>4.23</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>0.70</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr">
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AR12" t="inlineStr">
         <is>
           <t>92.45</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>88.76</t>
         </is>
       </c>
-      <c r="AP12" t="n">
+      <c r="AT12" t="n">
         <v>0.61</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AU12" t="n">
         <v>-0.29</v>
       </c>
-      <c r="AR12" t="inlineStr">
+      <c r="AV12" t="inlineStr">
         <is>
           <t>4.34</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>1.45</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>72.46000000000001</t>
         </is>
       </c>
-      <c r="AU12" t="n">
+      <c r="AY12" t="n">
         <v>72.67</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AZ12" t="n">
         <v>69.65000000000001</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>68.66</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>-20.53</t>
         </is>
       </c>
-      <c r="AY12" t="n">
+      <c r="BC12" t="n">
         <v>0.44</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BD12" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="BA12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>7.72</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>-92.76</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
         <is>
           <t>134833.5063202247</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>20650.0</t>
         </is>
       </c>
-      <c r="BF12" t="n">
+      <c r="BJ12" t="n">
         <v>27984</v>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>38579.4</t>
         </is>
       </c>
-      <c r="BH12" t="n">
+      <c r="BL12" t="n">
         <v>53075.12</v>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>-10595</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>-2680.134508332671</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-10606.93275384499</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>20650.0</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BR12" t="inlineStr">
         <is>
           <t>72.9</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>青雲</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>117.8366423644483</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
         <is>
           <t>90.00919392228472</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>22.16097965796244</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CE12" t="inlineStr">
         <is>
           <t>3.61</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
         <is>
           <t>2.74</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CG12" t="inlineStr">
         <is>
           <t>24.14</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
         <is>
           <t>15.66</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>6.00%</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>2.42%</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>50.14</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
         <is>
           <t>2594</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CM12" t="inlineStr">
         <is>
           <t>記憶體產品83.89%、板卡產品7.07%、伺服器6.59%、其他2.45% (2024年)</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CN12" t="inlineStr">
         <is>
           <t>青雲-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CK12" t="inlineStr">
+      <c r="CO12" t="inlineStr">
         <is>
           <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
-      <c r="CL12" t="inlineStr">
+      <c r="CP12" t="inlineStr">
         <is>
           <t>72.9</t>
         </is>
       </c>
-      <c r="CM12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>73.2</t>
         </is>
       </c>
-      <c r="CN12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>72.1</t>
         </is>
       </c>
-      <c r="CO12" t="inlineStr">
+      <c r="CS12" t="inlineStr">
         <is>
           <t>72.9</t>
         </is>
       </c>
-      <c r="CP12" t="inlineStr">
+      <c r="CT12" t="inlineStr">
         <is>
           <t>20.21</t>
         </is>
       </c>
-      <c r="CQ12" t="inlineStr">
+      <c r="CU12" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 顯示器模組、記憶體、主機板、顯示卡** 平面顯示器 - 顯示器模組** 觸控面板 - 電子觸控白板、工業用設備</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/電子觸控白板.xlsx
+++ b/Result/checksun_type/電子觸控白板.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>555.0</t>
+          <t>660.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,172 +958,172 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>70.2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-3.24</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-32.03</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-12-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>71.9</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-1.19</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-7.65</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-12-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>77.6</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>-2.36</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>6.74</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2025/08/04</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>71.3</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2025/08/06</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>70.2</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>2025/07/29</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>68.1</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>71.9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>77.6</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>72.7</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>-7.35</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>6.74</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2025/08/04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>71.3</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2025/08/06</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>2025/07/29</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>68.1</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>2025/12/15</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>71.9</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
-      </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,66 +1134,66 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>660</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>36.01</t>
+          <t>18.33</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-2.57</v>
+        <v>-3.84</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.18</v>
+        <v>1.09</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>72.22</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>71.2</v>
+        <v>71.34</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>69.1</t>
+          <t>69.14</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-40.05</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>0.65</v>
+        <v>0.36</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-91.55</t>
+          <t>-92.32</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,48 +1212,48 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>134833.5063202247</t>
+          <t>134742.6058906031</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>40182.0</t>
+          <t>46681.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>65609.39999999999</v>
+        <v>50021.4</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>71046.2</t>
+          <t>73598.0</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>61587.24</v>
+        <v>62398.68</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-5436</t>
+          <t>-23576</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>1339.913882168724</t>
+          <t>909.3468427163493</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>19.98896743562364</t>
+          <t>-1458.771874271712</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>40182.0</t>
+          <t>46681.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>50.14</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>555.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>63.81</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1520,12 +1520,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-7.35</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,63 +1616,63 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>660</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>36.01</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-0.85</v>
+        <v>-2.57</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.54</v>
+        <v>2.18</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>74.94</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>72.38</v>
+        <v>72.22</v>
       </c>
       <c r="AZ3" t="n">
-        <v>71.02</v>
+        <v>71.2</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>69.06</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>0.84</v>
+        <v>0.65</v>
       </c>
       <c r="BD3" t="n">
         <v>0.65</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-91.53</t>
+          <t>-91.55</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>134833.5063202247</t>
+          <t>134742.6058906031</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>48622.0</t>
+          <t>40182.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>113180</v>
+        <v>65609.39999999999</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>69093.0</t>
+          <t>71046.2</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>60910.4</v>
+        <v>61587.24</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>44087</t>
+          <t>-5436</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>1579.900230302015</t>
+          <t>1339.913882168724</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>2828.111992466278</t>
+          <t>19.98896743562364</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>48622.0</t>
+          <t>40182.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,22 +1795,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>50.14</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>788.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-5.84</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>70.88</t>
+          <t>63.81</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2002,12 +2002,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,66 +2098,66 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>660</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>53.03</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>49.49</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>0.13</v>
+        <v>-0.85</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.78</v>
+        <v>3.54</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.94</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>72.39</v>
+        <v>72.38</v>
       </c>
       <c r="AZ4" t="n">
-        <v>70.79000000000001</v>
+        <v>71.02</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>69.06</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>35.10</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-92.12</t>
+          <t>-91.53</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>134833.5063202247</t>
+          <t>134742.6058906031</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>59593.0</t>
+          <t>48622.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>112673</v>
+        <v>113180</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>65937.9</t>
+          <t>69093.0</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>60058.06</v>
+        <v>60910.4</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>46735</t>
+          <t>44087</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>1352.95263718124</t>
+          <t>1579.900230302015</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>5834.426599921979</t>
+          <t>2828.111992466278</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>59593.0</t>
+          <t>48622.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,22 +2277,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>50.14</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>742.0</t>
+          <t>788.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>64.16</t>
+          <t>70.88</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,87 +2559,87 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>660</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>46.97</t>
+          <t>53.03</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>65.15</t>
+          <t>49.49</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>0.24</v>
+        <v>0.13</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.16</v>
+        <v>2.78</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>73.92</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>72.36</v>
+        <v>72.39</v>
       </c>
       <c r="AZ5" t="n">
-        <v>70.55</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>68.94</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>35.10</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-92.81</t>
+          <t>-92.12</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>134833.5063202247</t>
+          <t>134742.6058906031</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>55029.0</t>
+          <t>59593.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>105789</v>
+        <v>112673</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>64444.5</t>
+          <t>65937.9</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>59232.94</v>
+        <v>60058.06</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>41344</t>
+          <t>46735</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>538.1391894101968</t>
+          <t>1352.95263718124</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>8745.325089147183</t>
+          <t>5834.426599921979</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>55029.0</t>
+          <t>59593.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,22 +2759,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>50.14</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1658.0</t>
+          <t>742.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>55.98</t>
+          <t>64.16</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,66 +3062,66 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>660</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>48.48</t>
+          <t>46.97</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>63.29</t>
+          <t>65.15</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1.06</v>
+        <v>0.24</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.61</v>
+        <v>2.16</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>73.41999999999999</t>
+          <t>73.92</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>72.26000000000001</v>
+        <v>72.36</v>
       </c>
       <c r="AZ6" t="n">
-        <v>70.37</v>
+        <v>70.55</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>68.94</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>38.86</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-93.51</t>
+          <t>-92.81</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>134833.5063202247</t>
+          <t>134742.6058906031</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>124621.0</t>
+          <t>55029.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>97174.60000000001</v>
+        <v>105789</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>62298.8</t>
+          <t>64444.5</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>58392.04</v>
+        <v>59232.94</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>34875</t>
+          <t>41344</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-954.076428723801</t>
+          <t>538.1391894101968</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>13080.41846342792</t>
+          <t>8745.325089147183</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>124621.0</t>
+          <t>55029.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>50.14</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="CS6" t="inlineStr">
+        <is>
           <t>74.1</t>
-        </is>
-      </c>
-      <c r="CS6" t="inlineStr">
-        <is>
-          <t>74.2</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3696.0</t>
+          <t>1658.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,172 +3368,172 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-5.7</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-3.24</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>55.98</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-12-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>77.6</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-7.93</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-1.19</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>46.43</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-12-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>71.9</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>77.6</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>-4.38</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>6.74</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025/08/04</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>71.3</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2025/08/06</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>70.2</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2025/07/29</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>68.1</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
         <is>
           <t>71.9</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>77.6</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>72.7</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>7.93</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>6.74</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025/08/04</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>71.3</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>0.38</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2025/08/06</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>2025/07/29</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>68.1</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>2025/12/15</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>71.9</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
-      </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>55.00</t>
+          <t>24.67</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,66 +3544,66 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>660</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>48.48</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>71.16</t>
+          <t>63.29</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>6.62</v>
+        <v>1.06</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.83</v>
+        <v>1.61</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>73.41999999999999</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>70.19</v>
+        <v>70.37</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>68.84</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>46.64</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-94.27</t>
+          <t>-93.51</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>134833.5063202247</t>
+          <t>134742.6058906031</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>278035.0</t>
+          <t>124621.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>76483</v>
+        <v>97174.60000000001</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>52233.5</t>
+          <t>62298.8</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>56172.26</v>
+        <v>58392.04</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>24249</t>
+          <t>34875</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-3505.802772751387</t>
+          <t>-954.076428723801</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>11349.96548156372</t>
+          <t>13080.41846342792</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>278035.0</t>
+          <t>124621.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,22 +3723,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>50.14</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3825,7 +3825,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>643.0</t>
+          <t>3696.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,22 +3860,22 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-10.54</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,87 +4005,87 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>55.00</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>660</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>41.38</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>60.47</t>
+          <t>71.16</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>-0.33</v>
+        <v>6.62</v>
       </c>
       <c r="AU8" t="n">
-        <v>-0.21</v>
+        <v>0.83</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>71.84</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>71.98999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>69.97</v>
+        <v>70.19</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>68.74</t>
+          <t>68.84</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-41.23</t>
+          <t>50.94</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>0.23</v>
+        <v>0.67</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-95.00</t>
+          <t>-94.27</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,48 +4104,48 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>134833.5063202247</t>
+          <t>134742.6058906031</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>46087.0</t>
+          <t>278035.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>25006</v>
+        <v>76483</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>26307.8</t>
+          <t>52233.5</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>50970.78</v>
+        <v>56172.26</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-1301</t>
+          <t>24249</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-6206.851546263225</t>
+          <t>-3505.802772751387</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-7964.680402583843</t>
+          <t>11349.96548156372</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>46087.0</t>
+          <t>278035.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,22 +4205,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>50.14</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>643.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-25.64</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,87 +4487,87 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>660</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>72.09</t>
+          <t>41.38</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>65.54</t>
+          <t>60.47</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>-0.08</v>
+        <v>-0.33</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.1</v>
+        <v>-0.21</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>72.16</t>
+          <t>71.84</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>72.09</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>69.89</v>
+        <v>69.97</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>68.72</t>
+          <t>68.74</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-36.20</t>
+          <t>-41.23</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-94.48</t>
+          <t>-95.00</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>134833.5063202247</t>
+          <t>134742.6058906031</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>25173.0</t>
+          <t>46087.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>19202.8</v>
+        <v>25006</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>25824.0</t>
+          <t>26307.8</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>50729.46</v>
+        <v>50970.78</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-6621</t>
+          <t>-1301</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-5887.246299659477</t>
+          <t>-6206.851546263225</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-10421.00736555951</t>
+          <t>-7964.680402583843</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>25173.0</t>
+          <t>46087.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,22 +4687,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>50.14</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-2.71</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-18.07</t>
+          <t>-25.64</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,87 +4969,87 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>660</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>72.09</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>72.33</t>
+          <t>65.54</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>-1.1</v>
+        <v>-0.08</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.39</v>
+        <v>0.1</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.16</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>72.12</v>
+        <v>72.09</v>
       </c>
       <c r="AZ10" t="n">
-        <v>69.84</v>
+        <v>69.89</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>68.69</t>
+          <t>68.72</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-40.98</t>
+          <t>-36.20</t>
         </is>
       </c>
       <c r="BC10" t="n">
         <v>0.27</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-93.98</t>
+          <t>-94.48</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>134833.5063202247</t>
+          <t>134742.6058906031</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>11957.0</t>
+          <t>25173.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>23100</v>
+        <v>19202.8</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>28195.8</t>
+          <t>25824.0</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>52497.52</v>
+        <v>50729.46</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-5095</t>
+          <t>-6621</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-5062.92610585947</t>
+          <t>-5887.246299659477</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-11317.0813353262</t>
+          <t>-10421.00736555951</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>11957.0</t>
+          <t>25173.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>50.14</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>295.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-12.43</t>
+          <t>-18.07</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,66 +5472,66 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>660</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>82.39</t>
+          <t>72.33</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>-2.18</v>
+        <v>-1.1</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.26</v>
+        <v>0.39</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>72.58000000000001</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>72.40000000000001</v>
+        <v>72.12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>69.77</v>
+        <v>69.84</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>68.67</t>
+          <t>68.69</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-36.70</t>
+          <t>-40.98</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.51</v>
+        <v>0.46</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-93.37</t>
+          <t>-93.98</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>134833.5063202247</t>
+          <t>134742.6058906031</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>21163.0</t>
+          <t>11957.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>27423</v>
+        <v>23100</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>31314.7</t>
+          <t>28195.8</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>53359.16</v>
+        <v>52497.52</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-3891</t>
+          <t>-5095</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-3925.806973229156</t>
+          <t>-5062.92610585947</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-10777.00553015982</t>
+          <t>-11317.0813353262</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>21163.0</t>
+          <t>11957.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>50.14</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>284.0</t>
+          <t>295.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-27.46</t>
+          <t>-12.43</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,66 +5954,66 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>660</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>92.45</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>88.76</t>
+          <t>82.39</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>0.61</v>
+        <v>-2.18</v>
       </c>
       <c r="AU12" t="n">
-        <v>-0.29</v>
+        <v>0.26</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>72.46000000000001</t>
+          <t>72.58000000000001</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>72.67</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AZ12" t="n">
-        <v>69.65000000000001</v>
+        <v>69.77</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>68.66</t>
+          <t>68.67</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-20.53</t>
+          <t>-36.70</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>0.44</v>
+        <v>0.32</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-92.76</t>
+          <t>-93.37</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>134833.5063202247</t>
+          <t>134742.6058906031</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>20650.0</t>
+          <t>21163.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>27984</v>
+        <v>27423</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>38579.4</t>
+          <t>31314.7</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>53075.12</v>
+        <v>53359.16</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-10595</t>
+          <t>-3891</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-2680.134508332671</t>
+          <t>-3925.806973229156</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-10606.93275384499</t>
+          <t>-10777.00553015982</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>20650.0</t>
+          <t>21163.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>50.14</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6203,17 +6203,17 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/電子觸控白板.xlsx
+++ b/Result/checksun_type/電子觸控白板.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>660.0</t>
+          <t>517.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,172 +958,172 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>72.2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-2.87</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-38.93</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-12-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>71.9</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>6.74</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2025/08/04</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>71.3</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2025/08/06</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
           <t>70.2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-3.24</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-32.03</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-12-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>77.6</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>2025/07/29</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>68.1</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>71.9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>72.7</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>-2.36</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>6.74</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2025/08/04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>71.3</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2025/08/06</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>2025/07/29</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>68.1</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>2025/12/15</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>71.9</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
-      </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,66 +1134,66 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.03</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>18.33</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-3.84</v>
+        <v>-0.58</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.09</v>
+        <v>0.46</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.61999999999999</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>72.20999999999999</v>
+        <v>72.28</v>
       </c>
       <c r="AZ2" t="n">
-        <v>71.34</v>
+        <v>71.52</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>69.14</t>
+          <t>69.19</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-40.05</t>
+          <t>-46.75</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>0.36</v>
+        <v>0.28</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-92.32</t>
+          <t>-93.12</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>134742.6058906031</t>
+          <t>134632.4789915966</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>46681.0</t>
+          <t>37408.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>50021.4</v>
+        <v>46497.2</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>73598.0</t>
+          <t>76143.1</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>62398.68</v>
+        <v>62908.84</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-23576</t>
+          <t>-29645</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>909.3468427163493</t>
+          <t>284.3842258969026</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-1458.771874271712</t>
+          <t>-3152.910166610054</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>46681.0</t>
+          <t>37408.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,22 +1313,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>15.73</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>49.56</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>555.0</t>
+          <t>660.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,172 +1440,172 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>70.2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-2.87</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-32.03</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-12-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>71.9</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-2.42</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-3.24</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-7.65</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-12-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>77.6</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-2.36</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>6.74</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025/08/04</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>71.3</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2025/08/06</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>70.2</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2025/07/29</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>68.1</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>71.9</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>77.6</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>72.7</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>-7.35</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>6.74</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025/08/04</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>71.3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2025/08/06</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2025/07/29</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>68.1</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>2025/12/15</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>71.9</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
-      </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,66 +1616,66 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>36.01</t>
+          <t>18.33</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-2.57</v>
+        <v>-3.84</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.18</v>
+        <v>1.09</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>72.22</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>71.2</v>
+        <v>71.34</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>69.1</t>
+          <t>69.14</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-40.05</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>0.65</v>
+        <v>0.36</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-91.55</t>
+          <t>-92.32</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,48 +1694,48 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>134742.6058906031</t>
+          <t>134632.4789915966</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>40182.0</t>
+          <t>46681.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>65609.39999999999</v>
+        <v>50021.4</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>71046.2</t>
+          <t>73598.0</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>61587.24</v>
+        <v>62398.68</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-5436</t>
+          <t>-23576</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>1339.913882168724</t>
+          <t>909.3468427163493</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>19.98896743562364</t>
+          <t>-1458.771874271712</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>40182.0</t>
+          <t>46681.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>15.73</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>49.56</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1897,7 +1897,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>555.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>63.81</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2002,12 +2002,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-7.35</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,63 +2098,63 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>36.01</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>-0.85</v>
+        <v>-2.57</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.54</v>
+        <v>2.18</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>74.94</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>72.38</v>
+        <v>72.22</v>
       </c>
       <c r="AZ4" t="n">
-        <v>71.02</v>
+        <v>71.2</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>69.06</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>0.84</v>
+        <v>0.65</v>
       </c>
       <c r="BD4" t="n">
         <v>0.65</v>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-91.53</t>
+          <t>-91.55</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>134742.6058906031</t>
+          <t>134632.4789915966</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>48622.0</t>
+          <t>40182.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>113180</v>
+        <v>65609.39999999999</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>69093.0</t>
+          <t>71046.2</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>60910.4</v>
+        <v>61587.24</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>44087</t>
+          <t>-5436</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>1579.900230302015</t>
+          <t>1339.913882168724</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>2828.111992466278</t>
+          <t>19.98896743562364</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>48622.0</t>
+          <t>40182.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,22 +2277,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>15.73</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>49.56</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>788.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>70.88</t>
+          <t>63.81</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,66 +2580,66 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>53.03</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>49.49</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>0.13</v>
+        <v>-0.85</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.78</v>
+        <v>3.54</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.94</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>72.39</v>
+        <v>72.38</v>
       </c>
       <c r="AZ5" t="n">
-        <v>70.79000000000001</v>
+        <v>71.02</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>69.06</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>35.10</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-92.12</t>
+          <t>-91.53</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>134742.6058906031</t>
+          <t>134632.4789915966</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>59593.0</t>
+          <t>48622.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>112673</v>
+        <v>113180</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>65937.9</t>
+          <t>69093.0</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>60058.06</v>
+        <v>60910.4</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>46735</t>
+          <t>44087</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>1352.95263718124</t>
+          <t>1579.900230302015</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>5834.426599921979</t>
+          <t>2828.111992466278</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>59593.0</t>
+          <t>48622.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,22 +2759,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>15.73</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>49.56</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>742.0</t>
+          <t>788.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>64.16</t>
+          <t>70.88</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,87 +3041,87 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>46.97</t>
+          <t>53.03</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>65.15</t>
+          <t>49.49</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>0.24</v>
+        <v>0.13</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.16</v>
+        <v>2.78</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>73.92</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>72.36</v>
+        <v>72.39</v>
       </c>
       <c r="AZ6" t="n">
-        <v>70.55</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>68.94</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>35.10</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-92.81</t>
+          <t>-92.12</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>134742.6058906031</t>
+          <t>134632.4789915966</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>55029.0</t>
+          <t>59593.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>105789</v>
+        <v>112673</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>64444.5</t>
+          <t>65937.9</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>59232.94</v>
+        <v>60058.06</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>41344</t>
+          <t>46735</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>538.1391894101968</t>
+          <t>1352.95263718124</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>8745.325089147183</t>
+          <t>5834.426599921979</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>55029.0</t>
+          <t>59593.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>15.73</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>49.56</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1658.0</t>
+          <t>742.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.7</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>55.98</t>
+          <t>64.16</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3448,12 +3448,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,66 +3544,66 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>48.48</t>
+          <t>46.97</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>63.29</t>
+          <t>65.15</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1.06</v>
+        <v>0.24</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.61</v>
+        <v>2.16</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>73.41999999999999</t>
+          <t>73.92</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>72.26000000000001</v>
+        <v>72.36</v>
       </c>
       <c r="AZ7" t="n">
-        <v>70.37</v>
+        <v>70.55</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>68.94</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>38.86</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-93.51</t>
+          <t>-92.81</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>134742.6058906031</t>
+          <t>134632.4789915966</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>124621.0</t>
+          <t>55029.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>97174.60000000001</v>
+        <v>105789</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>62298.8</t>
+          <t>64444.5</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>58392.04</v>
+        <v>59232.94</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>34875</t>
+          <t>41344</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-954.076428723801</t>
+          <t>538.1391894101968</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>13080.41846342792</t>
+          <t>8745.325089147183</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>124621.0</t>
+          <t>55029.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>15.73</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>49.56</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="CS7" t="inlineStr">
+        <is>
           <t>74.1</t>
-        </is>
-      </c>
-      <c r="CS7" t="inlineStr">
-        <is>
-          <t>74.2</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3696.0</t>
+          <t>1658.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,172 +3850,172 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-2.77</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-2.87</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>55.98</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-12-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>77.6</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-10.54</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-3.24</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>46.43</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-12-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>71.9</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>77.6</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>-4.38</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>6.74</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025/08/04</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>71.3</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2025/08/06</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>70.2</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>2025/07/29</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>68.1</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>71.9</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>77.6</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>72.7</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>7.93</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>6.74</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025/08/04</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>71.3</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>0.38</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2025/08/06</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>2025/07/29</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>68.1</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>2025/12/15</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>71.9</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
-      </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>55.00</t>
+          <t>24.67</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,66 +4026,66 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>48.48</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>71.16</t>
+          <t>63.29</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>6.62</v>
+        <v>1.06</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.83</v>
+        <v>1.61</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>73.41999999999999</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>72.18000000000001</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>70.19</v>
+        <v>70.37</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>68.84</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>46.64</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-94.27</t>
+          <t>-93.51</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>134742.6058906031</t>
+          <t>134632.4789915966</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>278035.0</t>
+          <t>124621.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>76483</v>
+        <v>97174.60000000001</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>52233.5</t>
+          <t>62298.8</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>56172.26</v>
+        <v>58392.04</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>24249</t>
+          <t>34875</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-3505.802772751387</t>
+          <t>-954.076428723801</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>11349.96548156372</t>
+          <t>13080.41846342792</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>278035.0</t>
+          <t>124621.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,22 +4205,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>15.73</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>49.56</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4307,7 +4307,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>643.0</t>
+          <t>3696.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,22 +4342,22 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-7.48</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,87 +4487,87 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>55.00</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>41.38</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>60.47</t>
+          <t>71.16</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>-0.33</v>
+        <v>6.62</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.21</v>
+        <v>0.83</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>71.84</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>71.98999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>69.97</v>
+        <v>70.19</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>68.74</t>
+          <t>68.84</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-41.23</t>
+          <t>50.94</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>0.23</v>
+        <v>0.67</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-95.00</t>
+          <t>-94.27</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,48 +4586,48 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>134742.6058906031</t>
+          <t>134632.4789915966</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>46087.0</t>
+          <t>278035.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>25006</v>
+        <v>76483</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>26307.8</t>
+          <t>52233.5</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>50970.78</v>
+        <v>56172.26</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-1301</t>
+          <t>24249</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-6206.851546263225</t>
+          <t>-3505.802772751387</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-7964.680402583843</t>
+          <t>11349.96548156372</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>46087.0</t>
+          <t>278035.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,22 +4687,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>15.73</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>49.56</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>643.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.71</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-25.64</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,87 +4969,87 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>72.09</t>
+          <t>41.38</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>65.54</t>
+          <t>60.47</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>-0.08</v>
+        <v>-0.33</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.1</v>
+        <v>-0.21</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>72.16</t>
+          <t>71.84</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>72.09</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>69.89</v>
+        <v>69.97</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>68.72</t>
+          <t>68.74</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-36.20</t>
+          <t>-41.23</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-94.48</t>
+          <t>-95.00</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>134742.6058906031</t>
+          <t>134632.4789915966</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>25173.0</t>
+          <t>46087.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>19202.8</v>
+        <v>25006</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>25824.0</t>
+          <t>26307.8</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>50729.46</v>
+        <v>50970.78</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-6621</t>
+          <t>-1301</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-5887.246299659477</t>
+          <t>-6206.851546263225</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-10421.00736555951</t>
+          <t>-7964.680402583843</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>25173.0</t>
+          <t>46087.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>15.73</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>49.56</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-18.07</t>
+          <t>-25.64</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,87 +5451,87 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>72.09</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>72.33</t>
+          <t>65.54</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>-1.1</v>
+        <v>-0.08</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.39</v>
+        <v>0.1</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.16</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>72.12</v>
+        <v>72.09</v>
       </c>
       <c r="AZ11" t="n">
-        <v>69.84</v>
+        <v>69.89</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>68.69</t>
+          <t>68.72</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-40.98</t>
+          <t>-36.20</t>
         </is>
       </c>
       <c r="BC11" t="n">
         <v>0.27</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-93.98</t>
+          <t>-94.48</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>134742.6058906031</t>
+          <t>134632.4789915966</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>11957.0</t>
+          <t>25173.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>23100</v>
+        <v>19202.8</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>28195.8</t>
+          <t>25824.0</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>52497.52</v>
+        <v>50729.46</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-5095</t>
+          <t>-6621</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-5062.92610585947</t>
+          <t>-5887.246299659477</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-11317.0813353262</t>
+          <t>-10421.00736555951</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>11957.0</t>
+          <t>25173.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>15.73</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>49.56</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>295.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-12.43</t>
+          <t>-18.07</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,66 +5954,66 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>82.39</t>
+          <t>72.33</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>-2.18</v>
+        <v>-1.1</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.26</v>
+        <v>0.39</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>72.58000000000001</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>72.40000000000001</v>
+        <v>72.12</v>
       </c>
       <c r="AZ12" t="n">
-        <v>69.77</v>
+        <v>69.84</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>68.67</t>
+          <t>68.69</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-36.70</t>
+          <t>-40.98</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.51</v>
+        <v>0.46</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-93.37</t>
+          <t>-93.98</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>134742.6058906031</t>
+          <t>134632.4789915966</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>21163.0</t>
+          <t>11957.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>27423</v>
+        <v>23100</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>31314.7</t>
+          <t>28195.8</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>53359.16</v>
+        <v>52497.52</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-3891</t>
+          <t>-5095</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-3925.806973229156</t>
+          <t>-5062.92610585947</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-10777.00553015982</t>
+          <t>-11317.0813353262</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>21163.0</t>
+          <t>11957.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>15.73</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>49.56</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/電子觸控白板.xlsx
+++ b/Result/checksun_type/電子觸控白板.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>517.0</t>
+          <t>984.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-38.93</t>
+          <t>-39.34</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>14.64</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,66 +1134,66 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>984</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
+          <t>54.05</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
           <t>27.03</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>10.68</t>
-        </is>
-      </c>
       <c r="AT2" t="n">
-        <v>-0.58</v>
+        <v>2.26</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.46</v>
+        <v>0.17</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>72.61999999999999</t>
+          <t>72.56000000000002</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>72.28</v>
+        <v>72.44</v>
       </c>
       <c r="AZ2" t="n">
-        <v>71.52</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>69.19</t>
+          <t>69.28</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-46.75</t>
+          <t>-23.77</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>0.28</v>
+        <v>0.38</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-93.12</t>
+          <t>-93.51</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>134632.4789915966</t>
+          <t>134595.9881118881</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>37408.0</t>
+          <t>72361.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>46497.2</v>
+        <v>49050.8</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>76143.1</t>
+          <t>80861.9</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>62908.84</v>
+        <v>62712.4</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-29645</t>
+          <t>-31811</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>284.3842258969026</t>
+          <t>-11.445534561334</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-3152.910166610054</t>
+          <t>-1638.509217081635</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>37408.0</t>
+          <t>72361.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,22 +1313,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>15.73</t>
+          <t>16.17</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>49.56</t>
+          <t>49.39</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1373,27 +1373,27 @@
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
+          <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>660.0</t>
+          <t>517.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,172 +1440,172 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>72.2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-2.97</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-38.93</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-12-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>71.9</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>6.74</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025/08/04</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>71.3</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2025/08/06</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
           <t>70.2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-2.87</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-32.03</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-12-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>77.6</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2025/07/29</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>68.1</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>71.9</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>72.7</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-2.36</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>6.74</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025/08/04</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>71.3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2025/08/06</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2025/07/29</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>68.1</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>2025/12/15</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>71.9</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
-      </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,66 +1616,66 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>984</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.03</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>18.33</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-3.84</v>
+        <v>-0.58</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.09</v>
+        <v>0.46</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.61999999999999</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>72.20999999999999</v>
+        <v>72.28</v>
       </c>
       <c r="AZ3" t="n">
-        <v>71.34</v>
+        <v>71.52</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>69.14</t>
+          <t>69.19</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-40.05</t>
+          <t>-46.75</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>0.36</v>
+        <v>0.28</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-92.32</t>
+          <t>-93.12</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>134632.4789915966</t>
+          <t>134595.9881118881</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>46681.0</t>
+          <t>37408.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>50021.4</v>
+        <v>46497.2</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>73598.0</t>
+          <t>76143.1</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>62398.68</v>
+        <v>62908.84</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-23576</t>
+          <t>-29645</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>909.3468427163493</t>
+          <t>284.3842258969026</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-1458.771874271712</t>
+          <t>-3152.910166610054</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>46681.0</t>
+          <t>37408.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,22 +1795,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>15.73</t>
+          <t>16.17</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>49.56</t>
+          <t>49.39</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1855,27 +1855,27 @@
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
+          <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>555.0</t>
+          <t>660.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,172 +1922,172 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>70.2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>5.39</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-2.97</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-32.03</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-12-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>71.9</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.42</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-2.87</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-7.65</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-12-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>77.6</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-2.36</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>6.74</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025/08/04</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>71.3</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2025/08/06</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>70.2</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2025/07/29</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>68.1</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>71.9</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>77.6</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>72.7</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>-7.35</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>6.74</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025/08/04</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>71.3</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2025/08/06</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2025/07/29</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>68.1</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2025/12/15</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>71.9</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
-      </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,66 +2098,66 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>984</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>36.01</t>
+          <t>18.33</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>-2.57</v>
+        <v>-3.84</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.18</v>
+        <v>1.09</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>72.22</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>71.2</v>
+        <v>71.34</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>69.1</t>
+          <t>69.14</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-40.05</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>0.65</v>
+        <v>0.36</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-91.55</t>
+          <t>-92.32</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,48 +2176,48 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>134632.4789915966</t>
+          <t>134595.9881118881</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>40182.0</t>
+          <t>46681.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>65609.39999999999</v>
+        <v>50021.4</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>71046.2</t>
+          <t>73598.0</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>61587.24</v>
+        <v>62398.68</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-5436</t>
+          <t>-23576</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>1339.913882168724</t>
+          <t>909.3468427163493</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>19.98896743562364</t>
+          <t>-1458.771874271712</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>40182.0</t>
+          <t>46681.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>15.73</t>
+          <t>16.17</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>49.56</t>
+          <t>49.39</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2337,27 +2337,27 @@
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
+          <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2379,7 +2379,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>645.0</t>
+          <t>555.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>63.81</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-7.35</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,63 +2580,63 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>984</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>36.01</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>-0.85</v>
+        <v>-2.57</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.54</v>
+        <v>2.18</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>74.94</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>72.38</v>
+        <v>72.22</v>
       </c>
       <c r="AZ5" t="n">
-        <v>71.02</v>
+        <v>71.2</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>69.06</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>0.84</v>
+        <v>0.65</v>
       </c>
       <c r="BD5" t="n">
         <v>0.65</v>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-91.53</t>
+          <t>-91.55</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>134632.4789915966</t>
+          <t>134595.9881118881</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>48622.0</t>
+          <t>40182.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>113180</v>
+        <v>65609.39999999999</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>69093.0</t>
+          <t>71046.2</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>60910.4</v>
+        <v>61587.24</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>44087</t>
+          <t>-5436</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>1579.900230302015</t>
+          <t>1339.913882168724</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>2828.111992466278</t>
+          <t>19.98896743562364</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>48622.0</t>
+          <t>40182.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,22 +2759,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>15.73</t>
+          <t>16.17</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>49.56</t>
+          <t>49.39</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2819,27 +2819,27 @@
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
+          <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>788.0</t>
+          <t>645.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.88</t>
+          <t>63.81</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,66 +3062,66 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>984</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>53.03</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>49.49</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>0.13</v>
+        <v>-0.85</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.78</v>
+        <v>3.54</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.94</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>72.39</v>
+        <v>72.38</v>
       </c>
       <c r="AZ6" t="n">
-        <v>70.79000000000001</v>
+        <v>71.02</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>69.06</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>35.10</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-92.12</t>
+          <t>-91.53</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>134632.4789915966</t>
+          <t>134595.9881118881</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>59593.0</t>
+          <t>48622.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>112673</v>
+        <v>113180</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>65937.9</t>
+          <t>69093.0</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>60058.06</v>
+        <v>60910.4</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>46735</t>
+          <t>44087</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>1352.95263718124</t>
+          <t>1579.900230302015</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>5834.426599921979</t>
+          <t>2828.111992466278</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>59593.0</t>
+          <t>48622.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>15.73</t>
+          <t>16.17</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>49.56</t>
+          <t>49.39</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3301,27 +3301,27 @@
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
+          <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>742.0</t>
+          <t>788.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>64.16</t>
+          <t>70.88</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3448,12 +3448,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,87 +3523,87 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>984</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>46.97</t>
+          <t>53.03</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>65.15</t>
+          <t>49.49</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>0.24</v>
+        <v>0.13</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.16</v>
+        <v>2.78</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>73.92</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>72.36</v>
+        <v>72.39</v>
       </c>
       <c r="AZ7" t="n">
-        <v>70.55</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>68.94</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>35.10</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-92.81</t>
+          <t>-92.12</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>134632.4789915966</t>
+          <t>134595.9881118881</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>55029.0</t>
+          <t>59593.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>105789</v>
+        <v>112673</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>64444.5</t>
+          <t>65937.9</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>59232.94</v>
+        <v>60058.06</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>41344</t>
+          <t>46735</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>538.1391894101968</t>
+          <t>1352.95263718124</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>8745.325089147183</t>
+          <t>5834.426599921979</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>55029.0</t>
+          <t>59593.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,22 +3723,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>15.73</t>
+          <t>16.17</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>49.56</t>
+          <t>49.39</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3783,27 +3783,27 @@
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
+          <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1658.0</t>
+          <t>742.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>55.98</t>
+          <t>64.16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,66 +4026,66 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>984</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>48.48</t>
+          <t>46.97</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>63.29</t>
+          <t>65.15</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1.06</v>
+        <v>0.24</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.61</v>
+        <v>2.16</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>73.41999999999999</t>
+          <t>73.92</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>72.26000000000001</v>
+        <v>72.36</v>
       </c>
       <c r="AZ8" t="n">
-        <v>70.37</v>
+        <v>70.55</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>68.94</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>38.86</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-93.51</t>
+          <t>-92.81</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>134632.4789915966</t>
+          <t>134595.9881118881</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>124621.0</t>
+          <t>55029.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>97174.60000000001</v>
+        <v>105789</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>62298.8</t>
+          <t>64444.5</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>58392.04</v>
+        <v>59232.94</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>34875</t>
+          <t>41344</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-954.076428723801</t>
+          <t>538.1391894101968</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>13080.41846342792</t>
+          <t>8745.325089147183</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>124621.0</t>
+          <t>55029.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>15.73</t>
+          <t>16.17</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>49.56</t>
+          <t>49.39</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4265,27 +4265,27 @@
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
+          <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="CS8" t="inlineStr">
+        <is>
           <t>74.1</t>
-        </is>
-      </c>
-      <c r="CS8" t="inlineStr">
-        <is>
-          <t>74.2</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3696.0</t>
+          <t>1658.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,172 +4332,172 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-2.97</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>55.98</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-12-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-11-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>77.6</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-7.48</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-2.87</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>46.43</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-12-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-11-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>71.9</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>77.6</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>-4.38</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>6.74</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025/08/04</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>71.3</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2025/08/06</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>70.2</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>2025/07/29</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>68.1</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
         <is>
           <t>71.9</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>77.6</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>72.7</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>7.93</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>6.74</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025/08/04</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>71.3</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>0.38</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2025/08/06</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>70.2</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>2025/07/29</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>68.1</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>2025/12/15</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>71.9</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
-      </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>55.00</t>
+          <t>24.67</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,66 +4508,66 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>984</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>48.48</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>71.16</t>
+          <t>63.29</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>6.62</v>
+        <v>1.06</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.83</v>
+        <v>1.61</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>73.41999999999999</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>72.18000000000001</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>70.19</v>
+        <v>70.37</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>68.84</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>46.64</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-94.27</t>
+          <t>-93.51</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>134632.4789915966</t>
+          <t>134595.9881118881</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>278035.0</t>
+          <t>124621.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>76483</v>
+        <v>97174.60000000001</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>52233.5</t>
+          <t>62298.8</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>56172.26</v>
+        <v>58392.04</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>24249</t>
+          <t>34875</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-3505.802772751387</t>
+          <t>-954.076428723801</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>11349.96548156372</t>
+          <t>13080.41846342792</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>278035.0</t>
+          <t>124621.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,22 +4687,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>15.73</t>
+          <t>16.17</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>49.56</t>
+          <t>49.39</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4747,27 +4747,27 @@
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
+          <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4789,7 +4789,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b